--- a/content/yarns.xlsx
+++ b/content/yarns.xlsx
@@ -10,65 +10,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!A1:AC64</definedName>
   </definedNames>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Maskerummet Review</author>
-  </authors>
-  <commentList>
-    <comment ref="F20" authorId="0">
-      <text>
-        <t xml:space="preserve">⚠ MULIG FEJL
-Gemte værdi: sport
-Korrekt kategori er "lace" – Ravelry og producent angiver lace/fingering. Kilde: ravelry.com</t>
-      </text>
-    </comment>
-    <comment ref="I20" authorId="0">
-      <text>
-        <t xml:space="preserve">⚠ MULIG FEJL
-Gemte værdi: 5.0
-Korrekt min-pind er 3,5 mm (enkelt tråd 3,5–6 mm). Kilde: gepardgarn.dk</t>
-      </text>
-    </comment>
-    <comment ref="I45" authorId="0">
-      <text>
-        <t xml:space="preserve">⚠ MULIG FEJL
-Gemte værdi: 3.5
-Korrekt anbefalet pind er 6,0 mm (fast pind). Kilde: permin.dk / lindehobby.com</t>
-      </text>
-    </comment>
-    <comment ref="J45" authorId="0">
-      <text>
-        <t xml:space="preserve">⚠ MULIG FEJL
-Gemte værdi: 15.0
-Korrekt anbefalet pind er 6,0 mm. Værdien 15 er fejl. Kilde: permin.dk / lindehobby.com</t>
-      </text>
-    </comment>
-    <comment ref="I46" authorId="0">
-      <text>
-        <t xml:space="preserve">⚠ MULIG FEJL
-Gemte værdi: 3.5
-Korrekt anbefalet pind er 6,0 mm (fast pind). Kilde: lindehobby.com/permin-bella-color</t>
-      </text>
-    </comment>
-    <comment ref="J46" authorId="0">
-      <text>
-        <t xml:space="preserve">⚠ MULIG FEJL
-Gemte værdi: 15.0
-Korrekt anbefalet pind er 6,0 mm. Værdien 15 er fejl. Kilde: lindehobby.com/permin-bella-color</t>
-      </text>
-    </comment>
-    <comment ref="E50" authorId="0">
-      <text>
-        <t xml:space="preserve">⚠ MULIG FEJL
-Gemte værdi: Bomuld
-Korrekt fiber er 100% Lyocell (pailletter er 100% polyester). Kilde: woolwarehouse.co.uk / urbanyarns.com</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
@@ -460,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA65"/>
+  <dimension ref="A1:AA66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -546,6 +487,9 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
       <c r="B2" t="str">
         <v>BC Garn</v>
       </c>
@@ -576,6 +520,24 @@
       <c r="K2">
         <v>25</v>
       </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
       <c r="R2" t="str">
         <v>handvask</v>
       </c>
@@ -590,6 +552,18 @@
       </c>
       <c r="V2" t="str">
         <v>["GOTS"]</v>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
       </c>
       <c r="AA2" t="str">
         <v>[{"fiber":"uld","percentage":55},{"fiber":"bomuld","percentage":45}]</v>
@@ -671,11 +645,17 @@
       <c r="Y3" t="str">
         <v>Luxor er et merceriseret bomuldsgarn i fingering-tykkelse (100% bomuld). Merceriseringen giver garnet en smuk glans, stærke og klare farver samt en meget tydelig maskedefinition. hBomulden stammer fra USA, mens garnet spindes og farves i Serbien. Farvestofferne er uden animalske ingredienser, så garnet kan betegnes som vegansk. Luxor kan maskinvaskes (op til 40 °C), men glansen kan aftage en smule over tid.</v>
       </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
       <c r="AA3" t="str">
         <v>[{"fiber":"merceriseret_bomuld","percentage":100}]</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
       <c r="B4" t="str">
         <v>BC Garn</v>
       </c>
@@ -706,6 +686,24 @@
       <c r="K4">
         <v>16</v>
       </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
       <c r="R4" t="str">
         <v>maskinvask_30</v>
       </c>
@@ -721,17 +719,35 @@
       <c r="V4" t="str">
         <v>["GOTS"]</v>
       </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
       <c r="AA4" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
       <c r="B5" t="str">
         <v>Drops</v>
       </c>
       <c r="C5" t="str">
         <v>Air</v>
       </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
       <c r="E5" t="str">
         <v>alpaka/uld/nylon</v>
       </c>
@@ -756,9 +772,15 @@
       <c r="L5">
         <v>22</v>
       </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
       <c r="N5" t="str">
         <v>Chainette/blown — fibre blæst ind i en tynd nylon-tube i stedet for klassisk spinding</v>
       </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
       <c r="P5" t="str">
         <v>chainette</v>
       </c>
@@ -788,6 +810,9 @@
       </c>
       <c r="Y5" t="str">
         <v>Lofty "blown" garn hvor baby-alpaka og merinould blæses ind i en tynd nylon-tube i stedet for at blive spundet. Færdige plagg er 30-35% lettere end tilsvarende tykkelse i klassisk spundet garn. Meget populær til behagelige oversize sweatre.</v>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
       </c>
       <c r="AA5" t="str">
         <v>[{"fiber":"baby_alpaka","percentage":65},{"fiber":"nylon_polyamid","percentage":28},{"fiber":"merinould","percentage":7}]</v>
@@ -803,6 +828,9 @@
       <c r="C6" t="str">
         <v>Alaska</v>
       </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
       <c r="E6" t="str">
         <v>Uld</v>
       </c>
@@ -848,6 +876,9 @@
       <c r="S6" t="str">
         <v>Norge</v>
       </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
       <c r="U6" t="str">
         <v>i_produktion</v>
       </c>
@@ -862,6 +893,9 @@
       </c>
       <c r="Y6" t="str">
         <v>Billigt budget-garn. Kan filtes.</v>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
       </c>
       <c r="AA6" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -877,6 +911,9 @@
       <c r="C7" t="str">
         <v>Alpaca</v>
       </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
       <c r="E7" t="str">
         <v>Alpaka</v>
       </c>
@@ -939,6 +976,9 @@
       </c>
       <c r="Y7" t="str">
         <v>Klassisk, let alpakagarn med fantastisk drapering og farvemætning. Populært til sjaler og lette projekter. Kradser ikke og er blødt mod huden. Et af DROPS' ældste og mest elskede kvaliteter.</v>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
       </c>
       <c r="AA7" t="str">
         <v>[{"fiber":"alpaka","percentage":100}]</v>
@@ -954,6 +994,9 @@
       <c r="C8" t="str">
         <v>Brushed Alpaca Silk</v>
       </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
       <c r="E8" t="str">
         <v>Alpaka-blanding</v>
       </c>
@@ -984,6 +1027,9 @@
       <c r="N8" t="str">
         <v>Brushed single, børstet superfin alpaka med silkekerne, kraftig halo</v>
       </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
       <c r="P8" t="str">
         <v>brushed_singles</v>
       </c>
@@ -996,6 +1042,9 @@
       <c r="S8" t="str">
         <v>Peru</v>
       </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
       <c r="U8" t="str">
         <v>i_produktion</v>
       </c>
@@ -1019,12 +1068,18 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
       <c r="B9" t="str">
         <v>Drops</v>
       </c>
       <c r="C9" t="str">
         <v>Flora</v>
       </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
       <c r="E9" t="str">
         <v>uld/alpaka</v>
       </c>
@@ -1049,6 +1104,9 @@
       <c r="L9">
         <v>32</v>
       </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
       <c r="N9" t="str">
         <v>4-trådet plied fingering, uld + superfin alpaka, medium twist</v>
       </c>
@@ -1084,6 +1142,9 @@
       </c>
       <c r="Y9" t="str">
         <v>Slidstærkt fingering-garn med alpaka-blanding — særligt populær til sokker pga. holdbarheden. Tynd nok til colorwork og sjaler, blød nok til barnetøj.</v>
+      </c>
+      <c r="Z9" t="str">
+        <v/>
       </c>
       <c r="AA9" t="str">
         <v>[{"fiber":"uld","percentage":65},{"fiber":"alpaka","percentage":35}]</v>
@@ -1099,6 +1160,9 @@
       <c r="C10" t="str">
         <v>Karisma</v>
       </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
       <c r="E10" t="str">
         <v>Uld</v>
       </c>
@@ -1161,6 +1225,9 @@
       </c>
       <c r="Y10" t="str">
         <v>En af de absolut mest populære DROPS-kvaliteter. Slidstærkt, superwash-behandlet uldgarn til en meget prisvenlig pris. Fast twist giver god maskedefinition — god til farvemønstre.</v>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
       </c>
       <c r="AA10" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -1176,6 +1243,9 @@
       <c r="C11" t="str">
         <v>Merino Extra Fine</v>
       </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
       <c r="E11" t="str">
         <v>Merinould</v>
       </c>
@@ -1238,6 +1308,9 @@
       </c>
       <c r="Y11" t="str">
         <v>Det foretrukne DK-garn fra DROPS — alsidigt, blødt og maskinvaskbart. Et af DROPS' absolut bedst sælgende garner i Danmark. Stor farvepalette og skarp pris.</v>
+      </c>
+      <c r="Z11" t="str">
+        <v/>
       </c>
       <c r="AA11" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -1253,6 +1326,9 @@
       <c r="C12" t="str">
         <v>Safran</v>
       </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
       <c r="E12" t="str">
         <v>Bomuld</v>
       </c>
@@ -1315,6 +1391,9 @@
       </c>
       <c r="Y12" t="str">
         <v>Go-to bomuldsgarn til sommerstrik og karklude. Enorm farvepalette og skarp pris — under 25 kr per nøgle. OEKO-TEX certificeret. Maskinvask 40°C på skåneprogram.</v>
+      </c>
+      <c r="Z12" t="str">
+        <v/>
       </c>
       <c r="AA12" t="str">
         <v>[{"fiber":"bomuld","percentage":100}]</v>
@@ -1330,6 +1409,9 @@
       <c r="C13" t="str">
         <v>Wave</v>
       </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
       <c r="E13" t="str">
         <v>Merinould-blanding</v>
       </c>
@@ -1360,6 +1442,9 @@
       <c r="N13" t="str">
         <v>Plied merino-silke-blanding, medium twist, blød og let glansfuld pga. silken</v>
       </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
       <c r="P13" t="str">
         <v>plied</v>
       </c>
@@ -1372,6 +1457,9 @@
       <c r="S13" t="str">
         <v>Italien</v>
       </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
       <c r="U13" t="str">
         <v>i_produktion</v>
       </c>
@@ -1387,17 +1475,26 @@
       <c r="Y13" t="str">
         <v>Specialgarn — ikke bredt distribueret i Danmark.</v>
       </c>
+      <c r="Z13" t="str">
+        <v/>
+      </c>
       <c r="AA13" t="str">
         <v>[{"fiber":"merinould","percentage":75},{"fiber":"silke","percentage":25}]</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
       <c r="B14" t="str">
         <v>Filcolana</v>
       </c>
       <c r="C14" t="str">
         <v>Anina</v>
       </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
       <c r="E14" t="str">
         <v>merino</v>
       </c>
@@ -1422,9 +1519,18 @@
       <c r="L14">
         <v>40</v>
       </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
       <c r="O14">
         <v>4</v>
       </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
       <c r="Q14" t="str">
         <v>superwash</v>
       </c>
@@ -1434,8 +1540,26 @@
       <c r="S14" t="str">
         <v>Peru</v>
       </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
       <c r="U14" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
+        <v/>
       </c>
       <c r="AA14" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -1451,6 +1575,9 @@
       <c r="C15" t="str">
         <v>Arwetta Classic</v>
       </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
       <c r="E15" t="str">
         <v>Uld</v>
       </c>
@@ -1514,11 +1641,17 @@
       <c r="Y15" t="str">
         <v>Min go-to sokkegarn — slidstærk pga. nylon</v>
       </c>
+      <c r="Z15" t="str">
+        <v/>
+      </c>
       <c r="AA15" t="str">
         <v>[{"fiber":"merinould","percentage":80},{"fiber":"nylon_polyamid","percentage":20}]</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
       <c r="B16" t="str">
         <v>Filcolana</v>
       </c>
@@ -1552,9 +1685,21 @@
       <c r="L16">
         <v>25</v>
       </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
       <c r="O16">
         <v>4</v>
       </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
       <c r="R16" t="str">
         <v>handvask</v>
       </c>
@@ -1566,6 +1711,21 @@
       </c>
       <c r="U16" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="str">
+        <v/>
       </c>
       <c r="AA16" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -1581,6 +1741,9 @@
       <c r="C17" t="str">
         <v>Tilia</v>
       </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
       <c r="E17" t="str">
         <v>Kid mohair</v>
       </c>
@@ -1610,6 +1773,9 @@
       </c>
       <c r="N17" t="str">
         <v>Brushed kid mohair single med silke, langfibret, kraftig halo</v>
+      </c>
+      <c r="O17" t="str">
+        <v/>
       </c>
       <c r="P17" t="str">
         <v>brushed_singles</v>
@@ -1643,6 +1809,9 @@
 _x000d__x000d_
 Kombinationen af silke og en let sky af mohair giver et luftigt, blødt og elegant udtryk – og er noget af det mest luksuriøse garn, man kan ønske sig at strikke med, både alene og som følgetråd.</v>
       </c>
+      <c r="Z17" t="str">
+        <v>/garn-eksempler/filcolana-tilia.jpg</v>
+      </c>
       <c r="AA17" t="str">
         <v>[{"fiber":"kid_mohair","percentage":70},{"fiber":"silke","percentage":30}]</v>
       </c>
@@ -1657,6 +1826,9 @@
       <c r="C18" t="str">
         <v>Ombelle</v>
       </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
       <c r="E18" t="str">
         <v>Kid mohair-blanding</v>
       </c>
@@ -1687,6 +1859,9 @@
       <c r="N18" t="str">
         <v>Brushed mohair-blanding, single ply med langt halo</v>
       </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
       <c r="P18" t="str">
         <v>brushed_singles</v>
       </c>
@@ -1699,6 +1874,9 @@
       <c r="S18" t="str">
         <v>Frankrig</v>
       </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
       <c r="U18" t="str">
         <v>i_produktion</v>
       </c>
@@ -1714,11 +1892,17 @@
       <c r="Y18" t="str">
         <v>Fransk mohair-klassiker. Samme fibersammensætning som Permin Bella, men strikkes på meget mindre pind — fin let kvalitet snarere end chunky.</v>
       </c>
+      <c r="Z18" t="str">
+        <v/>
+      </c>
       <c r="AA18" t="str">
         <v>[{"fiber":"kid_mohair","percentage":75},{"fiber":"uld","percentage":20},{"fiber":"nylon_polyamid","percentage":5}]</v>
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
       <c r="B19" t="str">
         <v>Gepard</v>
       </c>
@@ -1749,17 +1933,50 @@
       <c r="K19">
         <v>22</v>
       </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
       <c r="R19" t="str">
         <v>maskinvask_30</v>
       </c>
       <c r="S19" t="str">
         <v>Italien</v>
       </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
       <c r="U19" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V19" t="str">
         <v>["GOTS (bomuld)","Oeko-Tex 100"]</v>
+      </c>
+      <c r="W19" t="str">
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <v/>
+      </c>
+      <c r="Y19" t="str">
+        <v/>
+      </c>
+      <c r="Z19" t="str">
+        <v/>
       </c>
       <c r="AA19" t="str">
         <v>[{"fiber":"bomuld","percentage":50},{"fiber":"merinould","percentage":50}]</v>
@@ -1775,6 +1992,9 @@
       <c r="C20" t="str">
         <v>Kid Silk 5</v>
       </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
       <c r="E20" t="str">
         <v>Kid mohair</v>
       </c>
@@ -1805,6 +2025,9 @@
       <c r="N20" t="str">
         <v>Brushed single, kid mohair med silke, langfibret og kraftig halo</v>
       </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
       <c r="P20" t="str">
         <v>brushed_singles</v>
       </c>
@@ -1835,17 +2058,26 @@
       <c r="Y20" t="str">
         <v>Bliver løs i det med en tråd og dyr, hvis man skal strikke med 2 tråde</v>
       </c>
+      <c r="Z20" t="str">
+        <v/>
+      </c>
       <c r="AA20" t="str">
         <v>[{"fiber":"kid_mohair","percentage":80},{"fiber":"silke","percentage":20}]</v>
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
       <c r="B21" t="str">
         <v>Gepard</v>
       </c>
       <c r="C21" t="str">
         <v>Puno</v>
       </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
       <c r="E21" t="str">
         <v>alpaka/merino/nylon</v>
       </c>
@@ -1867,14 +2099,50 @@
       <c r="K21">
         <v>12.5</v>
       </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
       <c r="R21" t="str">
         <v>handvask</v>
       </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
       <c r="U21" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V21" t="str">
         <v>["RAS","RWS"]</v>
+      </c>
+      <c r="W21" t="str">
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
+        <v/>
+      </c>
+      <c r="Z21" t="str">
+        <v/>
       </c>
       <c r="AA21" t="str">
         <v>[{"fiber":"baby_alpaka","percentage":68},{"fiber":"merinould","percentage":10},{"fiber":"nylon_polyamid","percentage":22}]</v>
@@ -1890,6 +2158,9 @@
       <c r="C22" t="str">
         <v>Extrafine Merino 90</v>
       </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
       <c r="E22" t="str">
         <v>Merinould</v>
       </c>
@@ -1953,17 +2224,26 @@
       <c r="Y22" t="str">
         <v>Klassisk dansk storsælger fra Hjertegarn — bredt tilgængeligt i hele Danmark og meget prisvenligt. Superwash-behandlet merino i DK-tykkelse. Stor farvepalette og god kvalitet til hverdagsprojekter.</v>
       </c>
+      <c r="Z22" t="str">
+        <v/>
+      </c>
       <c r="AA22" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="str">
+        <v/>
+      </c>
       <c r="B23" t="str">
         <v>Holst Garn</v>
       </c>
       <c r="C23" t="str">
         <v>Coast</v>
       </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
       <c r="E23" t="str">
         <v>uld/bomuld</v>
       </c>
@@ -1985,26 +2265,68 @@
       <c r="K23">
         <v>26</v>
       </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
       <c r="O23">
         <v>2</v>
       </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
       <c r="R23" t="str">
         <v>maskinvask_30</v>
       </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
       <c r="U23" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V23" t="str">
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <v/>
+      </c>
+      <c r="Z23" t="str">
+        <v/>
       </c>
       <c r="AA23" t="str">
         <v>[{"fiber":"merinould","percentage":55},{"fiber":"bomuld","percentage":45}]</v>
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
       <c r="B24" t="str">
         <v>Holst Garn</v>
       </c>
       <c r="C24" t="str">
         <v>Supersoft</v>
       </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
       <c r="E24" t="str">
         <v>merino/shetland</v>
       </c>
@@ -2026,14 +2348,50 @@
       <c r="K24">
         <v>25</v>
       </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
       <c r="O24">
         <v>2</v>
       </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
       <c r="R24" t="str">
         <v>maskinvask_30</v>
       </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
       <c r="U24" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <v/>
+      </c>
+      <c r="Y24" t="str">
+        <v/>
+      </c>
+      <c r="Z24" t="str">
+        <v/>
       </c>
       <c r="AA24" t="str">
         <v>[{"fiber":"merinould","percentage":50},{"fiber":"shetland_uld","percentage":50}]</v>
@@ -2049,6 +2407,9 @@
       <c r="C25" t="str">
         <v>Alpaca 2</v>
       </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
       <c r="E25" t="str">
         <v>Alpaka-blanding</v>
       </c>
@@ -2112,17 +2473,26 @@
       <c r="Y25" t="str">
         <v>Isagers mest populære garn og en dansk klassiker siden 1977. Blød alpaka-uldblanding med smuk farvepalet og god drapering. Ikke-superwash — bæredygtig og holdbar. Meget brugt i Isager og Helga Isager opskrifter.</v>
       </c>
+      <c r="Z25" t="str">
+        <v/>
+      </c>
       <c r="AA25" t="str">
         <v>[{"fiber":"alpaka","percentage":50},{"fiber":"uld","percentage":50}]</v>
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
       <c r="B26" t="str">
         <v>Isager</v>
       </c>
       <c r="C26" t="str">
         <v>Jensen Yarn</v>
       </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
       <c r="E26" t="str">
         <v>uld</v>
       </c>
@@ -2150,9 +2520,18 @@
       <c r="M26">
         <v>3</v>
       </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
       <c r="O26">
         <v>3</v>
       </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
       <c r="R26" t="str">
         <v>handvask</v>
       </c>
@@ -2165,17 +2544,38 @@
       <c r="U26" t="str">
         <v>i_produktion</v>
       </c>
+      <c r="V26" t="str">
+        <v/>
+      </c>
+      <c r="W26" t="str">
+        <v/>
+      </c>
+      <c r="X26" t="str">
+        <v/>
+      </c>
+      <c r="Y26" t="str">
+        <v/>
+      </c>
+      <c r="Z26" t="str">
+        <v/>
+      </c>
       <c r="AA26" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="str">
+        <v/>
+      </c>
       <c r="B27" t="str">
         <v>Isager</v>
       </c>
       <c r="C27" t="str">
         <v>Silk Mohair</v>
       </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
       <c r="E27" t="str">
         <v>mohair/silke</v>
       </c>
@@ -2203,6 +2603,18 @@
       <c r="M27">
         <v>5</v>
       </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
       <c r="R27" t="str">
         <v>handvask</v>
       </c>
@@ -2217,6 +2629,18 @@
       </c>
       <c r="V27" t="str">
         <v>["RMS"]</v>
+      </c>
+      <c r="W27" t="str">
+        <v/>
+      </c>
+      <c r="X27" t="str">
+        <v/>
+      </c>
+      <c r="Y27" t="str">
+        <v/>
+      </c>
+      <c r="Z27" t="str">
+        <v/>
       </c>
       <c r="AA27" t="str">
         <v>[{"fiber":"kid_mohair","percentage":75},{"fiber":"silke","percentage":25}]</v>
@@ -2265,6 +2689,9 @@
       <c r="N28" t="str">
         <v>Let twistet, kraftigt woolen-spun, to tråde løst snoet</v>
       </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
       <c r="P28" t="str">
         <v>plied</v>
       </c>
@@ -2294,6 +2721,9 @@
       </c>
       <c r="Y28" t="str">
         <v>Den klassiske lopapeysa-tykkelse. Kradser på bar hud, men blødgøres ved vask. Varm og vandafvisende.</v>
+      </c>
+      <c r="Z28" t="str">
+        <v/>
       </c>
       <c r="AA28" t="str">
         <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
@@ -2375,6 +2805,9 @@
       <c r="Y29" t="str">
         <v>Singles-garn med karakteristisk islandsk tovhet. God til sjaler og som holdtråd.</v>
       </c>
+      <c r="Z29" t="str">
+        <v/>
+      </c>
       <c r="AA29" t="str">
         <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
       </c>
@@ -2455,6 +2888,9 @@
       <c r="Y30" t="str">
         <v>Light-version af Álafosslopi — halv vægt, halv tykkelse. Mest populære Lopi-kvalitet til moderne lopapeysa.</v>
       </c>
+      <c r="Z30" t="str">
+        <v/>
+      </c>
       <c r="AA30" t="str">
         <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
       </c>
@@ -2502,6 +2938,9 @@
       <c r="N31" t="str">
         <v>Uspundet plate — skrøbelig tråd, skal håndteres varsomt</v>
       </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
       <c r="P31" t="str">
         <v>unspun</v>
       </c>
@@ -2532,17 +2971,26 @@
       <c r="Y31" t="str">
         <v>Kommer i runde plader à ca. 100 g. Kan holdes 2-3 tråde sammen for tykkere strik.</v>
       </c>
+      <c r="Z31" t="str">
+        <v/>
+      </c>
       <c r="AA31" t="str">
         <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="str">
+        <v/>
+      </c>
       <c r="B32" t="str">
         <v>Knitting for Olive</v>
       </c>
       <c r="C32" t="str">
         <v>Cotton Merino</v>
       </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
       <c r="E32" t="str">
         <v>bomuld/merino</v>
       </c>
@@ -2570,26 +3018,62 @@
       <c r="M32">
         <v>3</v>
       </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
       <c r="R32" t="str">
         <v>handvask</v>
       </c>
+      <c r="S32" t="str">
+        <v/>
+      </c>
+      <c r="T32" t="str">
+        <v/>
+      </c>
       <c r="U32" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V32" t="str">
         <v>["Oeko-Tex Standard 100 (Class 1)","RWS","OCS"]</v>
       </c>
+      <c r="W32" t="str">
+        <v/>
+      </c>
+      <c r="X32" t="str">
+        <v/>
+      </c>
+      <c r="Y32" t="str">
+        <v/>
+      </c>
+      <c r="Z32" t="str">
+        <v/>
+      </c>
       <c r="AA32" t="str">
         <v>[{"fiber":"bomuld","percentage":70},{"fiber":"merinould","percentage":30}]</v>
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="str">
+        <v/>
+      </c>
       <c r="B33" t="str">
         <v>Knitting for Olive</v>
       </c>
       <c r="C33" t="str">
         <v>Heavy Merino</v>
       </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
       <c r="E33" t="str">
         <v>merino</v>
       </c>
@@ -2614,6 +3098,21 @@
       <c r="L33">
         <v>26</v>
       </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
       <c r="R33" t="str">
         <v>handvask</v>
       </c>
@@ -2628,6 +3127,18 @@
       </c>
       <c r="V33" t="str">
         <v>["Oeko-Tex Standard 100"]</v>
+      </c>
+      <c r="W33" t="str">
+        <v/>
+      </c>
+      <c r="X33" t="str">
+        <v/>
+      </c>
+      <c r="Y33" t="str">
+        <v/>
+      </c>
+      <c r="Z33" t="str">
+        <v/>
       </c>
       <c r="AA33" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -2643,6 +3154,9 @@
       <c r="C34" t="str">
         <v>Merino</v>
       </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
       <c r="E34" t="str">
         <v>Merinould</v>
       </c>
@@ -2705,6 +3219,9 @@
       </c>
       <c r="Y34" t="str">
         <v>KFO's suverænt mest solgte garn og det mest profilerede bæredygtige garnmærke i Danmark. Non-superwash, mulesing-fri og OEKO-TEX certificeret. Smukt farvekort og meget brugt i baby- og børnestrik.</v>
+      </c>
+      <c r="Z34" t="str">
+        <v/>
       </c>
       <c r="AA34" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -2720,6 +3237,9 @@
       <c r="C35" t="str">
         <v>Pure Silk</v>
       </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
       <c r="E35" t="str">
         <v>Silke</v>
       </c>
@@ -2741,12 +3261,18 @@
       <c r="K35">
         <v>28</v>
       </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
       <c r="M35">
         <v>3</v>
       </c>
       <c r="N35" t="str">
         <v>Plied bourrette silke, medium twist, lidt rustik med synlige fiberender, mat finish</v>
       </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
       <c r="P35" t="str">
         <v>plied</v>
       </c>
@@ -2756,6 +3282,12 @@
       <c r="R35" t="str">
         <v>handvask</v>
       </c>
+      <c r="S35" t="str">
+        <v/>
+      </c>
+      <c r="T35" t="str">
+        <v/>
+      </c>
       <c r="U35" t="str">
         <v>i_produktion</v>
       </c>
@@ -2771,17 +3303,26 @@
       <c r="Y35" t="str">
         <v>Temperaturregulerende. Bourette silke giver mat finish frem for klassisk silkeglans.</v>
       </c>
+      <c r="Z35" t="str">
+        <v/>
+      </c>
       <c r="AA35" t="str">
         <v>[{"fiber":"silke","percentage":100}]</v>
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="str">
+        <v/>
+      </c>
       <c r="B36" t="str">
         <v>Lana Grossa</v>
       </c>
       <c r="C36" t="str">
         <v>Cool Wool</v>
       </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
       <c r="E36" t="str">
         <v>merino</v>
       </c>
@@ -2806,6 +3347,21 @@
       <c r="L36">
         <v>34</v>
       </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
       <c r="R36" t="str">
         <v>maskinvask_30</v>
       </c>
@@ -2817,6 +3373,21 @@
       </c>
       <c r="U36" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V36" t="str">
+        <v/>
+      </c>
+      <c r="W36" t="str">
+        <v/>
+      </c>
+      <c r="X36" t="str">
+        <v/>
+      </c>
+      <c r="Y36" t="str">
+        <v/>
+      </c>
+      <c r="Z36" t="str">
+        <v/>
       </c>
       <c r="AA36" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -2832,6 +3403,9 @@
       <c r="C37" t="str">
         <v>Maglia</v>
       </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
       <c r="E37" t="str">
         <v>Bomuld-blanding</v>
       </c>
@@ -2862,6 +3436,9 @@
       <c r="N37" t="str">
         <v>Bomuldsblanding med let polyester-stretch</v>
       </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
       <c r="P37" t="str">
         <v>plied</v>
       </c>
@@ -2874,6 +3451,9 @@
       <c r="S37" t="str">
         <v>Italien</v>
       </c>
+      <c r="T37" t="str">
+        <v/>
+      </c>
       <c r="U37" t="str">
         <v>i_produktion</v>
       </c>
@@ -2889,11 +3469,17 @@
       <c r="Y37" t="str">
         <v>Bomuldsbaseret Lana Grossa-kvalitet med lille polyester-andel for form og styrke.</v>
       </c>
+      <c r="Z37" t="str">
+        <v/>
+      </c>
       <c r="AA37" t="str">
         <v>[{"fiber":"bomuld","percentage":92},{"fiber":"polyester","percentage":8}]</v>
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="str">
+        <v/>
+      </c>
       <c r="B38" t="str">
         <v>Lang Yarns</v>
       </c>
@@ -2927,29 +3513,65 @@
       <c r="L38">
         <v>41</v>
       </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
       <c r="Q38" t="str">
         <v>superwash</v>
       </c>
       <c r="R38" t="str">
         <v>maskinvask_40</v>
       </c>
+      <c r="S38" t="str">
+        <v/>
+      </c>
       <c r="T38" t="str">
         <v>Chile (Patagonia)</v>
       </c>
       <c r="U38" t="str">
         <v>i_produktion</v>
       </c>
+      <c r="V38" t="str">
+        <v/>
+      </c>
+      <c r="W38" t="str">
+        <v/>
+      </c>
+      <c r="X38" t="str">
+        <v/>
+      </c>
+      <c r="Y38" t="str">
+        <v/>
+      </c>
+      <c r="Z38" t="str">
+        <v/>
+      </c>
       <c r="AA38" t="str">
         <v>[{"fiber":"uld","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="str">
+        <v/>
+      </c>
       <c r="B39" t="str">
         <v>Lang Yarns</v>
       </c>
       <c r="C39" t="str">
         <v>Mille Colori Baby</v>
       </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
       <c r="E39" t="str">
         <v>merino</v>
       </c>
@@ -2974,29 +3596,65 @@
       <c r="L39">
         <v>36</v>
       </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
       <c r="Q39" t="str">
         <v>superwash</v>
       </c>
       <c r="R39" t="str">
         <v>maskinvask_40</v>
       </c>
+      <c r="S39" t="str">
+        <v/>
+      </c>
       <c r="T39" t="str">
         <v>Australien</v>
       </c>
       <c r="U39" t="str">
         <v>i_produktion</v>
       </c>
+      <c r="V39" t="str">
+        <v/>
+      </c>
+      <c r="W39" t="str">
+        <v/>
+      </c>
+      <c r="X39" t="str">
+        <v/>
+      </c>
+      <c r="Y39" t="str">
+        <v/>
+      </c>
+      <c r="Z39" t="str">
+        <v/>
+      </c>
       <c r="AA39" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="str">
+        <v/>
+      </c>
       <c r="B40" t="str">
         <v>Manos del Uruguay</v>
       </c>
       <c r="C40" t="str">
         <v>Alegria</v>
       </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
       <c r="E40" t="str">
         <v>merino/nylon</v>
       </c>
@@ -3018,26 +3676,68 @@
       <c r="K40">
         <v>29</v>
       </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
       <c r="Q40" t="str">
         <v>superwash</v>
       </c>
       <c r="R40" t="str">
         <v>maskinvask_40</v>
       </c>
+      <c r="S40" t="str">
+        <v/>
+      </c>
+      <c r="T40" t="str">
+        <v/>
+      </c>
       <c r="U40" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V40" t="str">
+        <v/>
+      </c>
+      <c r="W40" t="str">
+        <v/>
+      </c>
+      <c r="X40" t="str">
+        <v/>
+      </c>
+      <c r="Y40" t="str">
+        <v/>
+      </c>
+      <c r="Z40" t="str">
+        <v/>
       </c>
       <c r="AA40" t="str">
         <v>[{"fiber":"merinould","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="str">
+        <v/>
+      </c>
       <c r="B41" t="str">
         <v>Manos del Uruguay</v>
       </c>
       <c r="C41" t="str">
         <v>Serena</v>
       </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
       <c r="E41" t="str">
         <v>alpaka/bomuld</v>
       </c>
@@ -3059,14 +3759,50 @@
       <c r="K41">
         <v>24</v>
       </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
       <c r="R41" t="str">
         <v>handvask</v>
       </c>
+      <c r="S41" t="str">
+        <v/>
+      </c>
       <c r="T41" t="str">
         <v>Peru (alpaka), bomuld: ukendt</v>
       </c>
       <c r="U41" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V41" t="str">
+        <v/>
+      </c>
+      <c r="W41" t="str">
+        <v/>
+      </c>
+      <c r="X41" t="str">
+        <v/>
+      </c>
+      <c r="Y41" t="str">
+        <v/>
+      </c>
+      <c r="Z41" t="str">
+        <v/>
       </c>
       <c r="AA41" t="str">
         <v>[{"fiber":"baby_alpaka","percentage":60},{"fiber":"bomuld","percentage":40}]</v>
@@ -3082,6 +3818,9 @@
       <c r="C42" t="str">
         <v>Easy Care Big</v>
       </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
       <c r="E42" t="str">
         <v>Merinould</v>
       </c>
@@ -3124,6 +3863,9 @@
       <c r="R42" t="str">
         <v>maskinvask_40</v>
       </c>
+      <c r="S42" t="str">
+        <v/>
+      </c>
       <c r="T42" t="str">
         <v>Sydamerika</v>
       </c>
@@ -3141,6 +3883,9 @@
       </c>
       <c r="Y42" t="str">
         <v>Superwash-behandlet — kan maskinvaskes og tumbles. Bloomer mindre end ubehandlet uld og kan strække over tid.</v>
+      </c>
+      <c r="Z42" t="str">
+        <v/>
       </c>
       <c r="AA42" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -3156,6 +3901,9 @@
       <c r="C43" t="str">
         <v>Nordia</v>
       </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
       <c r="E43" t="str">
         <v>Uld-blanding</v>
       </c>
@@ -3177,9 +3925,18 @@
       <c r="K43">
         <v>19</v>
       </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
       <c r="M43">
         <v>4</v>
       </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
       <c r="P43" t="str">
         <v>plied</v>
       </c>
@@ -3189,6 +3946,12 @@
       <c r="R43" t="str">
         <v>maskinvask_30</v>
       </c>
+      <c r="S43" t="str">
+        <v/>
+      </c>
+      <c r="T43" t="str">
+        <v/>
+      </c>
       <c r="U43" t="str">
         <v>i_produktion</v>
       </c>
@@ -3200,6 +3963,12 @@
       </c>
       <c r="X43" t="str">
         <v>[]</v>
+      </c>
+      <c r="Y43" t="str">
+        <v/>
+      </c>
+      <c r="Z43" t="str">
+        <v/>
       </c>
       <c r="AA43" t="str">
         <v>[{"fiber":"uld","percentage":51},{"fiber":"acryl","percentage":34},{"fiber":"nylon_polyamid","percentage":15}]</v>
@@ -3215,6 +3984,9 @@
       <c r="C44" t="str">
         <v>Trio</v>
       </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
       <c r="E44" t="str">
         <v>Uld</v>
       </c>
@@ -3277,6 +4049,9 @@
       </c>
       <c r="Y44" t="str">
         <v>Ubehandlet færøsk uld. Filter hvis behandlet forkert.</v>
+      </c>
+      <c r="Z44" t="str">
+        <v/>
       </c>
       <c r="AA44" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -3325,12 +4100,24 @@
       <c r="N45" t="str">
         <v>Brushed mohair-blanding med langt halo</v>
       </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
       <c r="Q45" t="str">
         <v>standard</v>
       </c>
       <c r="R45" t="str">
         <v>handvask</v>
       </c>
+      <c r="S45" t="str">
+        <v/>
+      </c>
+      <c r="T45" t="str">
+        <v/>
+      </c>
       <c r="U45" t="str">
         <v>i_produktion</v>
       </c>
@@ -3342,9 +4129,15 @@
       </c>
       <c r="X45" t="str">
         <v>[]</v>
+      </c>
+      <c r="Y45" t="str">
+        <v/>
       </c>
       <c r="Z45" t="str">
         <v>/garn-eksempler/permin-bella.jpg</v>
+      </c>
+      <c r="AA45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -3390,6 +4183,9 @@
       <c r="N46" t="str">
         <v>Brushed mohair-blanding med langt halo</v>
       </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
       <c r="P46" t="str">
         <v>brushed_singles</v>
       </c>
@@ -3401,6 +4197,9 @@
       </c>
       <c r="S46" t="str">
         <v>Italien</v>
+      </c>
+      <c r="T46" t="str">
+        <v/>
       </c>
       <c r="U46" t="str">
         <v>i_produktion</v>
@@ -3434,6 +4233,9 @@
       <c r="C47" t="str">
         <v>Hannah</v>
       </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
       <c r="E47" t="str">
         <v>Merinould-blanding</v>
       </c>
@@ -3464,6 +4266,9 @@
       <c r="N47" t="str">
         <v>Brushed, silkekerne med uld/cashmere spundet udenom — let halo</v>
       </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
       <c r="P47" t="str">
         <v>brushed_singles</v>
       </c>
@@ -3476,6 +4281,9 @@
       <c r="S47" t="str">
         <v>Italien</v>
       </c>
+      <c r="T47" t="str">
+        <v/>
+      </c>
       <c r="U47" t="str">
         <v>i_produktion</v>
       </c>
@@ -3499,12 +4307,18 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="str">
+        <v/>
+      </c>
       <c r="B48" t="str">
         <v>Rauma Garn</v>
       </c>
       <c r="C48" t="str">
         <v>Finull</v>
       </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
       <c r="E48" t="str">
         <v>uld</v>
       </c>
@@ -3526,9 +4340,24 @@
       <c r="K48">
         <v>25</v>
       </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
       <c r="O48">
         <v>2</v>
       </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
       <c r="R48" t="str">
         <v>maskinvask_30</v>
       </c>
@@ -3540,6 +4369,21 @@
       </c>
       <c r="U48" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V48" t="str">
+        <v/>
+      </c>
+      <c r="W48" t="str">
+        <v/>
+      </c>
+      <c r="X48" t="str">
+        <v/>
+      </c>
+      <c r="Y48" t="str">
+        <v/>
+      </c>
+      <c r="Z48" t="str">
+        <v/>
       </c>
       <c r="AA48" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -3555,6 +4399,9 @@
       <c r="C49" t="str">
         <v>Vams</v>
       </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
       <c r="E49" t="str">
         <v>Uld</v>
       </c>
@@ -3576,12 +4423,18 @@
       <c r="K49">
         <v>15</v>
       </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
       <c r="M49">
         <v>5.5</v>
       </c>
       <c r="N49" t="str">
         <v>Kardegarn (woolen-spun), single, blød twist, luftig og let filtbar</v>
       </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
       <c r="P49" t="str">
         <v>singles</v>
       </c>
@@ -3611,6 +4464,9 @@
       </c>
       <c r="Y49" t="str">
         <v>Kardegarn = kartet ulden er på kryds og tværs, hvilket giver et luftigt, blødt rustikt garn der bloomer kraftigt ved vask.</v>
+      </c>
+      <c r="Z49" t="str">
+        <v/>
       </c>
       <c r="AA49" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -3626,6 +4482,9 @@
       <c r="C50" t="str">
         <v>Creative Make It Blümchen</v>
       </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
       <c r="E50" t="str">
         <v>Lyocell</v>
       </c>
@@ -3638,9 +4497,30 @@
       <c r="H50">
         <v>1500</v>
       </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
       <c r="N50" t="str">
         <v>Tråd med applikerede tekstil-blomster langs tråden (effektgarn)</v>
       </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
       <c r="Q50" t="str">
         <v>standard</v>
       </c>
@@ -3650,6 +4530,9 @@
       <c r="S50" t="str">
         <v>Tyskland</v>
       </c>
+      <c r="T50" t="str">
+        <v/>
+      </c>
       <c r="U50" t="str">
         <v>i_produktion</v>
       </c>
@@ -3664,6 +4547,12 @@
       </c>
       <c r="Y50" t="str">
         <v>USIKKER — bekræft producent og specs på banderolen.</v>
+      </c>
+      <c r="Z50" t="str">
+        <v/>
+      </c>
+      <c r="AA50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -3676,6 +4565,9 @@
       <c r="C51" t="str">
         <v>Paillettes Classic Collection</v>
       </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
       <c r="E51" t="str">
         <v>Polyester</v>
       </c>
@@ -3697,9 +4589,21 @@
       <c r="K51">
         <v>28</v>
       </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
       <c r="N51" t="str">
         <v>Tråd med indspundne/påsyede pailletter — effektgarn</v>
       </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
       <c r="Q51" t="str">
         <v>standard</v>
       </c>
@@ -3709,6 +4613,9 @@
       <c r="S51" t="str">
         <v>Portugal</v>
       </c>
+      <c r="T51" t="str">
+        <v/>
+      </c>
       <c r="U51" t="str">
         <v>i_produktion</v>
       </c>
@@ -3723,6 +4630,12 @@
       </c>
       <c r="Y51" t="str">
         <v>USIKKER — Rosários 4 har flere pailletgarn-serier. Bør verificeres på banderolen.</v>
+      </c>
+      <c r="Z51" t="str">
+        <v/>
+      </c>
+      <c r="AA51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -3735,6 +4648,9 @@
       <c r="C52" t="str">
         <v>Kitten Mohair</v>
       </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
       <c r="E52" t="str">
         <v>Mohair-blanding</v>
       </c>
@@ -3765,6 +4681,9 @@
       <c r="N52" t="str">
         <v>Plied DK-mohair-blend, let halo, blødt</v>
       </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
       <c r="P52" t="str">
         <v>plied</v>
       </c>
@@ -3777,6 +4696,9 @@
       <c r="S52" t="str">
         <v>Norge</v>
       </c>
+      <c r="T52" t="str">
+        <v/>
+      </c>
       <c r="U52" t="str">
         <v>i_produktion</v>
       </c>
@@ -3792,17 +4714,26 @@
       <c r="Y52" t="str">
         <v>80er/90er-stilstrik. Akrylindholdet gør den mere robust og mindre elegant — ikke et luksusgarn til lette overdele.</v>
       </c>
+      <c r="Z52" t="str">
+        <v/>
+      </c>
       <c r="AA52" t="str">
         <v>[{"fiber":"courtelle","percentage":50},{"fiber":"mohair","percentage":30},{"fiber":"uld","percentage":20}]</v>
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
       <c r="B53" t="str">
         <v>Sandnes Garn</v>
       </c>
       <c r="C53" t="str">
         <v>Kos</v>
       </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
       <c r="E53" t="str">
         <v>alpaka/uld/nylon</v>
       </c>
@@ -3824,26 +4755,68 @@
       <c r="K53">
         <v>17</v>
       </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
       <c r="R53" t="str">
         <v>maskinvask_30</v>
       </c>
+      <c r="S53" t="str">
+        <v/>
+      </c>
       <c r="T53" t="str">
         <v>Uruguay (uld), Peru (alpaka)</v>
       </c>
       <c r="U53" t="str">
         <v>i_produktion</v>
       </c>
+      <c r="V53" t="str">
+        <v/>
+      </c>
+      <c r="W53" t="str">
+        <v/>
+      </c>
+      <c r="X53" t="str">
+        <v/>
+      </c>
+      <c r="Y53" t="str">
+        <v/>
+      </c>
+      <c r="Z53" t="str">
+        <v/>
+      </c>
       <c r="AA53" t="str">
         <v>[{"fiber":"alpaka","percentage":62},{"fiber":"nylon_polyamid","percentage":29},{"fiber":"uld","percentage":9}]</v>
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
       <c r="B54" t="str">
         <v>Sandnes Garn</v>
       </c>
       <c r="C54" t="str">
         <v>Line</v>
       </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
       <c r="E54" t="str">
         <v>bomuld/viskose/lin</v>
       </c>
@@ -3865,14 +4838,50 @@
       <c r="K54">
         <v>20</v>
       </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
       <c r="R54" t="str">
         <v>maskinvask_30</v>
       </c>
+      <c r="S54" t="str">
+        <v/>
+      </c>
       <c r="T54" t="str">
         <v>Indien</v>
       </c>
       <c r="U54" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V54" t="str">
+        <v/>
+      </c>
+      <c r="W54" t="str">
+        <v/>
+      </c>
+      <c r="X54" t="str">
+        <v/>
+      </c>
+      <c r="Y54" t="str">
+        <v/>
+      </c>
+      <c r="Z54" t="str">
+        <v/>
       </c>
       <c r="AA54" t="str">
         <v>[{"fiber":"bomuld","percentage":53},{"fiber":"viskose","percentage":33},{"fiber":"lin","percentage":14}]</v>
@@ -3888,6 +4897,9 @@
       <c r="C55" t="str">
         <v>Peer Gynt</v>
       </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
       <c r="E55" t="str">
         <v>Uld</v>
       </c>
@@ -3933,6 +4945,9 @@
       <c r="S55" t="str">
         <v>Norge</v>
       </c>
+      <c r="T55" t="str">
+        <v/>
+      </c>
       <c r="U55" t="str">
         <v>i_produktion</v>
       </c>
@@ -3947,6 +4962,9 @@
       </c>
       <c r="Y55" t="str">
         <v>Nordisk klassiker. Bredt farveudvalg. Meget brugt i PetiteKnit-opskrifter.</v>
+      </c>
+      <c r="Z55" t="str">
+        <v/>
       </c>
       <c r="AA55" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -3962,6 +4980,9 @@
       <c r="C56" t="str">
         <v>Poppy</v>
       </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
       <c r="E56" t="str">
         <v>Bomuld</v>
       </c>
@@ -3992,6 +5013,9 @@
       <c r="N56" t="str">
         <v>Flertrådet, blød kæmmet bomuld</v>
       </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
       <c r="P56" t="str">
         <v>plied</v>
       </c>
@@ -4021,6 +5045,9 @@
       </c>
       <c r="Y56" t="str">
         <v>Blød bomuld uden glans, hverdagsprojekter i DK.</v>
+      </c>
+      <c r="Z56" t="str">
+        <v/>
       </c>
       <c r="AA56" t="str">
         <v>[{"fiber":"bomuld","percentage":100}]</v>
@@ -4036,6 +5063,9 @@
       <c r="C57" t="str">
         <v>Sunday</v>
       </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
       <c r="E57" t="str">
         <v>Merinould</v>
       </c>
@@ -4098,6 +5128,9 @@
       </c>
       <c r="Y57" t="str">
         <v>Et af Sandnes' mest populære garner — ekstremt smukt farvekort med jordfarver og pasteller valgt i samarbejde med PetiteKnit. Non-superwash merino, meget blød. Bruges i mange af de mest downloadede opskrifter i Danmark.</v>
+      </c>
+      <c r="Z57" t="str">
+        <v/>
       </c>
       <c r="AA57" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -4113,6 +5146,9 @@
       <c r="C58" t="str">
         <v>Tynn Silk Mohair</v>
       </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
       <c r="E58" t="str">
         <v>Kid mohair-blanding</v>
       </c>
@@ -4143,6 +5179,9 @@
       <c r="N58" t="str">
         <v>Brushed single, angora-ged mohair med silkekerne, medium halo</v>
       </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
       <c r="P58" t="str">
         <v>brushed_singles</v>
       </c>
@@ -4172,6 +5211,9 @@
       </c>
       <c r="Y58" t="str">
         <v>Meget populær silk mohair fra Sandnes — høj kvalitet, tåler maskinvask ved 30 grader (uldprogram), og bruges i mange gennemtestede opskrifter fra kendte strikkedesignere. Luksuriøs og luftig holdtråd.</v>
+      </c>
+      <c r="Z58" t="str">
+        <v/>
       </c>
       <c r="AA58" t="str">
         <v>[{"fiber":"mohair","percentage":57},{"fiber":"silke","percentage":28},{"fiber":"uld","percentage":15}]</v>
@@ -4235,6 +5277,9 @@
       <c r="S59" t="str">
         <v>Tyskland</v>
       </c>
+      <c r="T59" t="str">
+        <v/>
+      </c>
       <c r="U59" t="str">
         <v>i_produktion</v>
       </c>
@@ -4250,17 +5295,26 @@
       <c r="Y59" t="str">
         <v>Tysk sokkegarn-klassiker. Enormt farveudvalg inkl. selvstribende.</v>
       </c>
+      <c r="Z59" t="str">
+        <v/>
+      </c>
       <c r="AA59" t="str">
         <v>[{"fiber":"uld","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="str">
+        <v/>
+      </c>
       <c r="B60" t="str">
         <v>Schoppel Wolle</v>
       </c>
       <c r="C60" t="str">
         <v>Edition 3</v>
       </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
       <c r="E60" t="str">
         <v>merino</v>
       </c>
@@ -4279,26 +5333,71 @@
       <c r="J60">
         <v>3.5</v>
       </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
       <c r="Q60" t="str">
         <v>superwash</v>
       </c>
       <c r="R60" t="str">
         <v>maskinvask_40</v>
       </c>
+      <c r="S60" t="str">
+        <v/>
+      </c>
+      <c r="T60" t="str">
+        <v/>
+      </c>
       <c r="U60" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V60" t="str">
+        <v/>
+      </c>
+      <c r="W60" t="str">
+        <v/>
+      </c>
+      <c r="X60" t="str">
+        <v/>
+      </c>
+      <c r="Y60" t="str">
+        <v/>
+      </c>
+      <c r="Z60" t="str">
+        <v/>
       </c>
       <c r="AA60" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="str">
+        <v/>
+      </c>
       <c r="B61" t="str">
         <v>Schoppel Wolle</v>
       </c>
       <c r="C61" t="str">
         <v>Zauberball Stärke 6</v>
       </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
       <c r="E61" t="str">
         <v>uld/nylon</v>
       </c>
@@ -4317,14 +5416,53 @@
       <c r="J61">
         <v>4</v>
       </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
       <c r="Q61" t="str">
         <v>superwash</v>
       </c>
       <c r="R61" t="str">
         <v>maskinvask_40</v>
       </c>
+      <c r="S61" t="str">
+        <v/>
+      </c>
+      <c r="T61" t="str">
+        <v/>
+      </c>
       <c r="U61" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V61" t="str">
+        <v/>
+      </c>
+      <c r="W61" t="str">
+        <v/>
+      </c>
+      <c r="X61" t="str">
+        <v/>
+      </c>
+      <c r="Y61" t="str">
+        <v/>
+      </c>
+      <c r="Z61" t="str">
+        <v/>
       </c>
       <c r="AA61" t="str">
         <v>[{"fiber":"uld","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
@@ -4340,6 +5478,9 @@
       <c r="C62" t="str">
         <v>Mohair Blend</v>
       </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
       <c r="E62" t="str">
         <v>Kid mohair</v>
       </c>
@@ -4370,6 +5511,9 @@
       <c r="N62" t="str">
         <v>Brushed kid mohair single med syntetisk kerne, let halo</v>
       </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
       <c r="P62" t="str">
         <v>brushed_singles</v>
       </c>
@@ -4379,6 +5523,12 @@
       <c r="R62" t="str">
         <v>handvask</v>
       </c>
+      <c r="S62" t="str">
+        <v/>
+      </c>
+      <c r="T62" t="str">
+        <v/>
+      </c>
       <c r="U62" t="str">
         <v>i_produktion</v>
       </c>
@@ -4394,20 +5544,65 @@
       <c r="Y62" t="str">
         <v>Budget-alternativ til Tilia/Hannah. Mange bruger den til at teste mønstre før de investerer i dyrere mohair.</v>
       </c>
+      <c r="Z62" t="str">
+        <v/>
+      </c>
       <c r="AA62" t="str">
         <v>[{"fiber":"kid_mohair","percentage":80},{"fiber":"nylon_polyamid","percentage":20}]</v>
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="str">
+        <v/>
+      </c>
       <c r="B63" t="str">
         <v>Tynd Uld / dansk spinderi</v>
       </c>
       <c r="C63" t="str">
         <v>Spelsau</v>
       </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
       <c r="E63" t="str">
         <v>uld</v>
       </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
       <c r="R63" t="str">
         <v>ikke_angivet</v>
       </c>
@@ -4419,6 +5614,21 @@
       </c>
       <c r="U63" t="str">
         <v>i_produktion</v>
+      </c>
+      <c r="V63" t="str">
+        <v/>
+      </c>
+      <c r="W63" t="str">
+        <v/>
+      </c>
+      <c r="X63" t="str">
+        <v/>
+      </c>
+      <c r="Y63" t="str">
+        <v/>
+      </c>
+      <c r="Z63" t="str">
+        <v/>
       </c>
       <c r="AA63" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -4434,6 +5644,9 @@
       <c r="C64" t="str">
         <v>Korsika</v>
       </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
       <c r="E64" t="str">
         <v>Plantefiber-blanding</v>
       </c>
@@ -4464,6 +5677,9 @@
       <c r="N64" t="str">
         <v>Plied plantefiber — mindre elasticitet end uld, falder tungt og pænt</v>
       </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
       <c r="P64" t="str">
         <v>plied</v>
       </c>
@@ -4476,6 +5692,9 @@
       <c r="S64" t="str">
         <v>Tyskland</v>
       </c>
+      <c r="T64" t="str">
+        <v/>
+      </c>
       <c r="U64" t="str">
         <v>i_produktion</v>
       </c>
@@ -4491,17 +5710,26 @@
       <c r="Y64" t="str">
         <v>Aldi-kampagnegarn. Kølig drape, ingen varme.</v>
       </c>
+      <c r="Z64" t="str">
+        <v/>
+      </c>
       <c r="AA64" t="str">
         <v>[{"fiber":"bomuld","percentage":73},{"fiber":"lin","percentage":27}]</v>
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="str">
+        <v/>
+      </c>
       <c r="B65" t="str">
         <v>Drops</v>
       </c>
       <c r="C65" t="str">
         <v>Baby Merino</v>
       </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
       <c r="E65" t="str">
         <v>merinould</v>
       </c>
@@ -4523,6 +5751,12 @@
       <c r="K65">
         <v>24</v>
       </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
       <c r="N65" t="str">
         <v>3-trådet plied, superwash extrafine merino, medium twist</v>
       </c>
@@ -4566,13 +5800,93 @@
         <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v/>
+      </c>
+      <c r="B66" t="str">
+        <v>Filcolana</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Alva</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v>alpaka</v>
+      </c>
+      <c r="F66" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G66">
+        <v>25</v>
+      </c>
+      <c r="H66">
+        <v>700</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v>tyndt 2-trådet alpakagarn</v>
+      </c>
+      <c r="O66">
+        <v>2</v>
+      </c>
+      <c r="P66" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S66" t="str">
+        <v>Peru</v>
+      </c>
+      <c r="T66" t="str">
+        <v>Peru</v>
+      </c>
+      <c r="U66" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V66" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W66" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X66" t="str">
+        <v>["følgegarn","sjaler","lette bluser"]</v>
+      </c>
+      <c r="Y66" t="str">
+        <v>Alva er et tyndt 2-trådet garn spundet af fibre fra peruvianske alpakaer. Alva er blød, varm og glansfuld og velegnet til mange slags projekter. Det tynde garn er perfekt til at strikke sammen med vores andre kvaliteter. Desuden er Alva et herligt alternativt følgegarn i stedet for et tyndt mohairgarn.</v>
+      </c>
+      <c r="Z66" t="str">
+        <v>/garn-eksempler/filcolana-alva.jpg</v>
+      </c>
+      <c r="AA66" t="str">
+        <v>[{"fiber":"alpaka","percentage":100}]</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC64"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA66"/>
   </ignoredErrors>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/content/yarns.xlsx
+++ b/content/yarns.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Forklaring" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!A1:AC64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AA$86</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA66"/>
+  <dimension ref="A1:AA89"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -646,7 +646,7 @@
         <v>Luxor er et merceriseret bomuldsgarn i fingering-tykkelse (100% bomuld). Merceriseringen giver garnet en smuk glans, stærke og klare farver samt en meget tydelig maskedefinition. hBomulden stammer fra USA, mens garnet spindes og farves i Serbien. Farvestofferne er uden animalske ingredienser, så garnet kan betegnes som vegansk. Luxor kan maskinvaskes (op til 40 °C), men glansen kan aftage en smule over tid.</v>
       </c>
       <c r="Z3" t="str">
-        <v/>
+        <v>/garn-eksempler/bc-garn-luxor.jpg</v>
       </c>
       <c r="AA3" t="str">
         <v>[{"fiber":"merceriseret_bomuld","percentage":100}]</v>
@@ -740,58 +740,58 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v>Drops</v>
+        <v>CaMaRose</v>
       </c>
       <c r="C5" t="str">
-        <v>Air</v>
+        <v>Tynd Lamauld</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>alpaka/uld/nylon</v>
+        <v>lama/uld</v>
       </c>
       <c r="F5" t="str">
-        <v>aran</v>
+        <v>lace</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="L5">
-        <v>22</v>
-      </c>
-      <c r="M5" t="str">
-        <v/>
+        <v>40</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
       <c r="N5" t="str">
-        <v>Chainette/blown — fibre blæst ind i en tynd nylon-tube i stedet for klassisk spinding</v>
+        <v/>
       </c>
       <c r="O5" t="str">
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>chainette</v>
+        <v>singles</v>
       </c>
       <c r="Q5" t="str">
-        <v>standard</v>
+        <v/>
       </c>
       <c r="R5" t="str">
         <v>handvask</v>
       </c>
       <c r="S5" t="str">
-        <v>Peru/EU</v>
+        <v>Peru</v>
       </c>
       <c r="T5" t="str">
         <v>Peru</v>
@@ -800,81 +800,81 @@
         <v>i_produktion</v>
       </c>
       <c r="V5" t="str">
-        <v>["Oeko-Tex Standard 100 (Class I)"]</v>
+        <v>[]</v>
       </c>
       <c r="W5" t="str">
-        <v>[]</v>
+        <v>["forår", "efterår", "vinter"]</v>
       </c>
       <c r="X5" t="str">
-        <v>["lette sweatre","cardigans","oversize strik","babytæpper","tilbehør"]</v>
+        <v>["bluser", "cardigans", "sjaler", "babystrik"]</v>
       </c>
       <c r="Y5" t="str">
-        <v>Lofty "blown" garn hvor baby-alpaka og merinould blæses ind i en tynd nylon-tube i stedet for at blive spundet. Færdige plagg er 30-35% lettere end tilsvarende tykkelse i klassisk spundet garn. Meget populær til behagelige oversize sweatre.</v>
+        <v>Tynd, single-spun udgave af Lamauld i 50% lama og 50% peruviansk højlandsuld. Lanolin-frit og let, med rustik karakter der folder sig ud efter første vask. Velegnet til finstrik og som hold-ind-garn.</v>
       </c>
       <c r="Z5" t="str">
-        <v/>
+        <v>/garn-eksempler/camarose-tynd-lamauld.jpg</v>
       </c>
       <c r="AA5" t="str">
-        <v>[{"fiber":"baby_alpaka","percentage":65},{"fiber":"nylon_polyamid","percentage":28},{"fiber":"merinould","percentage":7}]</v>
+        <v>[{"fiber": "alpaka", "percentage": 50}, {"fiber": "uld", "percentage": 50}]</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>185bc557-cd0b-4256-8ac2-4b982b037a0d</v>
+        <v/>
       </c>
       <c r="B6" t="str">
-        <v>Drops</v>
+        <v>CaMaRose</v>
       </c>
       <c r="C6" t="str">
-        <v>Alaska</v>
+        <v>Økologisk Sommeruld</v>
       </c>
       <c r="D6" t="str">
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Uld</v>
+        <v>merinould/bomuld</v>
       </c>
       <c r="F6" t="str">
-        <v>aran</v>
+        <v>fingering</v>
       </c>
       <c r="G6">
         <v>50</v>
       </c>
       <c r="H6">
-        <v>140</v>
+        <v>460</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>17</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N6" t="str">
-        <v>3-trådet plied, klassisk spundet, ubehandlet ren ny uld, medium twist</v>
-      </c>
-      <c r="O6">
-        <v>3</v>
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
       </c>
       <c r="P6" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q6" t="str">
-        <v>standard</v>
+        <v/>
       </c>
       <c r="R6" t="str">
         <v>handvask</v>
       </c>
       <c r="S6" t="str">
-        <v>Norge</v>
+        <v/>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -883,164 +883,164 @@
         <v>i_produktion</v>
       </c>
       <c r="V6" t="str">
-        <v>["Oeko-Tex Standard 100 (Class I)"]</v>
+        <v>["GOTS"]</v>
       </c>
       <c r="W6" t="str">
-        <v>[]</v>
+        <v>["forår", "sommer"]</v>
       </c>
       <c r="X6" t="str">
-        <v>["tykke vintersweatre","jakker","tæpper","toveprojekter","læringsprojekter"]</v>
+        <v>["sommerbluser", "cardigans", "babystrik"]</v>
       </c>
       <c r="Y6" t="str">
-        <v>Billigt budget-garn. Kan filtes.</v>
+        <v>GOTS-certificeret sommergarn i 70% økologisk merinould og 30% økologisk bomuld. Mat overflade, åndbart og blødt — perfekt til sommertoppe og babystrik.</v>
       </c>
       <c r="Z6" t="str">
-        <v/>
+        <v>/garn-eksempler/camarose-oekologisk-sommeruld.jpg</v>
       </c>
       <c r="AA6" t="str">
-        <v>[{"fiber":"uld","percentage":100}]</v>
+        <v>[{"fiber": "merinould", "percentage": 70}, {"fiber": "bomuld", "percentage": 30}]</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>3db069d1-706a-440e-8e9e-327d4eeb8336</v>
+        <v/>
       </c>
       <c r="B7" t="str">
-        <v>Drops</v>
+        <v>CaMaRose</v>
       </c>
       <c r="C7" t="str">
-        <v>Alpaca</v>
+        <v>Løvetand</v>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Alpaka</v>
+        <v>hør</v>
       </c>
       <c r="F7" t="str">
-        <v>sport</v>
+        <v>dk</v>
       </c>
       <c r="G7">
         <v>50</v>
       </c>
       <c r="H7">
-        <v>334</v>
+        <v>280</v>
       </c>
       <c r="I7">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M7">
         <v>3</v>
       </c>
       <c r="N7" t="str">
-        <v>5-trådet plied, 100% superfin ubehandlet alpaka, blød og let med naturlig glans</v>
-      </c>
-      <c r="O7">
-        <v>5</v>
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
       </c>
       <c r="P7" t="str">
-        <v>plied</v>
+        <v>chainette</v>
       </c>
       <c r="Q7" t="str">
-        <v>standard</v>
+        <v/>
       </c>
       <c r="R7" t="str">
         <v>handvask</v>
       </c>
       <c r="S7" t="str">
-        <v>Peru</v>
+        <v>Italien</v>
       </c>
       <c r="T7" t="str">
-        <v>Peru</v>
+        <v>Belgien</v>
       </c>
       <c r="U7" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V7" t="str">
-        <v>[]</v>
+        <v>["GOTS"]</v>
       </c>
       <c r="W7" t="str">
-        <v>[]</v>
+        <v>["forår", "sommer"]</v>
       </c>
       <c r="X7" t="str">
-        <v>["sjaler","lette sweatre","cardigans","babytøj","tilbehør"]</v>
+        <v>["sommerbluser", "toppe", "tørklæder"]</v>
       </c>
       <c r="Y7" t="str">
-        <v>Klassisk, let alpakagarn med fantastisk drapering og farvemætning. Populært til sjaler og lette projekter. Kradser ikke og er blødt mod huden. Et af DROPS' ældste og mest elskede kvaliteter.</v>
+        <v>DK-tykt chainette-spundet garn i 100% økologisk hør. Belgiske hørfibre, spundet i Italien for CaMaRose. Tube-konstruktionen gør hør behageligere at strikke med — bliver blødere for hver vask.</v>
       </c>
       <c r="Z7" t="str">
-        <v/>
+        <v>/garn-eksempler/camarose-loevetand.jpg</v>
       </c>
       <c r="AA7" t="str">
-        <v>[{"fiber":"alpaka","percentage":100}]</v>
+        <v>[{"fiber": "lin", "percentage": 100}]</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>de1a9830-abbd-406b-9bc9-8461920f4618</v>
+        <v/>
       </c>
       <c r="B8" t="str">
-        <v>Drops</v>
+        <v>CaMaRose</v>
       </c>
       <c r="C8" t="str">
-        <v>Brushed Alpaca Silk</v>
+        <v>Lama Tweed</v>
       </c>
       <c r="D8" t="str">
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Alpaka-blanding</v>
+        <v>lama/uld/viskose</v>
       </c>
       <c r="F8" t="str">
-        <v>aran</v>
+        <v>worsted</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H8">
-        <v>560</v>
+        <v>200</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J8">
         <v>5</v>
       </c>
       <c r="K8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N8" t="str">
-        <v>Brushed single, børstet superfin alpaka med silkekerne, kraftig halo</v>
+        <v>tweed med små farvenuller</v>
       </c>
       <c r="O8" t="str">
         <v/>
       </c>
       <c r="P8" t="str">
-        <v>brushed_singles</v>
+        <v>singles</v>
       </c>
       <c r="Q8" t="str">
-        <v>brushed</v>
+        <v/>
       </c>
       <c r="R8" t="str">
         <v>handvask</v>
       </c>
       <c r="S8" t="str">
-        <v>Peru</v>
+        <v/>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -1052,19 +1052,19 @@
         <v>[]</v>
       </c>
       <c r="W8" t="str">
-        <v>[]</v>
+        <v>["efterår", "vinter"]</v>
       </c>
       <c r="X8" t="str">
-        <v>["sjaler","lette bluser","holdtråd","oversize sweatre"]</v>
+        <v>["sweatre", "cardigans", "huer"]</v>
       </c>
       <c r="Y8" t="str">
-        <v>Danmarks mest brugte held-together garn. Bruges i hundredvis af moderne opskrifter kombineret med merino eller andre garntyper for blødt halo-udtryk. Meget prisvenlig alternativ til kid-silk mohair.</v>
+        <v>Single-spun tweed-udgave af Lamauld med 40% lama, 40% ren ny uld og 20% viskose. Viskosen tilfører farvenoller og fald, lama/uld giver varme og rustik karakter.</v>
       </c>
       <c r="Z8" t="str">
-        <v>/garn-eksempler/drops-brushed-alpaca-silk.jpg</v>
+        <v>/garn-eksempler/camarose-lama-tweed.jpg</v>
       </c>
       <c r="AA8" t="str">
-        <v>[{"fiber":"alpaka","percentage":77},{"fiber":"silke","percentage":23}]</v>
+        <v>[{"fiber": "alpaka", "percentage": 40}, {"fiber": "uld", "percentage": 40}, {"fiber": "viskose", "percentage": 20}]</v>
       </c>
     </row>
     <row r="9">
@@ -1072,52 +1072,52 @@
         <v/>
       </c>
       <c r="B9" t="str">
-        <v>Drops</v>
+        <v>CaMaRose</v>
       </c>
       <c r="C9" t="str">
-        <v>Flora</v>
+        <v>Lamauld</v>
       </c>
       <c r="D9" t="str">
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>uld/alpaka</v>
+        <v>lama/uld</v>
       </c>
       <c r="F9" t="str">
-        <v>fingering</v>
+        <v>dk</v>
       </c>
       <c r="G9">
         <v>50</v>
       </c>
       <c r="H9">
-        <v>420</v>
+        <v>200</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K9">
+        <v>18</v>
+      </c>
+      <c r="L9">
         <v>24</v>
       </c>
-      <c r="L9">
-        <v>32</v>
-      </c>
-      <c r="M9" t="str">
-        <v/>
+      <c r="M9">
+        <v>4</v>
       </c>
       <c r="N9" t="str">
-        <v>4-trådet plied fingering, uld + superfin alpaka, medium twist</v>
-      </c>
-      <c r="O9">
-        <v>4</v>
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
       </c>
       <c r="P9" t="str">
-        <v>plied</v>
+        <v>singles</v>
       </c>
       <c r="Q9" t="str">
-        <v>standard</v>
+        <v/>
       </c>
       <c r="R9" t="str">
         <v>handvask</v>
@@ -1132,39 +1132,39 @@
         <v>i_produktion</v>
       </c>
       <c r="V9" t="str">
-        <v>["Oeko-Tex Standard 100 (Class I)"]</v>
+        <v>[]</v>
       </c>
       <c r="W9" t="str">
-        <v>[]</v>
+        <v>["efterår", "vinter"]</v>
       </c>
       <c r="X9" t="str">
-        <v>["sokker","sjaler","colorwork","barnetøj","lette sweatre"]</v>
+        <v>["sweatre", "cardigans", "huer", "tilbehør"]</v>
       </c>
       <c r="Y9" t="str">
-        <v>Slidstærkt fingering-garn med alpaka-blanding — særligt populær til sokker pga. holdbarheden. Tynd nok til colorwork og sjaler, blød nok til barnetøj.</v>
+        <v>Klassisk single-spun garn i 50% lama og 50% peruviansk højlandsuld fra CaMaRose. Lanolin-frit, let og varmt med naturlig glans. 50g/100m på pind 4,5-5 mm.</v>
       </c>
       <c r="Z9" t="str">
-        <v/>
+        <v>/garn-eksempler/camarose-lamauld.jpg</v>
       </c>
       <c r="AA9" t="str">
-        <v>[{"fiber":"uld","percentage":65},{"fiber":"alpaka","percentage":35}]</v>
+        <v>[{"fiber": "alpaka", "percentage": 50}, {"fiber": "uld", "percentage": 50}]</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1985c06d-d88b-4011-9024-b3fd9579926d</v>
+        <v/>
       </c>
       <c r="B10" t="str">
-        <v>Drops</v>
+        <v>CaMaRose</v>
       </c>
       <c r="C10" t="str">
-        <v>Karisma</v>
+        <v>Snefnug</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Uld</v>
+        <v>alpaka/bomuld/uld</v>
       </c>
       <c r="F10" t="str">
         <v>dk</v>
@@ -1173,43 +1173,43 @@
         <v>50</v>
       </c>
       <c r="H10">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="I10">
         <v>4</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>21</v>
-      </c>
-      <c r="L10">
-        <v>28</v>
+        <v>14</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N10" t="str">
-        <v>4-trådet plied klassisk uldgarn, fast twist, superwash-behandlet</v>
-      </c>
-      <c r="O10">
-        <v>4</v>
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
       </c>
       <c r="P10" t="str">
-        <v>plied</v>
+        <v>chainette</v>
       </c>
       <c r="Q10" t="str">
-        <v>superwash</v>
+        <v/>
       </c>
       <c r="R10" t="str">
-        <v>maskinvask_40</v>
+        <v>handvask</v>
       </c>
       <c r="S10" t="str">
-        <v>EU</v>
+        <v>Italien</v>
       </c>
       <c r="T10" t="str">
-        <v>Sydamerika</v>
+        <v>Peru</v>
       </c>
       <c r="U10" t="str">
         <v>i_produktion</v>
@@ -1218,232 +1218,232 @@
         <v>[]</v>
       </c>
       <c r="W10" t="str">
-        <v>[]</v>
+        <v>["efterår", "vinter"]</v>
       </c>
       <c r="X10" t="str">
-        <v>["sweatre","huer","vanter","børnetøj","mønsterstrik"]</v>
+        <v>["sweatre", "cardigans", "huer"]</v>
       </c>
       <c r="Y10" t="str">
-        <v>En af de absolut mest populære DROPS-kvaliteter. Slidstærkt, superwash-behandlet uldgarn til en meget prisvenlig pris. Fast twist giver god maskedefinition — god til farvemønstre.</v>
+        <v>Blow-yarn med bomuldskerne og 55% babyalpaka, 35% økologisk bomuld og 10% mulesing-fri merinould blæst rundt om. Let, luftigt og fyldigt — fra italiensk familieejet mølle.</v>
       </c>
       <c r="Z10" t="str">
-        <v/>
+        <v>/garn-eksempler/camarose-snefnug.jpg</v>
       </c>
       <c r="AA10" t="str">
-        <v>[{"fiber":"uld","percentage":100}]</v>
+        <v>[{"fiber": "baby_alpaka", "percentage": 55}, {"fiber": "bomuld", "percentage": 35}, {"fiber": "merinould", "percentage": 10}]</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>3d8d48b3-ffce-4733-9aa4-e9bc593a0218</v>
+        <v/>
       </c>
       <c r="B11" t="str">
-        <v>Drops</v>
+        <v>CaMaRose</v>
       </c>
       <c r="C11" t="str">
-        <v>Merino Extra Fine</v>
+        <v>Midnatssol</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Merinould</v>
+        <v>alpaka/lyocell/uld</v>
       </c>
       <c r="F11" t="str">
-        <v>dk</v>
+        <v>lace</v>
       </c>
       <c r="G11">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H11">
-        <v>210</v>
+        <v>800</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>21</v>
-      </c>
-      <c r="L11">
-        <v>28</v>
+        <v>20</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="str">
-        <v>4-trådet plied kamgarn, medium twist, superwash merino</v>
-      </c>
-      <c r="O11">
-        <v>4</v>
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
       </c>
       <c r="P11" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q11" t="str">
-        <v>superwash</v>
+        <v/>
       </c>
       <c r="R11" t="str">
-        <v>maskinvask_40</v>
+        <v>handvask</v>
       </c>
       <c r="S11" t="str">
-        <v>EU</v>
+        <v>Italien</v>
       </c>
       <c r="T11" t="str">
-        <v>Sydamerika</v>
+        <v/>
       </c>
       <c r="U11" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V11" t="str">
-        <v>["Oeko-Tex 100"]</v>
+        <v>[]</v>
       </c>
       <c r="W11" t="str">
-        <v>[]</v>
+        <v>["forår", "efterår", "vinter"]</v>
       </c>
       <c r="X11" t="str">
-        <v>["sweatre","cardigans","huer","vanter","babytøj"]</v>
+        <v>["sjaler", "lette bluser", "hold-ind-garn"]</v>
       </c>
       <c r="Y11" t="str">
-        <v>Det foretrukne DK-garn fra DROPS — alsidigt, blødt og maskinvaskbart. Et af DROPS' absolut bedst sælgende garner i Danmark. Stor farvepalette og skarp pris.</v>
+        <v>Let, luksuriøs blanding af 54% babyalpaka, 36% lyocell og 10% mulesing-fri merinould. Spundet på italiensk familiemølle. Egnet som hold-ind-garn eller alene til lette sjaler.</v>
       </c>
       <c r="Z11" t="str">
-        <v/>
+        <v>/garn-eksempler/camarose-midnatssol.jpg</v>
       </c>
       <c r="AA11" t="str">
-        <v>[{"fiber":"merinould","percentage":100}]</v>
+        <v>[{"fiber": "baby_alpaka", "percentage": 54}, {"fiber": "viskose", "percentage": 36}, {"fiber": "merinould", "percentage": 10}]</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>fbcf057a-b34a-410a-8cd9-5ff15a54884c</v>
+        <v/>
       </c>
       <c r="B12" t="str">
         <v>Drops</v>
       </c>
       <c r="C12" t="str">
-        <v>Safran</v>
+        <v>Air</v>
       </c>
       <c r="D12" t="str">
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Bomuld</v>
+        <v>alpaka/uld/nylon</v>
       </c>
       <c r="F12" t="str">
-        <v>sport</v>
+        <v>aran</v>
       </c>
       <c r="G12">
         <v>50</v>
       </c>
       <c r="H12">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L12">
-        <v>32</v>
-      </c>
-      <c r="M12">
-        <v>3</v>
+        <v>22</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
       </c>
       <c r="N12" t="str">
-        <v>4-trådet plied kæmmet bomuld, fast og glat twist, god maskedefinition</v>
-      </c>
-      <c r="O12">
-        <v>4</v>
+        <v>Chainette/blown — fibre blæst ind i en tynd nylon-tube i stedet for klassisk spinding</v>
+      </c>
+      <c r="O12" t="str">
+        <v/>
       </c>
       <c r="P12" t="str">
-        <v>plied</v>
+        <v>chainette</v>
       </c>
       <c r="Q12" t="str">
         <v>standard</v>
       </c>
       <c r="R12" t="str">
-        <v>maskinvask_40</v>
+        <v>handvask</v>
       </c>
       <c r="S12" t="str">
-        <v>Tyrkiet</v>
+        <v>Peru/EU</v>
       </c>
       <c r="T12" t="str">
-        <v>Egypten</v>
+        <v>Peru</v>
       </c>
       <c r="U12" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V12" t="str">
-        <v>["Oeko-Tex 100"]</v>
+        <v>["Oeko-Tex Standard 100 (Class I)"]</v>
       </c>
       <c r="W12" t="str">
         <v>[]</v>
       </c>
       <c r="X12" t="str">
-        <v>["sommertoppe","karklude","babytøj","hækling","sommerbluser"]</v>
+        <v>["lette sweatre","cardigans","oversize strik","babytæpper","tilbehør"]</v>
       </c>
       <c r="Y12" t="str">
-        <v>Go-to bomuldsgarn til sommerstrik og karklude. Enorm farvepalette og skarp pris — under 25 kr per nøgle. OEKO-TEX certificeret. Maskinvask 40°C på skåneprogram.</v>
+        <v>Lofty "blown" garn hvor baby-alpaka og merinould blæses ind i en tynd nylon-tube i stedet for at blive spundet. Færdige plagg er 30-35% lettere end tilsvarende tykkelse i klassisk spundet garn. Meget populær til behagelige oversize sweatre.</v>
       </c>
       <c r="Z12" t="str">
         <v/>
       </c>
       <c r="AA12" t="str">
-        <v>[{"fiber":"bomuld","percentage":100}]</v>
+        <v>[{"fiber":"baby_alpaka","percentage":65},{"fiber":"nylon_polyamid","percentage":28},{"fiber":"merinould","percentage":7}]</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>a27b8360-0521-4943-9f9c-dbb3e73b18ea</v>
+        <v>185bc557-cd0b-4256-8ac2-4b982b037a0d</v>
       </c>
       <c r="B13" t="str">
-        <v>Filatura di Crosa</v>
+        <v>Drops</v>
       </c>
       <c r="C13" t="str">
-        <v>Wave</v>
+        <v>Alaska</v>
       </c>
       <c r="D13" t="str">
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Merinould-blanding</v>
+        <v>Uld</v>
       </c>
       <c r="F13" t="str">
-        <v>worsted</v>
+        <v>aran</v>
       </c>
       <c r="G13">
         <v>50</v>
       </c>
       <c r="H13">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="I13">
         <v>5</v>
       </c>
       <c r="J13">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L13">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M13">
         <v>5</v>
       </c>
       <c r="N13" t="str">
-        <v>Plied merino-silke-blanding, medium twist, blød og let glansfuld pga. silken</v>
-      </c>
-      <c r="O13" t="str">
-        <v/>
+        <v>3-trådet plied, klassisk spundet, ubehandlet ren ny uld, medium twist</v>
+      </c>
+      <c r="O13">
+        <v>3</v>
       </c>
       <c r="P13" t="str">
         <v>plied</v>
@@ -1455,7 +1455,7 @@
         <v>handvask</v>
       </c>
       <c r="S13" t="str">
-        <v>Italien</v>
+        <v>Norge</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1464,167 +1464,167 @@
         <v>i_produktion</v>
       </c>
       <c r="V13" t="str">
-        <v>[]</v>
+        <v>["Oeko-Tex Standard 100 (Class I)"]</v>
       </c>
       <c r="W13" t="str">
         <v>[]</v>
       </c>
       <c r="X13" t="str">
-        <v>["lette sweatre","cardigans","sjaler","tørklæder"]</v>
+        <v>["tykke vintersweatre","jakker","tæpper","toveprojekter","læringsprojekter"]</v>
       </c>
       <c r="Y13" t="str">
-        <v>Specialgarn — ikke bredt distribueret i Danmark.</v>
+        <v>Billigt budget-garn. Kan filtes.</v>
       </c>
       <c r="Z13" t="str">
         <v/>
       </c>
       <c r="AA13" t="str">
-        <v>[{"fiber":"merinould","percentage":75},{"fiber":"silke","percentage":25}]</v>
+        <v>[{"fiber":"uld","percentage":100}]</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>3db069d1-706a-440e-8e9e-327d4eeb8336</v>
       </c>
       <c r="B14" t="str">
-        <v>Filcolana</v>
+        <v>Drops</v>
       </c>
       <c r="C14" t="str">
-        <v>Anina</v>
+        <v>Alpaca</v>
       </c>
       <c r="D14" t="str">
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>merino</v>
+        <v>Alpaka</v>
       </c>
       <c r="F14" t="str">
-        <v>fingering</v>
+        <v>sport</v>
       </c>
       <c r="G14">
         <v>50</v>
       </c>
       <c r="H14">
-        <v>420</v>
+        <v>334</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J14">
         <v>3.5</v>
       </c>
       <c r="K14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L14">
-        <v>40</v>
-      </c>
-      <c r="M14" t="str">
-        <v/>
+        <v>30</v>
+      </c>
+      <c r="M14">
+        <v>3</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>5-trådet plied, 100% superfin ubehandlet alpaka, blød og let med naturlig glans</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q14" t="str">
-        <v>superwash</v>
+        <v>standard</v>
       </c>
       <c r="R14" t="str">
-        <v>maskinvask_30</v>
+        <v>handvask</v>
       </c>
       <c r="S14" t="str">
         <v>Peru</v>
       </c>
       <c r="T14" t="str">
-        <v/>
+        <v>Peru</v>
       </c>
       <c r="U14" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V14" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="W14" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X14" t="str">
-        <v/>
+        <v>["sjaler","lette sweatre","cardigans","babytøj","tilbehør"]</v>
       </c>
       <c r="Y14" t="str">
-        <v/>
+        <v>Klassisk, let alpakagarn med fantastisk drapering og farvemætning. Populært til sjaler og lette projekter. Kradser ikke og er blødt mod huden. Et af DROPS' ældste og mest elskede kvaliteter.</v>
       </c>
       <c r="Z14" t="str">
         <v/>
       </c>
       <c r="AA14" t="str">
-        <v>[{"fiber":"merinould","percentage":100}]</v>
+        <v>[{"fiber":"alpaka","percentage":100}]</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>8734f3f3-3570-48de-81e7-182d37542093</v>
+        <v>de1a9830-abbd-406b-9bc9-8461920f4618</v>
       </c>
       <c r="B15" t="str">
-        <v>Filcolana</v>
+        <v>Drops</v>
       </c>
       <c r="C15" t="str">
-        <v>Arwetta Classic</v>
+        <v>Brushed Alpaca Silk</v>
       </c>
       <c r="D15" t="str">
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Uld</v>
+        <v>Alpaka-blanding</v>
       </c>
       <c r="F15" t="str">
-        <v>fingering</v>
+        <v>aran</v>
       </c>
       <c r="G15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H15">
-        <v>420</v>
+        <v>560</v>
       </c>
       <c r="I15">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="L15">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N15" t="str">
-        <v>4-trådet, klassisk plied</v>
-      </c>
-      <c r="O15">
-        <v>4</v>
+        <v>Brushed single, børstet superfin alpaka med silkekerne, kraftig halo</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
       </c>
       <c r="P15" t="str">
-        <v>plied</v>
+        <v>brushed_singles</v>
       </c>
       <c r="Q15" t="str">
-        <v>superwash</v>
+        <v>brushed</v>
       </c>
       <c r="R15" t="str">
-        <v>maskinvask_30</v>
+        <v>handvask</v>
       </c>
       <c r="S15" t="str">
-        <v>Danmark</v>
+        <v>Peru</v>
       </c>
       <c r="T15" t="str">
-        <v>Peru</v>
+        <v/>
       </c>
       <c r="U15" t="str">
         <v>i_produktion</v>
@@ -1636,16 +1636,16 @@
         <v>[]</v>
       </c>
       <c r="X15" t="str">
-        <v>["sokker","sjaler","babytøj"]</v>
+        <v>["sjaler","lette bluser","holdtråd","oversize sweatre"]</v>
       </c>
       <c r="Y15" t="str">
-        <v>Min go-to sokkegarn — slidstærk pga. nylon</v>
+        <v>Danmarks mest brugte held-together garn. Bruges i hundredvis af moderne opskrifter kombineret med merino eller andre garntyper for blødt halo-udtryk. Meget prisvenlig alternativ til kid-silk mohair.</v>
       </c>
       <c r="Z15" t="str">
-        <v/>
+        <v>/garn-eksempler/drops-brushed-alpaca-silk.jpg</v>
       </c>
       <c r="AA15" t="str">
-        <v>[{"fiber":"merinould","percentage":80},{"fiber":"nylon_polyamid","percentage":20}]</v>
+        <v>[{"fiber":"alpaka","percentage":77},{"fiber":"silke","percentage":23}]</v>
       </c>
     </row>
     <row r="16">
@@ -1653,52 +1653,52 @@
         <v/>
       </c>
       <c r="B16" t="str">
-        <v>Filcolana</v>
+        <v>Drops</v>
       </c>
       <c r="C16" t="str">
-        <v>Peruvian</v>
+        <v>Flora</v>
       </c>
       <c r="D16" t="str">
-        <v>Highland Wool</v>
+        <v/>
       </c>
       <c r="E16" t="str">
-        <v>uld</v>
+        <v>uld/alpaka</v>
       </c>
       <c r="F16" t="str">
-        <v>aran</v>
+        <v>fingering</v>
       </c>
       <c r="G16">
         <v>50</v>
       </c>
       <c r="H16">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="I16">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K16">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L16">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>4-trådet plied fingering, uld + superfin alpaka, medium twist</v>
       </c>
       <c r="O16">
         <v>4</v>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>standard</v>
       </c>
       <c r="R16" t="str">
         <v>handvask</v>
@@ -1713,54 +1713,54 @@
         <v>i_produktion</v>
       </c>
       <c r="V16" t="str">
-        <v/>
+        <v>["Oeko-Tex Standard 100 (Class I)"]</v>
       </c>
       <c r="W16" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X16" t="str">
-        <v/>
+        <v>["sokker","sjaler","colorwork","barnetøj","lette sweatre"]</v>
       </c>
       <c r="Y16" t="str">
-        <v/>
+        <v>Slidstærkt fingering-garn med alpaka-blanding — særligt populær til sokker pga. holdbarheden. Tynd nok til colorwork og sjaler, blød nok til barnetøj.</v>
       </c>
       <c r="Z16" t="str">
         <v/>
       </c>
       <c r="AA16" t="str">
-        <v>[{"fiber":"uld","percentage":100}]</v>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
+        <v>[{"fiber":"uld","percentage":65},{"fiber":"alpaka","percentage":35}]</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="str">
-        <v>730b2343-6a3c-430b-a25e-24cae2289d1b</v>
+        <v>1985c06d-d88b-4011-9024-b3fd9579926d</v>
       </c>
       <c r="B17" t="str">
-        <v>Filcolana</v>
+        <v>Drops</v>
       </c>
       <c r="C17" t="str">
-        <v>Tilia</v>
+        <v>Karisma</v>
       </c>
       <c r="D17" t="str">
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>Kid mohair</v>
+        <v>Uld</v>
       </c>
       <c r="F17" t="str">
-        <v>lace</v>
+        <v>dk</v>
       </c>
       <c r="G17">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H17">
-        <v>840</v>
+        <v>210</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K17">
         <v>21</v>
@@ -1772,25 +1772,25 @@
         <v>4</v>
       </c>
       <c r="N17" t="str">
-        <v>Brushed kid mohair single med silke, langfibret, kraftig halo</v>
-      </c>
-      <c r="O17" t="str">
-        <v/>
+        <v>4-trådet plied klassisk uldgarn, fast twist, superwash-behandlet</v>
+      </c>
+      <c r="O17">
+        <v>4</v>
       </c>
       <c r="P17" t="str">
-        <v>brushed_singles</v>
+        <v>plied</v>
       </c>
       <c r="Q17" t="str">
-        <v>brushed</v>
+        <v>superwash</v>
       </c>
       <c r="R17" t="str">
-        <v>handvask</v>
+        <v>maskinvask_40</v>
       </c>
       <c r="S17" t="str">
-        <v>Italien</v>
+        <v>EU</v>
       </c>
       <c r="T17" t="str">
-        <v>Sydafrika</v>
+        <v>Sydamerika</v>
       </c>
       <c r="U17" t="str">
         <v>i_produktion</v>
@@ -1802,267 +1802,265 @@
         <v>[]</v>
       </c>
       <c r="X17" t="str">
-        <v>["sjaler","lette bluser","let overtøj"]</v>
-      </c>
-      <c r="Y17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tilia er et luksuriøst garn spundet af 70% kidmohair og 30% morbærsilke. Teknisk set er Tilia et tyndt, kamgarnsspundet og børstet garn. Mohair har mange af de gode egenskaber, vi kender fra uld: det er varmt, let og kan absorbere fugt, hvilket gør det behageligt at have på. Mohairfibrene er desuden blanke og en smule stærkere end almindelige uldfibre. Silke har igennem årtusinder været en af de mest eftertragtede tekstilfibre – den er blank, smuk, stærk og utrolig behagelig at have på._x000d__x000d_
-_x000d__x000d_
-Kombinationen af silke og en let sky af mohair giver et luftigt, blødt og elegant udtryk – og er noget af det mest luksuriøse garn, man kan ønske sig at strikke med, både alene og som følgetråd.</v>
+        <v>["sweatre","huer","vanter","børnetøj","mønsterstrik"]</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>En af de absolut mest populære DROPS-kvaliteter. Slidstærkt, superwash-behandlet uldgarn til en meget prisvenlig pris. Fast twist giver god maskedefinition — god til farvemønstre.</v>
       </c>
       <c r="Z17" t="str">
-        <v>/garn-eksempler/filcolana-tilia.jpg</v>
+        <v/>
       </c>
       <c r="AA17" t="str">
-        <v>[{"fiber":"kid_mohair","percentage":70},{"fiber":"silke","percentage":30}]</v>
+        <v>[{"fiber":"uld","percentage":100}]</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>89d346f6-e898-4b94-b0f3-1d166d6c32a9</v>
+        <v>3d8d48b3-ffce-4733-9aa4-e9bc593a0218</v>
       </c>
       <c r="B18" t="str">
-        <v>Fonty</v>
+        <v>Drops</v>
       </c>
       <c r="C18" t="str">
-        <v>Ombelle</v>
+        <v>Merino Extra Fine</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Kid mohair-blanding</v>
+        <v>Merinould</v>
       </c>
       <c r="F18" t="str">
-        <v>fingering</v>
+        <v>dk</v>
       </c>
       <c r="G18">
         <v>50</v>
       </c>
       <c r="H18">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="I18">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J18">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L18">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M18">
         <v>4</v>
       </c>
       <c r="N18" t="str">
-        <v>Brushed mohair-blanding, single ply med langt halo</v>
-      </c>
-      <c r="O18" t="str">
-        <v/>
+        <v>4-trådet plied kamgarn, medium twist, superwash merino</v>
+      </c>
+      <c r="O18">
+        <v>4</v>
       </c>
       <c r="P18" t="str">
-        <v>brushed_singles</v>
+        <v>plied</v>
       </c>
       <c r="Q18" t="str">
-        <v>brushed</v>
+        <v>superwash</v>
       </c>
       <c r="R18" t="str">
-        <v>handvask</v>
+        <v>maskinvask_40</v>
       </c>
       <c r="S18" t="str">
-        <v>Frankrig</v>
+        <v>EU</v>
       </c>
       <c r="T18" t="str">
-        <v/>
+        <v>Sydamerika</v>
       </c>
       <c r="U18" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V18" t="str">
-        <v>[]</v>
+        <v>["Oeko-Tex 100"]</v>
       </c>
       <c r="W18" t="str">
         <v>[]</v>
       </c>
       <c r="X18" t="str">
-        <v>["lette sweatre","tørklæder","sjaler","holdtråd"]</v>
+        <v>["sweatre","cardigans","huer","vanter","babytøj"]</v>
       </c>
       <c r="Y18" t="str">
-        <v>Fransk mohair-klassiker. Samme fibersammensætning som Permin Bella, men strikkes på meget mindre pind — fin let kvalitet snarere end chunky.</v>
+        <v>Det foretrukne DK-garn fra DROPS — alsidigt, blødt og maskinvaskbart. Et af DROPS' absolut bedst sælgende garner i Danmark. Stor farvepalette og skarp pris.</v>
       </c>
       <c r="Z18" t="str">
         <v/>
       </c>
       <c r="AA18" t="str">
-        <v>[{"fiber":"kid_mohair","percentage":75},{"fiber":"uld","percentage":20},{"fiber":"nylon_polyamid","percentage":5}]</v>
+        <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>fbcf057a-b34a-410a-8cd9-5ff15a54884c</v>
       </c>
       <c r="B19" t="str">
-        <v>Gepard</v>
+        <v>Drops</v>
       </c>
       <c r="C19" t="str">
-        <v>CottonWool 5</v>
+        <v>Safran</v>
       </c>
       <c r="D19" t="str">
-        <v>Organic</v>
+        <v/>
       </c>
       <c r="E19" t="str">
-        <v>bomuld/merino</v>
+        <v>Bomuld</v>
       </c>
       <c r="F19" t="str">
-        <v>dk</v>
+        <v>sport</v>
       </c>
       <c r="G19">
         <v>50</v>
       </c>
       <c r="H19">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="I19">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>22</v>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <v/>
+        <v>24</v>
+      </c>
+      <c r="L19">
+        <v>32</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
       </c>
       <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <v/>
+        <v>4-trådet plied kæmmet bomuld, fast og glat twist, god maskedefinition</v>
+      </c>
+      <c r="O19">
+        <v>4</v>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>standard</v>
       </c>
       <c r="R19" t="str">
-        <v>maskinvask_30</v>
+        <v>maskinvask_40</v>
       </c>
       <c r="S19" t="str">
-        <v>Italien</v>
+        <v>Tyrkiet</v>
       </c>
       <c r="T19" t="str">
-        <v/>
+        <v>Egypten</v>
       </c>
       <c r="U19" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V19" t="str">
-        <v>["GOTS (bomuld)","Oeko-Tex 100"]</v>
+        <v>["Oeko-Tex 100"]</v>
       </c>
       <c r="W19" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X19" t="str">
-        <v/>
+        <v>["sommertoppe","karklude","babytøj","hækling","sommerbluser"]</v>
       </c>
       <c r="Y19" t="str">
-        <v/>
+        <v>Go-to bomuldsgarn til sommerstrik og karklude. Enorm farvepalette og skarp pris — under 25 kr per nøgle. OEKO-TEX certificeret. Maskinvask 40°C på skåneprogram.</v>
       </c>
       <c r="Z19" t="str">
         <v/>
       </c>
       <c r="AA19" t="str">
-        <v>[{"fiber":"bomuld","percentage":50},{"fiber":"merinould","percentage":50}]</v>
+        <v>[{"fiber":"bomuld","percentage":100}]</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>3a47d529-e8fb-4242-a04a-f3122e5e92bd</v>
+        <v/>
       </c>
       <c r="B20" t="str">
-        <v>Gepard</v>
+        <v>Drops</v>
       </c>
       <c r="C20" t="str">
-        <v>Kid Silk 5</v>
+        <v>Baby Merino</v>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Kid mohair</v>
+        <v>merinould</v>
       </c>
       <c r="F20" t="str">
-        <v>lace</v>
+        <v>sport</v>
       </c>
       <c r="G20">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H20">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20">
         <v>3.5</v>
       </c>
-      <c r="J20">
-        <v>8</v>
-      </c>
       <c r="K20">
-        <v>14</v>
-      </c>
-      <c r="L20">
-        <v>19</v>
-      </c>
-      <c r="M20">
-        <v>6</v>
+        <v>24</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
       </c>
       <c r="N20" t="str">
-        <v>Brushed single, kid mohair med silke, langfibret og kraftig halo</v>
-      </c>
-      <c r="O20" t="str">
-        <v/>
+        <v>3-trådet plied, superwash extrafine merino, medium twist</v>
+      </c>
+      <c r="O20">
+        <v>3</v>
       </c>
       <c r="P20" t="str">
-        <v>brushed_singles</v>
+        <v>plied</v>
       </c>
       <c r="Q20" t="str">
-        <v>brushed</v>
+        <v>superwash</v>
       </c>
       <c r="R20" t="str">
-        <v>handvask</v>
+        <v>maskinvask_40</v>
       </c>
       <c r="S20" t="str">
-        <v>Sydafrika</v>
+        <v>EU</v>
       </c>
       <c r="T20" t="str">
-        <v>Sydafrika</v>
+        <v>Sydamerika</v>
       </c>
       <c r="U20" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V20" t="str">
-        <v>[]</v>
+        <v>["Oeko-Tex Standard 100 (Class I)"]</v>
       </c>
       <c r="W20" t="str">
         <v>[]</v>
       </c>
       <c r="X20" t="str">
-        <v>["lette mohairbluser","oversize sweatre","sjaler","holdtråd"]</v>
+        <v>["babytøj","børnestrik","lette sweatre","sjaler","cardigans"]</v>
       </c>
       <c r="Y20" t="str">
-        <v>Bliver løs i det med en tråd og dyr, hvis man skal strikke med 2 tråde</v>
+        <v>Blød, superwash-behandlet extrafine merino til babytøj og lette voksenstrik. Oeko-Tex klasse I certificeret — godkendt til babyer under 3 år. Maskinvask på uldprogram 40°C.</v>
       </c>
       <c r="Z20" t="str">
-        <v/>
+        <v>/garn-eksempler/drops-baby-merino.jpg</v>
       </c>
       <c r="AA20" t="str">
-        <v>[{"fiber":"kid_mohair","percentage":80},{"fiber":"silke","percentage":20}]</v>
+        <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
     <row r="21">
@@ -2070,40 +2068,40 @@
         <v/>
       </c>
       <c r="B21" t="str">
-        <v>Gepard</v>
+        <v>Edy Angola</v>
       </c>
       <c r="C21" t="str">
-        <v>Puno</v>
+        <v>Mohair Edition Recy</v>
       </c>
       <c r="D21" t="str">
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>alpaka/merino/nylon</v>
+        <v>mohair-blanding</v>
       </c>
       <c r="F21" t="str">
-        <v>bulky</v>
+        <v>fingering</v>
       </c>
       <c r="G21">
         <v>50</v>
       </c>
       <c r="H21">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="I21">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="J21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="L21" t="str">
         <v/>
       </c>
-      <c r="M21" t="str">
-        <v/>
+      <c r="M21">
+        <v>3.5</v>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -2121,7 +2119,7 @@
         <v>handvask</v>
       </c>
       <c r="S21" t="str">
-        <v/>
+        <v>Danmark</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -2130,84 +2128,84 @@
         <v>i_produktion</v>
       </c>
       <c r="V21" t="str">
-        <v>["RAS","RWS"]</v>
+        <v>[]</v>
       </c>
       <c r="W21" t="str">
-        <v/>
+        <v>["efterår", "vinter"]</v>
       </c>
       <c r="X21" t="str">
-        <v/>
+        <v>["bluser", "sjaler", "hold-ind-garn"]</v>
       </c>
       <c r="Y21" t="str">
-        <v/>
+        <v>Dansk mohair-blanding med fokus på bæredygtighed: 21% mohair, 40% genanvendt bomuld, 26% merinould og 13% polyamid. 50g/165m, fnug-let med rustik karakter.</v>
       </c>
       <c r="Z21" t="str">
-        <v/>
+        <v>/garn-eksempler/edy-angola-mohair-edition-recy.jpg</v>
       </c>
       <c r="AA21" t="str">
-        <v>[{"fiber":"baby_alpaka","percentage":68},{"fiber":"merinould","percentage":10},{"fiber":"nylon_polyamid","percentage":22}]</v>
+        <v>[{"fiber": "mohair", "percentage": 21}, {"fiber": "bomuld", "percentage": 40}, {"fiber": "merinould", "percentage": 26}, {"fiber": "nylon_polyamid", "percentage": 13}]</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>33c79df9-c09b-4a41-8d83-6b00a7f1f33f</v>
+        <v/>
       </c>
       <c r="B22" t="str">
-        <v>Hjertegarn</v>
+        <v>Edy Angola</v>
       </c>
       <c r="C22" t="str">
-        <v>Extrafine Merino 90</v>
+        <v>Alpaca Merino</v>
       </c>
       <c r="D22" t="str">
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>Merinould</v>
+        <v>merino/alpaka</v>
       </c>
       <c r="F22" t="str">
-        <v>aran</v>
+        <v>fingering</v>
       </c>
       <c r="G22">
         <v>50</v>
       </c>
       <c r="H22">
-        <v>180</v>
+        <v>310</v>
       </c>
       <c r="I22">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J22">
         <v>5</v>
       </c>
       <c r="K22">
-        <v>18</v>
-      </c>
-      <c r="L22">
-        <v>28</v>
-      </c>
-      <c r="M22">
-        <v>4.5</v>
+        <v>20</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
       </c>
       <c r="N22" t="str">
-        <v>3-trådet plied kamgarn, superwash merino, glat og blød</v>
-      </c>
-      <c r="O22">
-        <v>3</v>
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
       </c>
       <c r="P22" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q22" t="str">
-        <v>superwash</v>
+        <v/>
       </c>
       <c r="R22" t="str">
-        <v>maskinvask_40</v>
+        <v>handvask</v>
       </c>
       <c r="S22" t="str">
         <v>Danmark</v>
       </c>
       <c r="T22" t="str">
-        <v>Sydamerika</v>
+        <v/>
       </c>
       <c r="U22" t="str">
         <v>i_produktion</v>
@@ -2216,78 +2214,78 @@
         <v>[]</v>
       </c>
       <c r="W22" t="str">
-        <v>[]</v>
+        <v>["forår", "efterår", "vinter"]</v>
       </c>
       <c r="X22" t="str">
-        <v>["sweatre","huer","vanter","børnetøj","hverdagsstrik"]</v>
+        <v>["sweatre", "cardigans", "tilbehør"]</v>
       </c>
       <c r="Y22" t="str">
-        <v>Klassisk dansk storsælger fra Hjertegarn — bredt tilgængeligt i hele Danmark og meget prisvenligt. Superwash-behandlet merino i DK-tykkelse. Stor farvepalette og god kvalitet til hverdagsprojekter.</v>
+        <v>Dansk merino-alpaka-blanding fra Edy Angola: 26% alpaca, 66% merino og 8% polyamid. 50g/155m på pind 3,5-5 mm — blødt, varmt og slidstærkt, godt til klassisk strik.</v>
       </c>
       <c r="Z22" t="str">
         <v/>
       </c>
       <c r="AA22" t="str">
-        <v>[{"fiber":"merinould","percentage":100}]</v>
+        <v>[{"fiber": "merinould", "percentage": 66}, {"fiber": "alpaka", "percentage": 26}, {"fiber": "nylon_polyamid", "percentage": 8}]</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>a27b8360-0521-4943-9f9c-dbb3e73b18ea</v>
       </c>
       <c r="B23" t="str">
-        <v>Holst Garn</v>
+        <v>Filatura di Crosa</v>
       </c>
       <c r="C23" t="str">
-        <v>Coast</v>
+        <v>Wave</v>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>uld/bomuld</v>
+        <v>Merinould-blanding</v>
       </c>
       <c r="F23" t="str">
-        <v>fingering</v>
+        <v>worsted</v>
       </c>
       <c r="G23">
         <v>50</v>
       </c>
       <c r="H23">
-        <v>700</v>
+        <v>230</v>
       </c>
       <c r="I23">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="K23">
-        <v>26</v>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
+        <v>20</v>
+      </c>
+      <c r="L23">
+        <v>25</v>
+      </c>
+      <c r="M23">
+        <v>5</v>
       </c>
       <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23">
-        <v>2</v>
+        <v>Plied merino-silke-blanding, medium twist, blød og let glansfuld pga. silken</v>
+      </c>
+      <c r="O23" t="str">
+        <v/>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q23" t="str">
-        <v/>
+        <v>standard</v>
       </c>
       <c r="R23" t="str">
-        <v>maskinvask_30</v>
+        <v>handvask</v>
       </c>
       <c r="S23" t="str">
-        <v/>
+        <v>Italien</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -2296,22 +2294,22 @@
         <v>i_produktion</v>
       </c>
       <c r="V23" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="W23" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X23" t="str">
-        <v/>
+        <v>["lette sweatre","cardigans","sjaler","tørklæder"]</v>
       </c>
       <c r="Y23" t="str">
-        <v/>
+        <v>Specialgarn — ikke bredt distribueret i Danmark.</v>
       </c>
       <c r="Z23" t="str">
         <v/>
       </c>
       <c r="AA23" t="str">
-        <v>[{"fiber":"merinould","percentage":55},{"fiber":"bomuld","percentage":45}]</v>
+        <v>[{"fiber":"merinould","percentage":75},{"fiber":"silke","percentage":25}]</v>
       </c>
     </row>
     <row r="24">
@@ -2319,16 +2317,16 @@
         <v/>
       </c>
       <c r="B24" t="str">
-        <v>Holst Garn</v>
+        <v>Filcolana</v>
       </c>
       <c r="C24" t="str">
-        <v>Supersoft</v>
+        <v>Anina</v>
       </c>
       <c r="D24" t="str">
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>merino/shetland</v>
+        <v>merino</v>
       </c>
       <c r="F24" t="str">
         <v>fingering</v>
@@ -2337,7 +2335,7 @@
         <v>50</v>
       </c>
       <c r="H24">
-        <v>574</v>
+        <v>420</v>
       </c>
       <c r="I24">
         <v>3</v>
@@ -2346,10 +2344,10 @@
         <v>3.5</v>
       </c>
       <c r="K24">
-        <v>25</v>
-      </c>
-      <c r="L24" t="str">
-        <v/>
+        <v>27</v>
+      </c>
+      <c r="L24">
+        <v>40</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -2358,19 +2356,19 @@
         <v/>
       </c>
       <c r="O24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P24" t="str">
         <v/>
       </c>
       <c r="Q24" t="str">
-        <v/>
+        <v>superwash</v>
       </c>
       <c r="R24" t="str">
         <v>maskinvask_30</v>
       </c>
       <c r="S24" t="str">
-        <v/>
+        <v>Peru</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -2394,24 +2392,24 @@
         <v/>
       </c>
       <c r="AA24" t="str">
-        <v>[{"fiber":"merinould","percentage":50},{"fiber":"shetland_uld","percentage":50}]</v>
+        <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>17d7cfcb-747e-4518-ba88-6e611fecb111</v>
+        <v>8734f3f3-3570-48de-81e7-182d37542093</v>
       </c>
       <c r="B25" t="str">
-        <v>Isager</v>
+        <v>Filcolana</v>
       </c>
       <c r="C25" t="str">
-        <v>Alpaca 2</v>
+        <v>Arwetta Classic</v>
       </c>
       <c r="D25" t="str">
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Alpaka-blanding</v>
+        <v>Uld</v>
       </c>
       <c r="F25" t="str">
         <v>fingering</v>
@@ -2420,7 +2418,7 @@
         <v>50</v>
       </c>
       <c r="H25">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="I25">
         <v>2.5</v>
@@ -2429,31 +2427,31 @@
         <v>3.5</v>
       </c>
       <c r="K25">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L25">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M25">
         <v>3</v>
       </c>
       <c r="N25" t="str">
-        <v>2-trådet plied, alpaka-uldblanding, blød med let glans og god drapering</v>
+        <v>4-trådet, klassisk plied</v>
       </c>
       <c r="O25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P25" t="str">
         <v>plied</v>
       </c>
       <c r="Q25" t="str">
-        <v>standard</v>
+        <v>superwash</v>
       </c>
       <c r="R25" t="str">
-        <v>handvask</v>
+        <v>maskinvask_30</v>
       </c>
       <c r="S25" t="str">
-        <v>Peru</v>
+        <v>Danmark</v>
       </c>
       <c r="T25" t="str">
         <v>Peru</v>
@@ -2468,16 +2466,16 @@
         <v>[]</v>
       </c>
       <c r="X25" t="str">
-        <v>["sweatre","sjaler","cardigans","lette overtøj","tilbehør"]</v>
+        <v>["sokker","sjaler","babytøj"]</v>
       </c>
       <c r="Y25" t="str">
-        <v>Isagers mest populære garn og en dansk klassiker siden 1977. Blød alpaka-uldblanding med smuk farvepalet og god drapering. Ikke-superwash — bæredygtig og holdbar. Meget brugt i Isager og Helga Isager opskrifter.</v>
+        <v>Min go-to sokkegarn — slidstærk pga. nylon</v>
       </c>
       <c r="Z25" t="str">
         <v/>
       </c>
       <c r="AA25" t="str">
-        <v>[{"fiber":"alpaka","percentage":50},{"fiber":"uld","percentage":50}]</v>
+        <v>[{"fiber":"merinould","percentage":80},{"fiber":"nylon_polyamid","percentage":20}]</v>
       </c>
     </row>
     <row r="26">
@@ -2485,46 +2483,46 @@
         <v/>
       </c>
       <c r="B26" t="str">
-        <v>Isager</v>
+        <v>Filcolana</v>
       </c>
       <c r="C26" t="str">
-        <v>Jensen Yarn</v>
+        <v>Peruvian</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>Highland Wool</v>
       </c>
       <c r="E26" t="str">
         <v>uld</v>
       </c>
       <c r="F26" t="str">
-        <v>sport</v>
+        <v>aran</v>
       </c>
       <c r="G26">
         <v>50</v>
       </c>
       <c r="H26">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L26">
-        <v>28</v>
-      </c>
-      <c r="M26">
-        <v>3</v>
+        <v>25</v>
+      </c>
+      <c r="M26" t="str">
+        <v/>
       </c>
       <c r="N26" t="str">
         <v/>
       </c>
       <c r="O26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P26" t="str">
         <v/>
@@ -2536,10 +2534,10 @@
         <v>handvask</v>
       </c>
       <c r="S26" t="str">
-        <v>Danmark</v>
+        <v>Peru</v>
       </c>
       <c r="T26" t="str">
-        <v>New Zealand (hvid), Europa (Gotland: grå/brun)</v>
+        <v>Peru</v>
       </c>
       <c r="U26" t="str">
         <v>i_produktion</v>
@@ -2563,21 +2561,21 @@
         <v>[{"fiber":"uld","percentage":100}]</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" xml:space="preserve">
       <c r="A27" t="str">
-        <v/>
+        <v>730b2343-6a3c-430b-a25e-24cae2289d1b</v>
       </c>
       <c r="B27" t="str">
-        <v>Isager</v>
+        <v>Filcolana</v>
       </c>
       <c r="C27" t="str">
-        <v>Silk Mohair</v>
+        <v>Tilia</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>mohair/silke</v>
+        <v>Kid mohair</v>
       </c>
       <c r="F27" t="str">
         <v>lace</v>
@@ -2586,34 +2584,34 @@
         <v>25</v>
       </c>
       <c r="H27">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27">
         <v>5</v>
       </c>
       <c r="K27">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L27">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N27" t="str">
-        <v/>
+        <v>Brushed kid mohair single med silke, langfibret, kraftig halo</v>
       </c>
       <c r="O27" t="str">
         <v/>
       </c>
       <c r="P27" t="str">
-        <v/>
+        <v>brushed_singles</v>
       </c>
       <c r="Q27" t="str">
-        <v/>
+        <v>brushed</v>
       </c>
       <c r="R27" t="str">
         <v>handvask</v>
@@ -2622,90 +2620,92 @@
         <v>Italien</v>
       </c>
       <c r="T27" t="str">
-        <v>Sydafrika (mohair), silke: ukendt</v>
+        <v>Sydafrika</v>
       </c>
       <c r="U27" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V27" t="str">
-        <v>["RMS"]</v>
+        <v>[]</v>
       </c>
       <c r="W27" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X27" t="str">
-        <v/>
-      </c>
-      <c r="Y27" t="str">
-        <v/>
+        <v>["sjaler","lette bluser","let overtøj"]</v>
+      </c>
+      <c r="Y27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Tilia er et luksuriøst garn spundet af 70% kidmohair og 30% morbærsilke. Teknisk set er Tilia et tyndt, kamgarnsspundet og børstet garn. Mohair har mange af de gode egenskaber, vi kender fra uld: det er varmt, let og kan absorbere fugt, hvilket gør det behageligt at have på. Mohairfibrene er desuden blanke og en smule stærkere end almindelige uldfibre. Silke har igennem årtusinder været en af de mest eftertragtede tekstilfibre – den er blank, smuk, stærk og utrolig behagelig at have på._x000d__x000d__x000d_
+_x000d__x000d__x000d_
+Kombinationen af silke og en let sky af mohair giver et luftigt, blødt og elegant udtryk – og er noget af det mest luksuriøse garn, man kan ønske sig at strikke med, både alene og som følgetråd.</v>
       </c>
       <c r="Z27" t="str">
-        <v/>
+        <v>/garn-eksempler/filcolana-tilia.jpg</v>
       </c>
       <c r="AA27" t="str">
-        <v>[{"fiber":"kid_mohair","percentage":75},{"fiber":"silke","percentage":25}]</v>
+        <v>[{"fiber":"kid_mohair","percentage":70},{"fiber":"silke","percentage":30}]</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>b61537a6-edb9-4e4f-b8ad-9778977a7861</v>
+        <v/>
       </c>
       <c r="B28" t="str">
-        <v>Ístex</v>
+        <v>Filcolana</v>
       </c>
       <c r="C28" t="str">
-        <v>Álafosslopi</v>
+        <v>Alva</v>
       </c>
       <c r="D28" t="str">
-        <v>Lopi</v>
+        <v/>
       </c>
       <c r="E28" t="str">
-        <v>Islandsk uld</v>
+        <v>alpaka</v>
       </c>
       <c r="F28" t="str">
-        <v>bulky</v>
+        <v>lace</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="H28">
-        <v>100</v>
-      </c>
-      <c r="I28">
-        <v>5.5</v>
-      </c>
-      <c r="J28">
-        <v>6.5</v>
-      </c>
-      <c r="K28">
-        <v>14</v>
-      </c>
-      <c r="L28">
-        <v>19</v>
-      </c>
-      <c r="M28">
-        <v>6</v>
+        <v>700</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
       </c>
       <c r="N28" t="str">
-        <v>Let twistet, kraftigt woolen-spun, to tråde løst snoet</v>
-      </c>
-      <c r="O28" t="str">
-        <v/>
+        <v>tyndt 2-trådet alpakagarn</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
       </c>
       <c r="P28" t="str">
         <v>plied</v>
       </c>
       <c r="Q28" t="str">
-        <v>standard</v>
+        <v/>
       </c>
       <c r="R28" t="str">
         <v>handvask</v>
       </c>
       <c r="S28" t="str">
-        <v>Island</v>
+        <v>Peru</v>
       </c>
       <c r="T28" t="str">
-        <v>Island</v>
+        <v>Peru</v>
       </c>
       <c r="U28" t="str">
         <v>i_produktion</v>
@@ -2717,78 +2717,78 @@
         <v>[]</v>
       </c>
       <c r="X28" t="str">
-        <v>["lopapeysa","yoke-trøjer","jakker","udendørstøj"]</v>
+        <v>["følgegarn","sjaler","lette bluser"]</v>
       </c>
       <c r="Y28" t="str">
-        <v>Den klassiske lopapeysa-tykkelse. Kradser på bar hud, men blødgøres ved vask. Varm og vandafvisende.</v>
+        <v>Alva er et tyndt 2-trådet garn spundet af fibre fra peruvianske alpakaer. Alva er blød, varm og glansfuld og velegnet til mange slags projekter. Det tynde garn er perfekt til at strikke sammen med vores andre kvaliteter. Desuden er Alva et herligt alternativt følgegarn i stedet for et tyndt mohairgarn.</v>
       </c>
       <c r="Z28" t="str">
-        <v/>
+        <v>/garn-eksempler/filcolana-alva.jpg</v>
       </c>
       <c r="AA28" t="str">
-        <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
+        <v>[{"fiber":"alpaka","percentage":100}]</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>c382bfc9-523d-42fd-b7dc-53a55b0ad805</v>
+        <v>89d346f6-e898-4b94-b0f3-1d166d6c32a9</v>
       </c>
       <c r="B29" t="str">
-        <v>Ístex</v>
+        <v>Fonty</v>
       </c>
       <c r="C29" t="str">
-        <v>Einband</v>
+        <v>Ombelle</v>
       </c>
       <c r="D29" t="str">
-        <v>Lopi</v>
+        <v/>
       </c>
       <c r="E29" t="str">
-        <v>Islandsk uld</v>
+        <v>Kid mohair-blanding</v>
       </c>
       <c r="F29" t="str">
-        <v>lace</v>
+        <v>fingering</v>
       </c>
       <c r="G29">
         <v>50</v>
       </c>
       <c r="H29">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="I29">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J29">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L29">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N29" t="str">
-        <v>1-trådet single, woolen-spun, let luftig</v>
-      </c>
-      <c r="O29">
-        <v>1</v>
+        <v>Brushed mohair-blanding, single ply med langt halo</v>
+      </c>
+      <c r="O29" t="str">
+        <v/>
       </c>
       <c r="P29" t="str">
-        <v>singles</v>
+        <v>brushed_singles</v>
       </c>
       <c r="Q29" t="str">
-        <v>standard</v>
+        <v>brushed</v>
       </c>
       <c r="R29" t="str">
         <v>handvask</v>
       </c>
       <c r="S29" t="str">
-        <v>Island</v>
+        <v>Frankrig</v>
       </c>
       <c r="T29" t="str">
-        <v>Island</v>
+        <v/>
       </c>
       <c r="U29" t="str">
         <v>i_produktion</v>
@@ -2800,78 +2800,78 @@
         <v>[]</v>
       </c>
       <c r="X29" t="str">
-        <v>["sjaler","lace","holdtråd","islandske mønstre"]</v>
+        <v>["lette sweatre","tørklæder","sjaler","holdtråd"]</v>
       </c>
       <c r="Y29" t="str">
-        <v>Singles-garn med karakteristisk islandsk tovhet. God til sjaler og som holdtråd.</v>
+        <v>Fransk mohair-klassiker. Samme fibersammensætning som Permin Bella, men strikkes på meget mindre pind — fin let kvalitet snarere end chunky.</v>
       </c>
       <c r="Z29" t="str">
-        <v/>
+        <v>/garn-eksempler/fonty-ombelle.jpg</v>
       </c>
       <c r="AA29" t="str">
-        <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
+        <v>[{"fiber":"kid_mohair","percentage":75},{"fiber":"uld","percentage":20},{"fiber":"nylon_polyamid","percentage":5}]</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>68558e71-4c6b-4f9c-b5fd-e884cbbc4cbe</v>
+        <v/>
       </c>
       <c r="B30" t="str">
-        <v>Ístex</v>
+        <v>Froehlich Wolle</v>
       </c>
       <c r="C30" t="str">
-        <v>Léttlopi</v>
+        <v>Special Blauband</v>
       </c>
       <c r="D30" t="str">
-        <v>Lopi</v>
+        <v/>
       </c>
       <c r="E30" t="str">
-        <v>Islandsk uld</v>
+        <v>uld/polyamid</v>
       </c>
       <c r="F30" t="str">
-        <v>aran</v>
+        <v>fingering</v>
       </c>
       <c r="G30">
         <v>50</v>
       </c>
       <c r="H30">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="I30">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="J30">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="K30">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="L30">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="M30">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="N30" t="str">
-        <v>2-trådet woolen-spun, lettere og blødere end Álafosslopi</v>
+        <v/>
       </c>
       <c r="O30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P30" t="str">
         <v>plied</v>
       </c>
       <c r="Q30" t="str">
-        <v>standard</v>
+        <v>superwash</v>
       </c>
       <c r="R30" t="str">
-        <v>handvask</v>
+        <v>maskinvask_30</v>
       </c>
       <c r="S30" t="str">
-        <v>Island</v>
+        <v>Schweiz</v>
       </c>
       <c r="T30" t="str">
-        <v>Island</v>
+        <v/>
       </c>
       <c r="U30" t="str">
         <v>i_produktion</v>
@@ -2880,185 +2880,185 @@
         <v>[]</v>
       </c>
       <c r="W30" t="str">
-        <v>[]</v>
+        <v>["efterår", "vinter"]</v>
       </c>
       <c r="X30" t="str">
-        <v>["lopapeysa","yoke-sweatre","huer","vanter","børnetrøjer"]</v>
+        <v>["sokker", "strømper", "babystrik", "sweatre"]</v>
       </c>
       <c r="Y30" t="str">
-        <v>Light-version af Álafosslopi — halv vægt, halv tykkelse. Mest populære Lopi-kvalitet til moderne lopapeysa.</v>
+        <v>Schweizisk strapadserdygtigt sokkegarn i 75% ny uld og 25% polyamid superwash. 50g/210m, maskinvaskbart — leveres med separat forstærkningstråd til hæl og tå.</v>
       </c>
       <c r="Z30" t="str">
-        <v/>
+        <v>/garn-eksempler/froehlich-wolle-special-blauband.jpg</v>
       </c>
       <c r="AA30" t="str">
-        <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
+        <v>[{"fiber": "uld", "percentage": 75}, {"fiber": "nylon_polyamid", "percentage": 25}]</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>29fbd725-e5c6-4f97-88d7-0cc0b6e91e57</v>
+        <v/>
       </c>
       <c r="B31" t="str">
-        <v>Ístex</v>
+        <v>Gepard</v>
       </c>
       <c r="C31" t="str">
-        <v>Plötulopi</v>
+        <v>CottonWool 5</v>
       </c>
       <c r="D31" t="str">
-        <v>Lopi</v>
+        <v>Organic</v>
       </c>
       <c r="E31" t="str">
-        <v>Islandsk uld</v>
+        <v>bomuld/merino</v>
       </c>
       <c r="F31" t="str">
-        <v>unspun</v>
+        <v>dk</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H31">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I31">
         <v>4.5</v>
       </c>
       <c r="J31">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>18</v>
-      </c>
-      <c r="L31">
-        <v>24</v>
-      </c>
-      <c r="M31">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
       </c>
       <c r="N31" t="str">
-        <v>Uspundet plate — skrøbelig tråd, skal håndteres varsomt</v>
+        <v/>
       </c>
       <c r="O31" t="str">
         <v/>
       </c>
       <c r="P31" t="str">
-        <v>unspun</v>
+        <v/>
       </c>
       <c r="Q31" t="str">
-        <v>standard</v>
+        <v/>
       </c>
       <c r="R31" t="str">
-        <v>handvask</v>
+        <v>maskinvask_30</v>
       </c>
       <c r="S31" t="str">
-        <v>Island</v>
+        <v>Italien</v>
       </c>
       <c r="T31" t="str">
-        <v>Island</v>
+        <v/>
       </c>
       <c r="U31" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V31" t="str">
-        <v>[]</v>
+        <v>["GOTS (bomuld)","Oeko-Tex 100"]</v>
       </c>
       <c r="W31" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="X31" t="str">
-        <v>["lopapeysa","yoke-trøjer","let og luftig strik"]</v>
+        <v/>
       </c>
       <c r="Y31" t="str">
-        <v>Kommer i runde plader à ca. 100 g. Kan holdes 2-3 tråde sammen for tykkere strik.</v>
+        <v/>
       </c>
       <c r="Z31" t="str">
         <v/>
       </c>
       <c r="AA31" t="str">
-        <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
+        <v>[{"fiber":"bomuld","percentage":50},{"fiber":"merinould","percentage":50}]</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>3a47d529-e8fb-4242-a04a-f3122e5e92bd</v>
       </c>
       <c r="B32" t="str">
-        <v>Knitting for Olive</v>
+        <v>Gepard</v>
       </c>
       <c r="C32" t="str">
-        <v>Cotton Merino</v>
+        <v>Kid Silk 5</v>
       </c>
       <c r="D32" t="str">
         <v/>
       </c>
       <c r="E32" t="str">
-        <v>bomuld/merino</v>
+        <v>Kid mohair</v>
       </c>
       <c r="F32" t="str">
-        <v>fingering</v>
+        <v>lace</v>
       </c>
       <c r="G32">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H32">
         <v>500</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="L32">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N32" t="str">
-        <v/>
+        <v>Brushed single, kid mohair med silke, langfibret og kraftig halo</v>
       </c>
       <c r="O32" t="str">
         <v/>
       </c>
       <c r="P32" t="str">
-        <v/>
+        <v>brushed_singles</v>
       </c>
       <c r="Q32" t="str">
-        <v/>
+        <v>brushed</v>
       </c>
       <c r="R32" t="str">
         <v>handvask</v>
       </c>
       <c r="S32" t="str">
-        <v/>
+        <v>Sydafrika</v>
       </c>
       <c r="T32" t="str">
-        <v/>
+        <v>Sydafrika</v>
       </c>
       <c r="U32" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V32" t="str">
-        <v>["Oeko-Tex Standard 100 (Class 1)","RWS","OCS"]</v>
+        <v>[]</v>
       </c>
       <c r="W32" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X32" t="str">
-        <v/>
+        <v>["lette mohairbluser","oversize sweatre","sjaler","holdtråd"]</v>
       </c>
       <c r="Y32" t="str">
-        <v/>
+        <v>Bliver løs i det med en tråd og dyr, hvis man skal strikke med 2 tråde</v>
       </c>
       <c r="Z32" t="str">
         <v/>
       </c>
       <c r="AA32" t="str">
-        <v>[{"fiber":"bomuld","percentage":70},{"fiber":"merinould","percentage":30}]</v>
+        <v>[{"fiber":"kid_mohair","percentage":80},{"fiber":"silke","percentage":20}]</v>
       </c>
     </row>
     <row r="33">
@@ -3066,37 +3066,37 @@
         <v/>
       </c>
       <c r="B33" t="str">
-        <v>Knitting for Olive</v>
+        <v>Gepard</v>
       </c>
       <c r="C33" t="str">
-        <v>Heavy Merino</v>
+        <v>Puno</v>
       </c>
       <c r="D33" t="str">
         <v/>
       </c>
       <c r="E33" t="str">
-        <v>merino</v>
+        <v>alpaka/merino/nylon</v>
       </c>
       <c r="F33" t="str">
-        <v>worsted</v>
+        <v>bulky</v>
       </c>
       <c r="G33">
         <v>50</v>
       </c>
       <c r="H33">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="I33">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J33">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>18</v>
-      </c>
-      <c r="L33">
-        <v>26</v>
+        <v>12.5</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -3117,16 +3117,16 @@
         <v>handvask</v>
       </c>
       <c r="S33" t="str">
-        <v>Italien</v>
+        <v/>
       </c>
       <c r="T33" t="str">
-        <v>New Zealand</v>
+        <v/>
       </c>
       <c r="U33" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V33" t="str">
-        <v>["Oeko-Tex Standard 100"]</v>
+        <v>["RAS","RWS"]</v>
       </c>
       <c r="W33" t="str">
         <v/>
@@ -3141,60 +3141,60 @@
         <v/>
       </c>
       <c r="AA33" t="str">
-        <v>[{"fiber":"merinould","percentage":100}]</v>
+        <v>[{"fiber":"baby_alpaka","percentage":68},{"fiber":"merinould","percentage":10},{"fiber":"nylon_polyamid","percentage":22}]</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>b947e987-4132-4898-9578-e4039e8e70fa</v>
+        <v/>
       </c>
       <c r="B34" t="str">
-        <v>Knitting for Olive</v>
+        <v>HipKnitShop</v>
       </c>
       <c r="C34" t="str">
-        <v>Merino</v>
+        <v>Wild</v>
       </c>
       <c r="D34" t="str">
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>Merinould</v>
+        <v>alpaka/uld/polyamid</v>
       </c>
       <c r="F34" t="str">
-        <v>fingering</v>
+        <v>bulky</v>
       </c>
       <c r="G34">
         <v>50</v>
       </c>
       <c r="H34">
-        <v>500</v>
+        <v>202</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>28</v>
-      </c>
-      <c r="L34">
-        <v>38</v>
+        <v>12</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
       </c>
       <c r="M34">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N34" t="str">
-        <v>4-trådet plied, non-superwash merino, blød og mulesing-fri</v>
-      </c>
-      <c r="O34">
-        <v>4</v>
+        <v>børstet eyelash-effekt</v>
+      </c>
+      <c r="O34" t="str">
+        <v/>
       </c>
       <c r="P34" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q34" t="str">
-        <v>standard</v>
+        <v>brushed</v>
       </c>
       <c r="R34" t="str">
         <v>handvask</v>
@@ -3203,87 +3203,87 @@
         <v>Italien</v>
       </c>
       <c r="T34" t="str">
-        <v>Patagonia</v>
+        <v/>
       </c>
       <c r="U34" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V34" t="str">
-        <v>["Oeko-Tex 100","RWS"]</v>
+        <v>[]</v>
       </c>
       <c r="W34" t="str">
-        <v>[]</v>
+        <v>["efterår", "vinter"]</v>
       </c>
       <c r="X34" t="str">
-        <v>["sweatre","sjaler","sokker","babytøj","tilbehør"]</v>
+        <v>["sweatre", "jakker", "kanter"]</v>
       </c>
       <c r="Y34" t="str">
-        <v>KFO's suverænt mest solgte garn og det mest profilerede bæredygtige garnmærke i Danmark. Non-superwash, mulesing-fri og OEKO-TEX certificeret. Smukt farvekort og meget brugt i baby- og børnestrik.</v>
+        <v>Bulky-vægt eyelash-garn fra norske HipKnitShop i 38% alpaka, 37% uld og 25% polyamid. Børstet overflade giver fluffy fnug — strikkes på pind 5-9 mm.</v>
       </c>
       <c r="Z34" t="str">
-        <v/>
+        <v>/garn-eksempler/hipknitshop-wild.jpg</v>
       </c>
       <c r="AA34" t="str">
-        <v>[{"fiber":"merinould","percentage":100}]</v>
+        <v>[{"fiber": "alpaka", "percentage": 38}, {"fiber": "uld", "percentage": 37}, {"fiber": "nylon_polyamid", "percentage": 25}]</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>aecaf848-1fd8-4117-8e93-51b9547ea2d1</v>
+        <v/>
       </c>
       <c r="B35" t="str">
-        <v>Knitting for Olive</v>
+        <v>HipKnitShop</v>
       </c>
       <c r="C35" t="str">
-        <v>Pure Silk</v>
+        <v>Pop</v>
       </c>
       <c r="D35" t="str">
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>Silke</v>
+        <v>merinould</v>
       </c>
       <c r="F35" t="str">
-        <v>sport</v>
+        <v>dk</v>
       </c>
       <c r="G35">
         <v>50</v>
       </c>
       <c r="H35">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="I35">
         <v>3</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="K35">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L35" t="str">
         <v/>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N35" t="str">
-        <v>Plied bourrette silke, medium twist, lidt rustik med synlige fiberender, mat finish</v>
+        <v/>
       </c>
       <c r="O35" t="str">
         <v/>
       </c>
       <c r="P35" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q35" t="str">
-        <v>standard</v>
+        <v/>
       </c>
       <c r="R35" t="str">
         <v>handvask</v>
       </c>
       <c r="S35" t="str">
-        <v/>
+        <v>Italien</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -3292,99 +3292,99 @@
         <v>i_produktion</v>
       </c>
       <c r="V35" t="str">
-        <v>["Oeko-Tex 100"]</v>
+        <v>[]</v>
       </c>
       <c r="W35" t="str">
-        <v>[]</v>
+        <v>["efterår", "vinter", "forår"]</v>
       </c>
       <c r="X35" t="str">
-        <v>["sommertopper","lette bluser","sjaler","holdtråd til mohair og merino"]</v>
+        <v>["sweatre", "cardigans", "babystrik"]</v>
       </c>
       <c r="Y35" t="str">
-        <v>Temperaturregulerende. Bourette silke giver mat finish frem for klassisk silkeglans.</v>
+        <v>DK-vægt i 100% extra fine merinould fra norske HipKnitShop. Blødt mod huden med god elasticitet — 50g/115m på pind 3-4,5 mm.</v>
       </c>
       <c r="Z35" t="str">
-        <v/>
+        <v>/garn-eksempler/hipknitshop-pop.jpg</v>
       </c>
       <c r="AA35" t="str">
-        <v>[{"fiber":"silke","percentage":100}]</v>
+        <v>[{"fiber": "merinould", "percentage": 100}]</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v/>
+        <v>33c79df9-c09b-4a41-8d83-6b00a7f1f33f</v>
       </c>
       <c r="B36" t="str">
-        <v>Lana Grossa</v>
+        <v>Hjertegarn</v>
       </c>
       <c r="C36" t="str">
-        <v>Cool Wool</v>
+        <v>Extrafine Merino 90</v>
       </c>
       <c r="D36" t="str">
         <v/>
       </c>
       <c r="E36" t="str">
-        <v>merino</v>
+        <v>Merinould</v>
       </c>
       <c r="F36" t="str">
-        <v>sport</v>
+        <v>aran</v>
       </c>
       <c r="G36">
         <v>50</v>
       </c>
       <c r="H36">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="I36">
+        <v>4.5</v>
+      </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
+      <c r="K36">
+        <v>18</v>
+      </c>
+      <c r="L36">
+        <v>28</v>
+      </c>
+      <c r="M36">
+        <v>4.5</v>
+      </c>
+      <c r="N36" t="str">
+        <v>3-trådet plied kamgarn, superwash merino, glat og blød</v>
+      </c>
+      <c r="O36">
         <v>3</v>
       </c>
-      <c r="J36">
-        <v>3.5</v>
-      </c>
-      <c r="K36">
-        <v>24</v>
-      </c>
-      <c r="L36">
-        <v>34</v>
-      </c>
-      <c r="M36" t="str">
-        <v/>
-      </c>
-      <c r="N36" t="str">
-        <v/>
-      </c>
-      <c r="O36" t="str">
-        <v/>
-      </c>
       <c r="P36" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q36" t="str">
-        <v/>
+        <v>superwash</v>
       </c>
       <c r="R36" t="str">
-        <v>maskinvask_30</v>
+        <v>maskinvask_40</v>
       </c>
       <c r="S36" t="str">
-        <v>Italien</v>
+        <v>Danmark</v>
       </c>
       <c r="T36" t="str">
-        <v>Australien</v>
+        <v>Sydamerika</v>
       </c>
       <c r="U36" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V36" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="W36" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X36" t="str">
-        <v/>
+        <v>["sweatre","huer","vanter","børnetøj","hverdagsstrik"]</v>
       </c>
       <c r="Y36" t="str">
-        <v/>
+        <v>Klassisk dansk storsælger fra Hjertegarn — bredt tilgængeligt i hele Danmark og meget prisvenligt. Superwash-behandlet merino i DK-tykkelse. Stor farvepalette og god kvalitet til hverdagsprojekter.</v>
       </c>
       <c r="Z36" t="str">
         <v/>
@@ -3395,61 +3395,61 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ee587b63-918e-4a50-a426-c847437fe059</v>
+        <v/>
       </c>
       <c r="B37" t="str">
-        <v>Lana Grossa</v>
+        <v>Holst Garn</v>
       </c>
       <c r="C37" t="str">
-        <v>Maglia</v>
+        <v>Coast</v>
       </c>
       <c r="D37" t="str">
         <v/>
       </c>
       <c r="E37" t="str">
-        <v>Bomuld-blanding</v>
+        <v>uld/bomuld</v>
       </c>
       <c r="F37" t="str">
-        <v>sport</v>
+        <v>fingering</v>
       </c>
       <c r="G37">
         <v>50</v>
       </c>
       <c r="H37">
-        <v>310</v>
+        <v>700</v>
       </c>
       <c r="I37">
+        <v>2.5</v>
+      </c>
+      <c r="J37">
         <v>3</v>
       </c>
-      <c r="J37">
-        <v>3.5</v>
-      </c>
       <c r="K37">
-        <v>24</v>
-      </c>
-      <c r="L37">
-        <v>32</v>
-      </c>
-      <c r="M37">
-        <v>3</v>
+        <v>26</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
       </c>
       <c r="N37" t="str">
-        <v>Bomuldsblanding med let polyester-stretch</v>
-      </c>
-      <c r="O37" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="O37">
+        <v>2</v>
       </c>
       <c r="P37" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q37" t="str">
-        <v>standard</v>
+        <v/>
       </c>
       <c r="R37" t="str">
         <v>maskinvask_30</v>
       </c>
       <c r="S37" t="str">
-        <v>Italien</v>
+        <v/>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -3458,22 +3458,22 @@
         <v>i_produktion</v>
       </c>
       <c r="V37" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="W37" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="X37" t="str">
-        <v>["sommerprojekter","toppe","babytøj","tørklæder"]</v>
+        <v/>
       </c>
       <c r="Y37" t="str">
-        <v>Bomuldsbaseret Lana Grossa-kvalitet med lille polyester-andel for form og styrke.</v>
+        <v/>
       </c>
       <c r="Z37" t="str">
         <v/>
       </c>
       <c r="AA37" t="str">
-        <v>[{"fiber":"bomuld","percentage":92},{"fiber":"polyester","percentage":8}]</v>
+        <v>[{"fiber":"merinould","percentage":55},{"fiber":"bomuld","percentage":45}]</v>
       </c>
     </row>
     <row r="38">
@@ -3481,16 +3481,16 @@
         <v/>
       </c>
       <c r="B38" t="str">
-        <v>Lang Yarns</v>
+        <v>Holst Garn</v>
       </c>
       <c r="C38" t="str">
-        <v>Jawoll</v>
+        <v>Supersoft</v>
       </c>
       <c r="D38" t="str">
-        <v>Superwash</v>
+        <v/>
       </c>
       <c r="E38" t="str">
-        <v>uld/nylon</v>
+        <v>merino/shetland</v>
       </c>
       <c r="F38" t="str">
         <v>fingering</v>
@@ -3499,19 +3499,19 @@
         <v>50</v>
       </c>
       <c r="H38">
-        <v>420</v>
+        <v>574</v>
       </c>
       <c r="I38">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J38">
         <v>3.5</v>
       </c>
       <c r="K38">
-        <v>30</v>
-      </c>
-      <c r="L38">
-        <v>41</v>
+        <v>25</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -3519,23 +3519,23 @@
       <c r="N38" t="str">
         <v/>
       </c>
-      <c r="O38" t="str">
-        <v/>
+      <c r="O38">
+        <v>2</v>
       </c>
       <c r="P38" t="str">
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>superwash</v>
+        <v/>
       </c>
       <c r="R38" t="str">
-        <v>maskinvask_40</v>
+        <v>maskinvask_30</v>
       </c>
       <c r="S38" t="str">
         <v/>
       </c>
       <c r="T38" t="str">
-        <v>Chile (Patagonia)</v>
+        <v/>
       </c>
       <c r="U38" t="str">
         <v>i_produktion</v>
@@ -3556,24 +3556,24 @@
         <v/>
       </c>
       <c r="AA38" t="str">
-        <v>[{"fiber":"uld","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
+        <v>[{"fiber":"merinould","percentage":50},{"fiber":"shetland_uld","percentage":50}]</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v/>
+        <v>17d7cfcb-747e-4518-ba88-6e611fecb111</v>
       </c>
       <c r="B39" t="str">
-        <v>Lang Yarns</v>
+        <v>Isager</v>
       </c>
       <c r="C39" t="str">
-        <v>Mille Colori Baby</v>
+        <v>Alpaca 2</v>
       </c>
       <c r="D39" t="str">
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>merino</v>
+        <v>Alpaka-blanding</v>
       </c>
       <c r="F39" t="str">
         <v>fingering</v>
@@ -3582,64 +3582,64 @@
         <v>50</v>
       </c>
       <c r="H39">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J39">
         <v>3.5</v>
       </c>
       <c r="K39">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L39">
-        <v>36</v>
-      </c>
-      <c r="M39" t="str">
-        <v/>
+        <v>30</v>
+      </c>
+      <c r="M39">
+        <v>3</v>
       </c>
       <c r="N39" t="str">
-        <v/>
-      </c>
-      <c r="O39" t="str">
-        <v/>
+        <v>2-trådet plied, alpaka-uldblanding, blød med let glans og god drapering</v>
+      </c>
+      <c r="O39">
+        <v>2</v>
       </c>
       <c r="P39" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q39" t="str">
-        <v>superwash</v>
+        <v>standard</v>
       </c>
       <c r="R39" t="str">
-        <v>maskinvask_40</v>
+        <v>handvask</v>
       </c>
       <c r="S39" t="str">
-        <v/>
+        <v>Peru</v>
       </c>
       <c r="T39" t="str">
-        <v>Australien</v>
+        <v>Peru</v>
       </c>
       <c r="U39" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V39" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="W39" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X39" t="str">
-        <v/>
+        <v>["sweatre","sjaler","cardigans","lette overtøj","tilbehør"]</v>
       </c>
       <c r="Y39" t="str">
-        <v/>
+        <v>Isagers mest populære garn og en dansk klassiker siden 1977. Blød alpaka-uldblanding med smuk farvepalet og god drapering. Ikke-superwash — bæredygtig og holdbar. Meget brugt i Isager og Helga Isager opskrifter.</v>
       </c>
       <c r="Z39" t="str">
         <v/>
       </c>
       <c r="AA39" t="str">
-        <v>[{"fiber":"merinould","percentage":100}]</v>
+        <v>[{"fiber":"alpaka","percentage":50},{"fiber":"uld","percentage":50}]</v>
       </c>
     </row>
     <row r="40">
@@ -3647,61 +3647,61 @@
         <v/>
       </c>
       <c r="B40" t="str">
-        <v>Manos del Uruguay</v>
+        <v>Isager</v>
       </c>
       <c r="C40" t="str">
-        <v>Alegria</v>
+        <v>Jensen Yarn</v>
       </c>
       <c r="D40" t="str">
         <v/>
       </c>
       <c r="E40" t="str">
-        <v>merino/nylon</v>
+        <v>uld</v>
       </c>
       <c r="F40" t="str">
-        <v>fingering</v>
+        <v>sport</v>
       </c>
       <c r="G40">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H40">
-        <v>425</v>
+        <v>250</v>
       </c>
       <c r="I40">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="J40">
         <v>3</v>
       </c>
       <c r="K40">
-        <v>29</v>
-      </c>
-      <c r="L40" t="str">
-        <v/>
-      </c>
-      <c r="M40" t="str">
-        <v/>
+        <v>22</v>
+      </c>
+      <c r="L40">
+        <v>28</v>
+      </c>
+      <c r="M40">
+        <v>3</v>
       </c>
       <c r="N40" t="str">
         <v/>
       </c>
-      <c r="O40" t="str">
-        <v/>
+      <c r="O40">
+        <v>3</v>
       </c>
       <c r="P40" t="str">
         <v/>
       </c>
       <c r="Q40" t="str">
-        <v>superwash</v>
+        <v/>
       </c>
       <c r="R40" t="str">
-        <v>maskinvask_40</v>
+        <v>handvask</v>
       </c>
       <c r="S40" t="str">
-        <v/>
+        <v>Danmark</v>
       </c>
       <c r="T40" t="str">
-        <v/>
+        <v>New Zealand (hvid), Europa (Gotland: grå/brun)</v>
       </c>
       <c r="U40" t="str">
         <v>i_produktion</v>
@@ -3722,7 +3722,7 @@
         <v/>
       </c>
       <c r="AA40" t="str">
-        <v>[{"fiber":"merinould","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
+        <v>[{"fiber":"uld","percentage":100}]</v>
       </c>
     </row>
     <row r="41">
@@ -3730,40 +3730,40 @@
         <v/>
       </c>
       <c r="B41" t="str">
-        <v>Manos del Uruguay</v>
+        <v>Isager</v>
       </c>
       <c r="C41" t="str">
-        <v>Serena</v>
+        <v>Silk Mohair</v>
       </c>
       <c r="D41" t="str">
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>alpaka/bomuld</v>
+        <v>mohair/silke</v>
       </c>
       <c r="F41" t="str">
-        <v>sport</v>
+        <v>lace</v>
       </c>
       <c r="G41">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H41">
-        <v>310</v>
+        <v>848</v>
       </c>
       <c r="I41">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>24</v>
-      </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="M41" t="str">
-        <v/>
+        <v>18</v>
+      </c>
+      <c r="L41">
+        <v>23</v>
+      </c>
+      <c r="M41">
+        <v>5</v>
       </c>
       <c r="N41" t="str">
         <v/>
@@ -3781,16 +3781,16 @@
         <v>handvask</v>
       </c>
       <c r="S41" t="str">
-        <v/>
+        <v>Italien</v>
       </c>
       <c r="T41" t="str">
-        <v>Peru (alpaka), bomuld: ukendt</v>
+        <v>Sydafrika (mohair), silke: ukendt</v>
       </c>
       <c r="U41" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V41" t="str">
-        <v/>
+        <v>["RMS"]</v>
       </c>
       <c r="W41" t="str">
         <v/>
@@ -3802,72 +3802,72 @@
         <v/>
       </c>
       <c r="Z41" t="str">
-        <v/>
+        <v>/garn-eksempler/isager-silk-mohair.jpg</v>
       </c>
       <c r="AA41" t="str">
-        <v>[{"fiber":"baby_alpaka","percentage":60},{"fiber":"bomuld","percentage":40}]</v>
+        <v>[{"fiber":"kid_mohair","percentage":75},{"fiber":"silke","percentage":25}]</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>5d2b4e49-fe99-492b-914c-5241e34e6e60</v>
+        <v>b61537a6-edb9-4e4f-b8ad-9778977a7861</v>
       </c>
       <c r="B42" t="str">
-        <v>Mayflower</v>
+        <v>Ístex</v>
       </c>
       <c r="C42" t="str">
-        <v>Easy Care Big</v>
+        <v>Álafosslopi</v>
       </c>
       <c r="D42" t="str">
-        <v/>
+        <v>Lopi</v>
       </c>
       <c r="E42" t="str">
-        <v>Merinould</v>
+        <v>Islandsk uld</v>
       </c>
       <c r="F42" t="str">
-        <v>aran</v>
+        <v>bulky</v>
       </c>
       <c r="G42">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H42">
-        <v>370</v>
+        <v>100</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="K42">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L42">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N42" t="str">
-        <v>6-trådet plied kamgarn, medium twist, glat overflade, superwash</v>
-      </c>
-      <c r="O42">
-        <v>6</v>
+        <v>Let twistet, kraftigt woolen-spun, to tråde løst snoet</v>
+      </c>
+      <c r="O42" t="str">
+        <v/>
       </c>
       <c r="P42" t="str">
         <v>plied</v>
       </c>
       <c r="Q42" t="str">
-        <v>superwash</v>
+        <v>standard</v>
       </c>
       <c r="R42" t="str">
-        <v>maskinvask_40</v>
+        <v>handvask</v>
       </c>
       <c r="S42" t="str">
-        <v/>
+        <v>Island</v>
       </c>
       <c r="T42" t="str">
-        <v>Sydamerika</v>
+        <v>Island</v>
       </c>
       <c r="U42" t="str">
         <v>i_produktion</v>
@@ -3879,78 +3879,78 @@
         <v>[]</v>
       </c>
       <c r="X42" t="str">
-        <v>["børnetøj","hverdagssweatre","huer","vanter","mønsterstrik"]</v>
+        <v>["lopapeysa","yoke-trøjer","jakker","udendørstøj"]</v>
       </c>
       <c r="Y42" t="str">
-        <v>Superwash-behandlet — kan maskinvaskes og tumbles. Bloomer mindre end ubehandlet uld og kan strække over tid.</v>
+        <v>Den klassiske lopapeysa-tykkelse. Kradser på bar hud, men blødgøres ved vask. Varm og vandafvisende.</v>
       </c>
       <c r="Z42" t="str">
         <v/>
       </c>
       <c r="AA42" t="str">
-        <v>[{"fiber":"merinould","percentage":100}]</v>
+        <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>3b16b2f3-c9b8-44e5-b542-485e9b9c9c44</v>
+        <v>c382bfc9-523d-42fd-b7dc-53a55b0ad805</v>
       </c>
       <c r="B43" t="str">
-        <v>Mayflower</v>
+        <v>Ístex</v>
       </c>
       <c r="C43" t="str">
-        <v>Nordia</v>
+        <v>Einband</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>Lopi</v>
       </c>
       <c r="E43" t="str">
-        <v>Uld-blanding</v>
+        <v>Islandsk uld</v>
       </c>
       <c r="F43" t="str">
-        <v>dk</v>
+        <v>lace</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H43">
-        <v>142</v>
+        <v>500</v>
       </c>
       <c r="I43">
+        <v>2.5</v>
+      </c>
+      <c r="J43">
         <v>3.5</v>
       </c>
-      <c r="J43">
-        <v>4</v>
-      </c>
       <c r="K43">
-        <v>19</v>
-      </c>
-      <c r="L43" t="str">
-        <v/>
+        <v>27</v>
+      </c>
+      <c r="L43">
+        <v>36</v>
       </c>
       <c r="M43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N43" t="str">
-        <v/>
-      </c>
-      <c r="O43" t="str">
-        <v/>
+        <v>1-trådet single, woolen-spun, let luftig</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
       </c>
       <c r="P43" t="str">
-        <v>plied</v>
+        <v>singles</v>
       </c>
       <c r="Q43" t="str">
-        <v>superwash</v>
+        <v>standard</v>
       </c>
       <c r="R43" t="str">
-        <v>maskinvask_30</v>
+        <v>handvask</v>
       </c>
       <c r="S43" t="str">
-        <v/>
+        <v>Island</v>
       </c>
       <c r="T43" t="str">
-        <v/>
+        <v>Island</v>
       </c>
       <c r="U43" t="str">
         <v>i_produktion</v>
@@ -3962,63 +3962,63 @@
         <v>[]</v>
       </c>
       <c r="X43" t="str">
-        <v>[]</v>
+        <v>["sjaler","lace","holdtråd","islandske mønstre"]</v>
       </c>
       <c r="Y43" t="str">
-        <v/>
+        <v>Singles-garn med karakteristisk islandsk tovhet. God til sjaler og som holdtråd.</v>
       </c>
       <c r="Z43" t="str">
         <v/>
       </c>
       <c r="AA43" t="str">
-        <v>[{"fiber":"uld","percentage":51},{"fiber":"acryl","percentage":34},{"fiber":"nylon_polyamid","percentage":15}]</v>
+        <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>a5b59189-9d7a-4b1c-a4fd-7735366e6090</v>
+        <v>68558e71-4c6b-4f9c-b5fd-e884cbbc4cbe</v>
       </c>
       <c r="B44" t="str">
-        <v>Navia</v>
+        <v>Ístex</v>
       </c>
       <c r="C44" t="str">
-        <v>Trio</v>
+        <v>Léttlopi</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>Lopi</v>
       </c>
       <c r="E44" t="str">
-        <v>Uld</v>
+        <v>Islandsk uld</v>
       </c>
       <c r="F44" t="str">
-        <v>dk</v>
+        <v>aran</v>
       </c>
       <c r="G44">
         <v>50</v>
       </c>
       <c r="H44">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="I44">
         <v>4.5</v>
       </c>
       <c r="J44">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="K44">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L44">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M44">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N44" t="str">
-        <v>3-trådet plied, klassisk worsted-spun, medium twist, lidt rustik overflade</v>
+        <v>2-trådet woolen-spun, lettere og blødere end Álafosslopi</v>
       </c>
       <c r="O44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P44" t="str">
         <v>plied</v>
@@ -4030,10 +4030,10 @@
         <v>handvask</v>
       </c>
       <c r="S44" t="str">
-        <v>Færøerne</v>
+        <v>Island</v>
       </c>
       <c r="T44" t="str">
-        <v>Færøerne</v>
+        <v>Island</v>
       </c>
       <c r="U44" t="str">
         <v>i_produktion</v>
@@ -4045,66 +4045,66 @@
         <v>[]</v>
       </c>
       <c r="X44" t="str">
-        <v>["tykke sweatre","jakker","vanter","huer","fair isle","lopapeysa-stil"]</v>
+        <v>["lopapeysa","yoke-sweatre","huer","vanter","børnetrøjer"]</v>
       </c>
       <c r="Y44" t="str">
-        <v>Ubehandlet færøsk uld. Filter hvis behandlet forkert.</v>
+        <v>Light-version af Álafosslopi — halv vægt, halv tykkelse. Mest populære Lopi-kvalitet til moderne lopapeysa.</v>
       </c>
       <c r="Z44" t="str">
         <v/>
       </c>
       <c r="AA44" t="str">
-        <v>[{"fiber":"uld","percentage":100}]</v>
+        <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>c2e8f4a1-3d7b-4c91-b5e2-9f1a6d4e83c0</v>
+        <v>29fbd725-e5c6-4f97-88d7-0cc0b6e91e57</v>
       </c>
       <c r="B45" t="str">
-        <v>Permin</v>
+        <v>Ístex</v>
       </c>
       <c r="C45" t="str">
-        <v>Bella</v>
+        <v>Plötulopi</v>
       </c>
       <c r="D45" t="str">
-        <v>by Permin</v>
+        <v>Lopi</v>
       </c>
       <c r="E45" t="str">
-        <v>Kid mohair-blanding</v>
+        <v>Islandsk uld</v>
       </c>
       <c r="F45" t="str">
-        <v>bulky</v>
+        <v>unspun</v>
       </c>
       <c r="G45">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H45">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="K45">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L45">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N45" t="str">
-        <v>Brushed mohair-blanding med langt halo</v>
+        <v>Uspundet plate — skrøbelig tråd, skal håndteres varsomt</v>
       </c>
       <c r="O45" t="str">
         <v/>
       </c>
       <c r="P45" t="str">
-        <v/>
+        <v>unspun</v>
       </c>
       <c r="Q45" t="str">
         <v>standard</v>
@@ -4113,10 +4113,10 @@
         <v>handvask</v>
       </c>
       <c r="S45" t="str">
-        <v/>
+        <v>Island</v>
       </c>
       <c r="T45" t="str">
-        <v/>
+        <v>Island</v>
       </c>
       <c r="U45" t="str">
         <v>i_produktion</v>
@@ -4128,78 +4128,78 @@
         <v>[]</v>
       </c>
       <c r="X45" t="str">
-        <v>[]</v>
+        <v>["lopapeysa","yoke-trøjer","let og luftig strik"]</v>
       </c>
       <c r="Y45" t="str">
-        <v/>
+        <v>Kommer i runde plader à ca. 100 g. Kan holdes 2-3 tråde sammen for tykkere strik.</v>
       </c>
       <c r="Z45" t="str">
-        <v>/garn-eksempler/permin-bella.jpg</v>
+        <v/>
       </c>
       <c r="AA45" t="str">
-        <v/>
+        <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>87699410-92dc-4d28-b711-a23bfad2cb6d</v>
+        <v/>
       </c>
       <c r="B46" t="str">
-        <v>Permin</v>
+        <v>KAOS Yarn</v>
       </c>
       <c r="C46" t="str">
-        <v>Bella Color</v>
+        <v>Fine Andean Wool</v>
       </c>
       <c r="D46" t="str">
-        <v>Bella Color by Permin</v>
+        <v/>
       </c>
       <c r="E46" t="str">
-        <v>Kid mohair-blanding</v>
+        <v>uld</v>
       </c>
       <c r="F46" t="str">
-        <v>bulky</v>
+        <v>fingering</v>
       </c>
       <c r="G46">
         <v>50</v>
       </c>
       <c r="H46">
-        <v>290</v>
+        <v>450</v>
       </c>
       <c r="I46">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="J46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K46">
-        <v>14</v>
-      </c>
-      <c r="L46">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
       </c>
       <c r="M46">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="str">
-        <v>Brushed mohair-blanding med langt halo</v>
+        <v/>
       </c>
       <c r="O46" t="str">
         <v/>
       </c>
       <c r="P46" t="str">
-        <v>brushed_singles</v>
+        <v/>
       </c>
       <c r="Q46" t="str">
-        <v>brushed</v>
+        <v/>
       </c>
       <c r="R46" t="str">
         <v>handvask</v>
       </c>
       <c r="S46" t="str">
-        <v>Italien</v>
+        <v>Peru</v>
       </c>
       <c r="T46" t="str">
-        <v/>
+        <v>Peru</v>
       </c>
       <c r="U46" t="str">
         <v>i_produktion</v>
@@ -4208,81 +4208,81 @@
         <v>[]</v>
       </c>
       <c r="W46" t="str">
-        <v>[]</v>
+        <v>["forår", "efterår", "vinter"]</v>
       </c>
       <c r="X46" t="str">
-        <v>["store sweatre","kjoler","tørklæder","sjaler"]</v>
+        <v>["bluser", "cardigans", "tilbehør"]</v>
       </c>
       <c r="Y46" t="str">
-        <v>Mohair-klassiker fra Permin. Langfibret halo, let og varm. Stort pind-interval.</v>
+        <v>Fingering-vægt i 100% peruviansk højlandsuld fra KAOS Yarn — naturlig krydsning af lokale får × Corriedale, 3000m over havet. Spundet på fair-trade-certificeret familiemølle i Peru.</v>
       </c>
       <c r="Z46" t="str">
-        <v>/garn-eksempler/permin-bella-color.jpg</v>
+        <v>/garn-eksempler/kaos-yarn-fine-andean-wool.jpg</v>
       </c>
       <c r="AA46" t="str">
-        <v>[{"fiber":"kid_mohair","percentage":75},{"fiber":"uld","percentage":20},{"fiber":"nylon_polyamid","percentage":5}]</v>
+        <v>[{"fiber": "uld", "percentage": 100}]</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>7839f1ad-bed5-4b8e-9be1-18a79709c53c</v>
+        <v/>
       </c>
       <c r="B47" t="str">
-        <v>Permin</v>
+        <v>KAOS Yarn</v>
       </c>
       <c r="C47" t="str">
-        <v>Hannah</v>
+        <v>Chunky Andean Wool</v>
       </c>
       <c r="D47" t="str">
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>Merinould-blanding</v>
+        <v>uld</v>
       </c>
       <c r="F47" t="str">
-        <v>lace</v>
+        <v>bulky</v>
       </c>
       <c r="G47">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H47">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="I47">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K47">
-        <v>28</v>
-      </c>
-      <c r="L47">
-        <v>46</v>
+        <v>16</v>
+      </c>
+      <c r="L47" t="str">
+        <v/>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N47" t="str">
-        <v>Brushed, silkekerne med uld/cashmere spundet udenom — let halo</v>
+        <v/>
       </c>
       <c r="O47" t="str">
         <v/>
       </c>
       <c r="P47" t="str">
-        <v>brushed_singles</v>
+        <v>singles</v>
       </c>
       <c r="Q47" t="str">
-        <v>brushed</v>
+        <v/>
       </c>
       <c r="R47" t="str">
         <v>handvask</v>
       </c>
       <c r="S47" t="str">
-        <v>Italien</v>
+        <v>Peru</v>
       </c>
       <c r="T47" t="str">
-        <v/>
+        <v>Peru</v>
       </c>
       <c r="U47" t="str">
         <v>i_produktion</v>
@@ -4291,19 +4291,19 @@
         <v>[]</v>
       </c>
       <c r="W47" t="str">
-        <v>[]</v>
+        <v>["efterår", "vinter"]</v>
       </c>
       <c r="X47" t="str">
-        <v>["sjaler","tørklæder","holdtråd","babygaver"]</v>
+        <v>["tykke sweatre", "jakker", "tæpper", "huer"]</v>
       </c>
       <c r="Y47" t="str">
-        <v>Følgetråd sammen med andre for blødhed og brushed effekt</v>
+        <v>Tyk single-spun udgave af Andean Wool i 100% peruviansk højlandsuld. Strikkes hurtigt på pind 5-8 mm — godt valg til oversize sweatre og statement-strik.</v>
       </c>
       <c r="Z47" t="str">
-        <v>/garn-eksempler/permin-hannah.jpg</v>
+        <v>/garn-eksempler/kaos-yarn-chunky-andean-wool.jpg</v>
       </c>
       <c r="AA47" t="str">
-        <v>[{"fiber":"merinould","percentage":50},{"fiber":"silke","percentage":30},{"fiber":"kashmir","percentage":20}]</v>
+        <v>[{"fiber": "uld", "percentage": 100}]</v>
       </c>
     </row>
     <row r="48">
@@ -4311,10 +4311,10 @@
         <v/>
       </c>
       <c r="B48" t="str">
-        <v>Rauma Garn</v>
+        <v>KAOS Yarn</v>
       </c>
       <c r="C48" t="str">
-        <v>Finull</v>
+        <v>Skinny Andean Wool</v>
       </c>
       <c r="D48" t="str">
         <v/>
@@ -4329,28 +4329,28 @@
         <v>50</v>
       </c>
       <c r="H48">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J48">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="K48">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L48" t="str">
         <v/>
       </c>
-      <c r="M48" t="str">
-        <v/>
+      <c r="M48">
+        <v>4.5</v>
       </c>
       <c r="N48" t="str">
         <v/>
       </c>
-      <c r="O48">
-        <v>2</v>
+      <c r="O48" t="str">
+        <v/>
       </c>
       <c r="P48" t="str">
         <v/>
@@ -4359,161 +4359,161 @@
         <v/>
       </c>
       <c r="R48" t="str">
-        <v>maskinvask_30</v>
+        <v>handvask</v>
       </c>
       <c r="S48" t="str">
-        <v>Norge</v>
+        <v>Peru</v>
       </c>
       <c r="T48" t="str">
-        <v>Norge</v>
+        <v>Peru</v>
       </c>
       <c r="U48" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V48" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="W48" t="str">
-        <v/>
+        <v>["forår", "efterår", "vinter"]</v>
       </c>
       <c r="X48" t="str">
-        <v/>
+        <v>["sweatre", "cardigans", "tilbehør"]</v>
       </c>
       <c r="Y48" t="str">
-        <v/>
+        <v>Sport-vægt i 100% peruviansk højlandsuld — naturlig krydsning af lokale får × Corriedale, fra fair-trade-mølle. Rustik karakter, holder formen godt på pind 4-5,5 mm.</v>
       </c>
       <c r="Z48" t="str">
-        <v/>
+        <v>/garn-eksempler/kaos-yarn-skinny-andean-wool.jpg</v>
       </c>
       <c r="AA48" t="str">
-        <v>[{"fiber":"uld","percentage":100}]</v>
+        <v>[{"fiber": "uld", "percentage": 100}]</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>5775ac2a-7b97-4858-a2cc-f9a9df63dee8</v>
+        <v/>
       </c>
       <c r="B49" t="str">
-        <v>Rauma Garn</v>
+        <v>Knitting for Olive</v>
       </c>
       <c r="C49" t="str">
-        <v>Vams</v>
+        <v>Cotton Merino</v>
       </c>
       <c r="D49" t="str">
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>Uld</v>
+        <v>bomuld/merino</v>
       </c>
       <c r="F49" t="str">
-        <v>aran</v>
+        <v>fingering</v>
       </c>
       <c r="G49">
         <v>50</v>
       </c>
       <c r="H49">
-        <v>166</v>
+        <v>500</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J49">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K49">
-        <v>15</v>
-      </c>
-      <c r="L49" t="str">
-        <v/>
+        <v>28</v>
+      </c>
+      <c r="L49">
+        <v>38</v>
       </c>
       <c r="M49">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="N49" t="str">
-        <v>Kardegarn (woolen-spun), single, blød twist, luftig og let filtbar</v>
+        <v/>
       </c>
       <c r="O49" t="str">
         <v/>
       </c>
       <c r="P49" t="str">
-        <v>singles</v>
+        <v/>
       </c>
       <c r="Q49" t="str">
-        <v>standard</v>
+        <v/>
       </c>
       <c r="R49" t="str">
         <v>handvask</v>
       </c>
       <c r="S49" t="str">
-        <v>Norge</v>
+        <v/>
       </c>
       <c r="T49" t="str">
-        <v>Norge</v>
+        <v/>
       </c>
       <c r="U49" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V49" t="str">
-        <v>[]</v>
+        <v>["Oeko-Tex Standard 100 (Class 1)","RWS","OCS"]</v>
       </c>
       <c r="W49" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="X49" t="str">
-        <v>["tykke sweatre","jakker","vanter","tæpper","toveprojekter"]</v>
+        <v/>
       </c>
       <c r="Y49" t="str">
-        <v>Kardegarn = kartet ulden er på kryds og tværs, hvilket giver et luftigt, blødt rustikt garn der bloomer kraftigt ved vask.</v>
+        <v/>
       </c>
       <c r="Z49" t="str">
         <v/>
       </c>
       <c r="AA49" t="str">
-        <v>[{"fiber":"uld","percentage":100}]</v>
+        <v>[{"fiber":"bomuld","percentage":70},{"fiber":"merinould","percentage":30}]</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bce5c06c-a587-47e4-a824-5d3de89c05d7</v>
+        <v/>
       </c>
       <c r="B50" t="str">
-        <v>Rico Design</v>
+        <v>Knitting for Olive</v>
       </c>
       <c r="C50" t="str">
-        <v>Creative Make It Blümchen</v>
+        <v>Heavy Merino</v>
       </c>
       <c r="D50" t="str">
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>Lyocell</v>
+        <v>merino</v>
       </c>
       <c r="F50" t="str">
-        <v>lace</v>
+        <v>worsted</v>
       </c>
       <c r="G50">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H50">
-        <v>1500</v>
-      </c>
-      <c r="I50" t="str">
-        <v/>
-      </c>
-      <c r="J50" t="str">
-        <v/>
-      </c>
-      <c r="K50" t="str">
-        <v/>
-      </c>
-      <c r="L50" t="str">
-        <v/>
+        <v>250</v>
+      </c>
+      <c r="I50">
+        <v>4.5</v>
+      </c>
+      <c r="J50">
+        <v>4.5</v>
+      </c>
+      <c r="K50">
+        <v>18</v>
+      </c>
+      <c r="L50">
+        <v>26</v>
       </c>
       <c r="M50" t="str">
         <v/>
       </c>
       <c r="N50" t="str">
-        <v>Tråd med applikerede tekstil-blomster langs tråden (effektgarn)</v>
+        <v/>
       </c>
       <c r="O50" t="str">
         <v/>
@@ -4522,164 +4522,164 @@
         <v/>
       </c>
       <c r="Q50" t="str">
-        <v>standard</v>
+        <v/>
       </c>
       <c r="R50" t="str">
         <v>handvask</v>
       </c>
       <c r="S50" t="str">
-        <v>Tyskland</v>
+        <v>Italien</v>
       </c>
       <c r="T50" t="str">
-        <v/>
+        <v>New Zealand</v>
       </c>
       <c r="U50" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V50" t="str">
-        <v>[]</v>
+        <v>["Oeko-Tex Standard 100"]</v>
       </c>
       <c r="W50" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="X50" t="str">
-        <v>["børnehuer","dekorative projekter","amigurumi-detaljer"]</v>
+        <v/>
       </c>
       <c r="Y50" t="str">
-        <v>USIKKER — bekræft producent og specs på banderolen.</v>
+        <v/>
       </c>
       <c r="Z50" t="str">
         <v/>
       </c>
       <c r="AA50" t="str">
-        <v/>
+        <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>953a7d29-d932-4334-a9ca-6403f4db7c28</v>
+        <v>b947e987-4132-4898-9578-e4039e8e70fa</v>
       </c>
       <c r="B51" t="str">
-        <v>Rosários 4</v>
+        <v>Knitting for Olive</v>
       </c>
       <c r="C51" t="str">
-        <v>Paillettes Classic Collection</v>
+        <v>Merino</v>
       </c>
       <c r="D51" t="str">
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>Polyester</v>
+        <v>Merinould</v>
       </c>
       <c r="F51" t="str">
-        <v>lace</v>
+        <v>fingering</v>
       </c>
       <c r="G51">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H51">
-        <v>548</v>
+        <v>500</v>
       </c>
       <c r="I51">
         <v>3</v>
       </c>
       <c r="J51">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K51">
         <v>28</v>
       </c>
-      <c r="L51" t="str">
-        <v/>
-      </c>
-      <c r="M51" t="str">
-        <v/>
+      <c r="L51">
+        <v>38</v>
+      </c>
+      <c r="M51">
+        <v>3</v>
       </c>
       <c r="N51" t="str">
-        <v>Tråd med indspundne/påsyede pailletter — effektgarn</v>
-      </c>
-      <c r="O51" t="str">
-        <v/>
+        <v>4-trådet plied, non-superwash merino, blød og mulesing-fri</v>
+      </c>
+      <c r="O51">
+        <v>4</v>
       </c>
       <c r="P51" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q51" t="str">
         <v>standard</v>
       </c>
       <c r="R51" t="str">
-        <v>maskinvask_30</v>
+        <v>handvask</v>
       </c>
       <c r="S51" t="str">
-        <v>Portugal</v>
+        <v>Italien</v>
       </c>
       <c r="T51" t="str">
-        <v/>
+        <v>Patagonia</v>
       </c>
       <c r="U51" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V51" t="str">
-        <v>[]</v>
+        <v>["Oeko-Tex 100","RWS"]</v>
       </c>
       <c r="W51" t="str">
         <v>[]</v>
       </c>
       <c r="X51" t="str">
-        <v>["fest-projekter","holdtråd","aftentoppe"]</v>
+        <v>["sweatre","sjaler","sokker","babytøj","tilbehør"]</v>
       </c>
       <c r="Y51" t="str">
-        <v>USIKKER — Rosários 4 har flere pailletgarn-serier. Bør verificeres på banderolen.</v>
+        <v>KFO's suverænt mest solgte garn og det mest profilerede bæredygtige garnmærke i Danmark. Non-superwash, mulesing-fri og OEKO-TEX certificeret. Smukt farvekort og meget brugt i baby- og børnestrik.</v>
       </c>
       <c r="Z51" t="str">
         <v/>
       </c>
       <c r="AA51" t="str">
-        <v/>
+        <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>d73ecbc9-ecf6-4a05-8fcc-6719640cd6b7</v>
+        <v>aecaf848-1fd8-4117-8e93-51b9547ea2d1</v>
       </c>
       <c r="B52" t="str">
-        <v>Sandnes Garn</v>
+        <v>Knitting for Olive</v>
       </c>
       <c r="C52" t="str">
-        <v>Kitten Mohair</v>
+        <v>Pure Silk</v>
       </c>
       <c r="D52" t="str">
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>Mohair-blanding</v>
+        <v>Silke</v>
       </c>
       <c r="F52" t="str">
-        <v>dk</v>
+        <v>sport</v>
       </c>
       <c r="G52">
         <v>50</v>
       </c>
       <c r="H52">
-        <v>326</v>
+        <v>500</v>
       </c>
       <c r="I52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52">
-        <v>19</v>
-      </c>
-      <c r="L52">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N52" t="str">
-        <v>Plied DK-mohair-blend, let halo, blødt</v>
+        <v>Plied bourrette silke, medium twist, lidt rustik med synlige fiberender, mat finish</v>
       </c>
       <c r="O52" t="str">
         <v/>
@@ -4694,7 +4694,7 @@
         <v>handvask</v>
       </c>
       <c r="S52" t="str">
-        <v>Norge</v>
+        <v/>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -4703,22 +4703,22 @@
         <v>i_produktion</v>
       </c>
       <c r="V52" t="str">
-        <v>[]</v>
+        <v>["Oeko-Tex 100"]</v>
       </c>
       <c r="W52" t="str">
         <v>[]</v>
       </c>
       <c r="X52" t="str">
-        <v>["hverdagshuer","vanter","vintertilbehør","retro-projekter"]</v>
+        <v>["sommertopper","lette bluser","sjaler","holdtråd til mohair og merino"]</v>
       </c>
       <c r="Y52" t="str">
-        <v>80er/90er-stilstrik. Akrylindholdet gør den mere robust og mindre elegant — ikke et luksusgarn til lette overdele.</v>
+        <v>Temperaturregulerende. Bourette silke giver mat finish frem for klassisk silkeglans.</v>
       </c>
       <c r="Z52" t="str">
-        <v/>
+        <v>/garn-eksempler/knitting-for-olive-pure-silk.jpg</v>
       </c>
       <c r="AA52" t="str">
-        <v>[{"fiber":"courtelle","percentage":50},{"fiber":"mohair","percentage":30},{"fiber":"uld","percentage":20}]</v>
+        <v>[{"fiber":"silke","percentage":100}]</v>
       </c>
     </row>
     <row r="53">
@@ -4726,37 +4726,37 @@
         <v/>
       </c>
       <c r="B53" t="str">
-        <v>Sandnes Garn</v>
+        <v>Lana Grossa</v>
       </c>
       <c r="C53" t="str">
-        <v>Kos</v>
+        <v>Cool Wool</v>
       </c>
       <c r="D53" t="str">
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>alpaka/uld/nylon</v>
+        <v>merino</v>
       </c>
       <c r="F53" t="str">
-        <v>aran</v>
+        <v>sport</v>
       </c>
       <c r="G53">
         <v>50</v>
       </c>
       <c r="H53">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="I53">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J53">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="K53">
-        <v>17</v>
-      </c>
-      <c r="L53" t="str">
-        <v/>
+        <v>24</v>
+      </c>
+      <c r="L53">
+        <v>34</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -4777,10 +4777,10 @@
         <v>maskinvask_30</v>
       </c>
       <c r="S53" t="str">
-        <v/>
+        <v>Italien</v>
       </c>
       <c r="T53" t="str">
-        <v>Uruguay (uld), Peru (alpaka)</v>
+        <v>Australien</v>
       </c>
       <c r="U53" t="str">
         <v>i_produktion</v>
@@ -4801,107 +4801,107 @@
         <v/>
       </c>
       <c r="AA53" t="str">
-        <v>[{"fiber":"alpaka","percentage":62},{"fiber":"nylon_polyamid","percentage":29},{"fiber":"uld","percentage":9}]</v>
+        <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v/>
+        <v>ee587b63-918e-4a50-a426-c847437fe059</v>
       </c>
       <c r="B54" t="str">
-        <v>Sandnes Garn</v>
+        <v>Lana Grossa</v>
       </c>
       <c r="C54" t="str">
-        <v>Line</v>
+        <v>Maglia</v>
       </c>
       <c r="D54" t="str">
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>bomuld/viskose/lin</v>
+        <v>Bomuld-blanding</v>
       </c>
       <c r="F54" t="str">
-        <v>dk</v>
+        <v>sport</v>
       </c>
       <c r="G54">
         <v>50</v>
       </c>
       <c r="H54">
-        <v>220</v>
+        <v>310</v>
       </c>
       <c r="I54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J54">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K54">
-        <v>20</v>
-      </c>
-      <c r="L54" t="str">
-        <v/>
-      </c>
-      <c r="M54" t="str">
-        <v/>
+        <v>24</v>
+      </c>
+      <c r="L54">
+        <v>32</v>
+      </c>
+      <c r="M54">
+        <v>3</v>
       </c>
       <c r="N54" t="str">
-        <v/>
+        <v>Bomuldsblanding med let polyester-stretch</v>
       </c>
       <c r="O54" t="str">
         <v/>
       </c>
       <c r="P54" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q54" t="str">
-        <v/>
+        <v>standard</v>
       </c>
       <c r="R54" t="str">
         <v>maskinvask_30</v>
       </c>
       <c r="S54" t="str">
-        <v/>
+        <v>Italien</v>
       </c>
       <c r="T54" t="str">
-        <v>Indien</v>
+        <v/>
       </c>
       <c r="U54" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V54" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="W54" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X54" t="str">
-        <v/>
+        <v>["sommerprojekter","toppe","babytøj","tørklæder"]</v>
       </c>
       <c r="Y54" t="str">
-        <v/>
+        <v>Bomuldsbaseret Lana Grossa-kvalitet med lille polyester-andel for form og styrke.</v>
       </c>
       <c r="Z54" t="str">
-        <v/>
+        <v>/garn-eksempler/lana-grossa-maglia.jpg</v>
       </c>
       <c r="AA54" t="str">
-        <v>[{"fiber":"bomuld","percentage":53},{"fiber":"viskose","percentage":33},{"fiber":"lin","percentage":14}]</v>
+        <v>[{"fiber":"bomuld","percentage":92},{"fiber":"polyester","percentage":8}]</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>41e54067-9d9b-45a7-83f0-873ba436eaf3</v>
+        <v/>
       </c>
       <c r="B55" t="str">
-        <v>Sandnes Garn</v>
+        <v>Lana Grossa</v>
       </c>
       <c r="C55" t="str">
-        <v>Peer Gynt</v>
+        <v>Sommerseide</v>
       </c>
       <c r="D55" t="str">
-        <v/>
+        <v>Landlust</v>
       </c>
       <c r="E55" t="str">
-        <v>Uld</v>
+        <v>bomuld/silke</v>
       </c>
       <c r="F55" t="str">
         <v>dk</v>
@@ -4910,7 +4910,7 @@
         <v>50</v>
       </c>
       <c r="H55">
-        <v>182</v>
+        <v>340</v>
       </c>
       <c r="I55">
         <v>3.5</v>
@@ -4922,28 +4922,28 @@
         <v>22</v>
       </c>
       <c r="L55">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M55">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N55" t="str">
-        <v>3-trådet, klassisk plied</v>
-      </c>
-      <c r="O55">
-        <v>3</v>
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
       </c>
       <c r="P55" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q55" t="str">
-        <v>superwash</v>
+        <v/>
       </c>
       <c r="R55" t="str">
-        <v>maskinvask_30</v>
+        <v>handvask</v>
       </c>
       <c r="S55" t="str">
-        <v>Norge</v>
+        <v>Italien</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -4955,119 +4955,119 @@
         <v>[]</v>
       </c>
       <c r="W55" t="str">
-        <v>[]</v>
+        <v>["forår", "sommer"]</v>
       </c>
       <c r="X55" t="str">
-        <v>["huer","vanter","sweatre","børnetøj"]</v>
+        <v>["sommerbluser", "lette sjaler", "toppe"]</v>
       </c>
       <c r="Y55" t="str">
-        <v>Nordisk klassiker. Bredt farveudvalg. Meget brugt i PetiteKnit-opskrifter.</v>
+        <v>DK-tykt sommergarn i 50% bomuld og 50% silke fra Lana Grossas Landlust-serie, udviklet i samarbejde med Landlust-magasinet. Silke giver glans og fald, bomulden svalhed — egnet til toppe og lette bluser.</v>
       </c>
       <c r="Z55" t="str">
-        <v/>
+        <v>/garn-eksempler/lana-grossa-sommerseide.jpg</v>
       </c>
       <c r="AA55" t="str">
-        <v>[{"fiber":"uld","percentage":100}]</v>
+        <v>[{"fiber": "bomuld", "percentage": 50}, {"fiber": "silke", "percentage": 50}]</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>55127529-cff3-4ec8-bb48-60d902d1cbda</v>
+        <v/>
       </c>
       <c r="B56" t="str">
-        <v>Sandnes Garn</v>
+        <v>Lang Yarns</v>
       </c>
       <c r="C56" t="str">
-        <v>Poppy</v>
+        <v>Jawoll</v>
       </c>
       <c r="D56" t="str">
-        <v/>
+        <v>Superwash</v>
       </c>
       <c r="E56" t="str">
-        <v>Bomuld</v>
+        <v>uld/nylon</v>
       </c>
       <c r="F56" t="str">
-        <v>dk</v>
+        <v>fingering</v>
       </c>
       <c r="G56">
         <v>50</v>
       </c>
       <c r="H56">
-        <v>210</v>
+        <v>420</v>
       </c>
       <c r="I56">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K56">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L56">
-        <v>28</v>
-      </c>
-      <c r="M56">
-        <v>4</v>
+        <v>41</v>
+      </c>
+      <c r="M56" t="str">
+        <v/>
       </c>
       <c r="N56" t="str">
-        <v>Flertrådet, blød kæmmet bomuld</v>
+        <v/>
       </c>
       <c r="O56" t="str">
         <v/>
       </c>
       <c r="P56" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q56" t="str">
-        <v>standard</v>
+        <v>superwash</v>
       </c>
       <c r="R56" t="str">
         <v>maskinvask_40</v>
       </c>
       <c r="S56" t="str">
-        <v>Norge</v>
+        <v/>
       </c>
       <c r="T56" t="str">
-        <v>Tyrkiet</v>
+        <v>Chile (Patagonia)</v>
       </c>
       <c r="U56" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V56" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="W56" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="X56" t="str">
-        <v>["sommertoppe","babytøj","tørklæder","hverdagsbomuld"]</v>
+        <v/>
       </c>
       <c r="Y56" t="str">
-        <v>Blød bomuld uden glans, hverdagsprojekter i DK.</v>
+        <v/>
       </c>
       <c r="Z56" t="str">
         <v/>
       </c>
       <c r="AA56" t="str">
-        <v>[{"fiber":"bomuld","percentage":100}]</v>
+        <v>[{"fiber":"uld","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>6f707938-0284-4d82-afab-72fbe185cb5b</v>
+        <v/>
       </c>
       <c r="B57" t="str">
-        <v>Sandnes Garn</v>
+        <v>Lang Yarns</v>
       </c>
       <c r="C57" t="str">
-        <v>Sunday</v>
+        <v>Mille Colori Baby</v>
       </c>
       <c r="D57" t="str">
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>Merinould</v>
+        <v>merino</v>
       </c>
       <c r="F57" t="str">
         <v>fingering</v>
@@ -5076,58 +5076,58 @@
         <v>50</v>
       </c>
       <c r="H57">
-        <v>470</v>
+        <v>380</v>
       </c>
       <c r="I57">
         <v>3</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K57">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L57">
-        <v>28</v>
-      </c>
-      <c r="M57">
-        <v>3</v>
+        <v>36</v>
+      </c>
+      <c r="M57" t="str">
+        <v/>
       </c>
       <c r="N57" t="str">
-        <v>3-trådet plied kamgarn, non-superwash merino, blød</v>
-      </c>
-      <c r="O57">
-        <v>3</v>
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
       </c>
       <c r="P57" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q57" t="str">
-        <v>standard</v>
+        <v>superwash</v>
       </c>
       <c r="R57" t="str">
-        <v>maskinvask_30</v>
+        <v>maskinvask_40</v>
       </c>
       <c r="S57" t="str">
-        <v>Norge</v>
+        <v/>
       </c>
       <c r="T57" t="str">
-        <v>Uruguay</v>
+        <v>Australien</v>
       </c>
       <c r="U57" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V57" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="W57" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="X57" t="str">
-        <v>["sweatre","cardigans","babytøj","huer","sjaler"]</v>
+        <v/>
       </c>
       <c r="Y57" t="str">
-        <v>Et af Sandnes' mest populære garner — ekstremt smukt farvekort med jordfarver og pasteller valgt i samarbejde med PetiteKnit. Non-superwash merino, meget blød. Bruges i mange af de mest downloadede opskrifter i Danmark.</v>
+        <v/>
       </c>
       <c r="Z57" t="str">
         <v/>
@@ -5138,64 +5138,64 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ed2c4d04-de90-4cfb-96fe-220123f18b56</v>
+        <v/>
       </c>
       <c r="B58" t="str">
-        <v>Sandnes Garn</v>
+        <v>Ligne Noire</v>
       </c>
       <c r="C58" t="str">
-        <v>Tynn Silk Mohair</v>
+        <v>Lurex</v>
       </c>
       <c r="D58" t="str">
         <v/>
       </c>
       <c r="E58" t="str">
-        <v>Kid mohair-blanding</v>
+        <v>metallic/polyester</v>
       </c>
       <c r="F58" t="str">
         <v>lace</v>
       </c>
-      <c r="G58">
-        <v>25</v>
-      </c>
-      <c r="H58">
-        <v>848</v>
-      </c>
-      <c r="I58">
-        <v>3</v>
-      </c>
-      <c r="J58">
-        <v>5</v>
-      </c>
-      <c r="K58">
-        <v>18</v>
-      </c>
-      <c r="L58">
-        <v>28</v>
-      </c>
-      <c r="M58">
-        <v>4</v>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
       </c>
       <c r="N58" t="str">
-        <v>Brushed single, angora-ged mohair med silkekerne, medium halo</v>
+        <v/>
       </c>
       <c r="O58" t="str">
         <v/>
       </c>
       <c r="P58" t="str">
-        <v>brushed_singles</v>
+        <v/>
       </c>
       <c r="Q58" t="str">
-        <v>brushed</v>
+        <v/>
       </c>
       <c r="R58" t="str">
-        <v>maskinvask_30</v>
+        <v>handvask</v>
       </c>
       <c r="S58" t="str">
-        <v>Norge</v>
+        <v/>
       </c>
       <c r="T58" t="str">
-        <v>Sydafrika</v>
+        <v/>
       </c>
       <c r="U58" t="str">
         <v>i_produktion</v>
@@ -5207,66 +5207,66 @@
         <v>[]</v>
       </c>
       <c r="X58" t="str">
-        <v>["holdtråd","lette bluser","sjaler","oversize sweatre"]</v>
+        <v>["effektgarn", "beilauf", "festtøj"]</v>
       </c>
       <c r="Y58" t="str">
-        <v>Meget populær silk mohair fra Sandnes — høj kvalitet, tåler maskinvask ved 30 grader (uldprogram), og bruges i mange gennemtestede opskrifter fra kendte strikkedesignere. Luksuriøs og luftig holdtråd.</v>
+        <v>Tynd metallisk lurex-tråd til beilauf. Strikkes sammen med uld eller mohair for at tilføre fint glimt — bruges typisk på cones.</v>
       </c>
       <c r="Z58" t="str">
-        <v/>
+        <v>/garn-eksempler/ligne-noire-lurex.jpg</v>
       </c>
       <c r="AA58" t="str">
-        <v>[{"fiber":"mohair","percentage":57},{"fiber":"silke","percentage":28},{"fiber":"uld","percentage":15}]</v>
+        <v>[{"fiber": "polyester", "percentage": 100}]</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>c31f243d-5f2e-47de-89a2-d9e5a80d63d9</v>
+        <v/>
       </c>
       <c r="B59" t="str">
-        <v>Schachenmayr</v>
+        <v>Manos del Uruguay</v>
       </c>
       <c r="C59" t="str">
-        <v>Regia 4-ply</v>
+        <v>Alegria</v>
       </c>
       <c r="D59" t="str">
-        <v>Regia</v>
+        <v/>
       </c>
       <c r="E59" t="str">
-        <v>Uld</v>
+        <v>merino/nylon</v>
       </c>
       <c r="F59" t="str">
         <v>fingering</v>
       </c>
       <c r="G59">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H59">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="I59">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="J59">
         <v>3</v>
       </c>
       <c r="K59">
-        <v>30</v>
-      </c>
-      <c r="L59">
-        <v>42</v>
-      </c>
-      <c r="M59">
-        <v>2.5</v>
+        <v>29</v>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
       </c>
       <c r="N59" t="str">
-        <v>4-trådet klassisk sokkegarn, superwash</v>
-      </c>
-      <c r="O59">
-        <v>4</v>
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
       </c>
       <c r="P59" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q59" t="str">
         <v>superwash</v>
@@ -5275,7 +5275,7 @@
         <v>maskinvask_40</v>
       </c>
       <c r="S59" t="str">
-        <v>Tyskland</v>
+        <v/>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -5284,22 +5284,22 @@
         <v>i_produktion</v>
       </c>
       <c r="V59" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="W59" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="X59" t="str">
-        <v>["sokker","vanter","slidstærkt hverdagsstrik"]</v>
+        <v/>
       </c>
       <c r="Y59" t="str">
-        <v>Tysk sokkegarn-klassiker. Enormt farveudvalg inkl. selvstribende.</v>
+        <v/>
       </c>
       <c r="Z59" t="str">
         <v/>
       </c>
       <c r="AA59" t="str">
-        <v>[{"fiber":"uld","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
+        <v>[{"fiber":"merinould","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
       </c>
     </row>
     <row r="60">
@@ -5307,16 +5307,16 @@
         <v/>
       </c>
       <c r="B60" t="str">
-        <v>Schoppel Wolle</v>
+        <v>Manos del Uruguay</v>
       </c>
       <c r="C60" t="str">
-        <v>Edition 3</v>
+        <v>Serena</v>
       </c>
       <c r="D60" t="str">
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>merino</v>
+        <v>alpaka/bomuld</v>
       </c>
       <c r="F60" t="str">
         <v>sport</v>
@@ -5325,16 +5325,16 @@
         <v>50</v>
       </c>
       <c r="H60">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I60">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J60">
-        <v>3.5</v>
-      </c>
-      <c r="K60" t="str">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="K60">
+        <v>24</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -5352,16 +5352,16 @@
         <v/>
       </c>
       <c r="Q60" t="str">
-        <v>superwash</v>
+        <v/>
       </c>
       <c r="R60" t="str">
-        <v>maskinvask_40</v>
+        <v>handvask</v>
       </c>
       <c r="S60" t="str">
         <v/>
       </c>
       <c r="T60" t="str">
-        <v/>
+        <v>Peru (alpaka), bomuld: ukendt</v>
       </c>
       <c r="U60" t="str">
         <v>i_produktion</v>
@@ -5382,57 +5382,57 @@
         <v/>
       </c>
       <c r="AA60" t="str">
-        <v>[{"fiber":"merinould","percentage":100}]</v>
+        <v>[{"fiber":"baby_alpaka","percentage":60},{"fiber":"bomuld","percentage":40}]</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>5d2b4e49-fe99-492b-914c-5241e34e6e60</v>
       </c>
       <c r="B61" t="str">
-        <v>Schoppel Wolle</v>
+        <v>Mayflower</v>
       </c>
       <c r="C61" t="str">
-        <v>Zauberball Stärke 6</v>
+        <v>Easy Care Big</v>
       </c>
       <c r="D61" t="str">
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>uld/nylon</v>
+        <v>Merinould</v>
       </c>
       <c r="F61" t="str">
-        <v>sport</v>
+        <v>aran</v>
       </c>
       <c r="G61">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H61">
-        <v>266.667</v>
+        <v>370</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J61">
-        <v>4</v>
-      </c>
-      <c r="K61" t="str">
-        <v/>
-      </c>
-      <c r="L61" t="str">
-        <v/>
-      </c>
-      <c r="M61" t="str">
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="K61">
+        <v>18</v>
+      </c>
+      <c r="L61">
+        <v>26</v>
+      </c>
+      <c r="M61">
+        <v>5</v>
       </c>
       <c r="N61" t="str">
-        <v/>
-      </c>
-      <c r="O61" t="str">
-        <v/>
+        <v>6-trådet plied kamgarn, medium twist, glat overflade, superwash</v>
+      </c>
+      <c r="O61">
+        <v>6</v>
       </c>
       <c r="P61" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q61" t="str">
         <v>superwash</v>
@@ -5444,84 +5444,84 @@
         <v/>
       </c>
       <c r="T61" t="str">
-        <v/>
+        <v>Sydamerika</v>
       </c>
       <c r="U61" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V61" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="W61" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X61" t="str">
-        <v/>
+        <v>["børnetøj","hverdagssweatre","huer","vanter","mønsterstrik"]</v>
       </c>
       <c r="Y61" t="str">
-        <v/>
+        <v>Superwash-behandlet — kan maskinvaskes og tumbles. Bloomer mindre end ubehandlet uld og kan strække over tid.</v>
       </c>
       <c r="Z61" t="str">
         <v/>
       </c>
       <c r="AA61" t="str">
-        <v>[{"fiber":"uld","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
+        <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>f385005c-a56f-475f-bb89-ff2a53809dae</v>
+        <v>3b16b2f3-c9b8-44e5-b542-485e9b9c9c44</v>
       </c>
       <c r="B62" t="str">
-        <v>Søstrene Grene</v>
+        <v>Mayflower</v>
       </c>
       <c r="C62" t="str">
-        <v>Mohair Blend</v>
+        <v>Nordia</v>
       </c>
       <c r="D62" t="str">
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>Kid mohair</v>
+        <v>Uld-blanding</v>
       </c>
       <c r="F62" t="str">
-        <v>lace</v>
+        <v>dk</v>
       </c>
       <c r="G62">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H62">
-        <v>860</v>
+        <v>142</v>
       </c>
       <c r="I62">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K62">
-        <v>41</v>
-      </c>
-      <c r="L62">
-        <v>47</v>
+        <v>19</v>
+      </c>
+      <c r="L62" t="str">
+        <v/>
       </c>
       <c r="M62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N62" t="str">
-        <v>Brushed kid mohair single med syntetisk kerne, let halo</v>
+        <v/>
       </c>
       <c r="O62" t="str">
         <v/>
       </c>
       <c r="P62" t="str">
-        <v>brushed_singles</v>
+        <v>plied</v>
       </c>
       <c r="Q62" t="str">
-        <v>brushed</v>
+        <v>superwash</v>
       </c>
       <c r="R62" t="str">
-        <v>handvask</v>
+        <v>maskinvask_30</v>
       </c>
       <c r="S62" t="str">
         <v/>
@@ -5539,93 +5539,93 @@
         <v>[]</v>
       </c>
       <c r="X62" t="str">
-        <v>["lette mohairbluser","sjaler","holdtråd","øve-projekter"]</v>
+        <v>[]</v>
       </c>
       <c r="Y62" t="str">
-        <v>Budget-alternativ til Tilia/Hannah. Mange bruger den til at teste mønstre før de investerer i dyrere mohair.</v>
+        <v/>
       </c>
       <c r="Z62" t="str">
         <v/>
       </c>
       <c r="AA62" t="str">
-        <v>[{"fiber":"kid_mohair","percentage":80},{"fiber":"nylon_polyamid","percentage":20}]</v>
+        <v>[{"fiber":"uld","percentage":51},{"fiber":"acryl","percentage":34},{"fiber":"nylon_polyamid","percentage":15}]</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v/>
+        <v>a5b59189-9d7a-4b1c-a4fd-7735366e6090</v>
       </c>
       <c r="B63" t="str">
-        <v>Tynd Uld / dansk spinderi</v>
+        <v>Navia</v>
       </c>
       <c r="C63" t="str">
-        <v>Spelsau</v>
+        <v>Trio</v>
       </c>
       <c r="D63" t="str">
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>uld</v>
+        <v>Uld</v>
       </c>
       <c r="F63" t="str">
-        <v/>
-      </c>
-      <c r="G63" t="str">
-        <v/>
-      </c>
-      <c r="H63" t="str">
-        <v/>
-      </c>
-      <c r="I63" t="str">
-        <v/>
-      </c>
-      <c r="J63" t="str">
-        <v/>
-      </c>
-      <c r="K63" t="str">
-        <v/>
-      </c>
-      <c r="L63" t="str">
-        <v/>
-      </c>
-      <c r="M63" t="str">
-        <v/>
+        <v>dk</v>
+      </c>
+      <c r="G63">
+        <v>50</v>
+      </c>
+      <c r="H63">
+        <v>240</v>
+      </c>
+      <c r="I63">
+        <v>4.5</v>
+      </c>
+      <c r="J63">
+        <v>4.5</v>
+      </c>
+      <c r="K63">
+        <v>19</v>
+      </c>
+      <c r="L63">
+        <v>26</v>
+      </c>
+      <c r="M63">
+        <v>4.5</v>
       </c>
       <c r="N63" t="str">
-        <v/>
-      </c>
-      <c r="O63" t="str">
-        <v/>
+        <v>3-trådet plied, klassisk worsted-spun, medium twist, lidt rustik overflade</v>
+      </c>
+      <c r="O63">
+        <v>3</v>
       </c>
       <c r="P63" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q63" t="str">
-        <v/>
+        <v>standard</v>
       </c>
       <c r="R63" t="str">
-        <v>ikke_angivet</v>
+        <v>handvask</v>
       </c>
       <c r="S63" t="str">
-        <v>Danmark</v>
+        <v>Færøerne</v>
       </c>
       <c r="T63" t="str">
-        <v>Danmark</v>
+        <v>Færøerne</v>
       </c>
       <c r="U63" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V63" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="W63" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X63" t="str">
-        <v/>
+        <v>["tykke sweatre","jakker","vanter","huer","fair isle","lopapeysa-stil"]</v>
       </c>
       <c r="Y63" t="str">
-        <v/>
+        <v>Ubehandlet færøsk uld. Filter hvis behandlet forkert.</v>
       </c>
       <c r="Z63" t="str">
         <v/>
@@ -5636,61 +5636,61 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>a049e5a8-e7f4-4310-8267-96d259e78076</v>
+        <v>c2e8f4a1-3d7b-4c91-b5e2-9f1a6d4e83c0</v>
       </c>
       <c r="B64" t="str">
-        <v>Vendita GmbH</v>
+        <v>Permin</v>
       </c>
       <c r="C64" t="str">
-        <v>Korsika</v>
+        <v>Bella</v>
       </c>
       <c r="D64" t="str">
-        <v/>
+        <v>by Permin</v>
       </c>
       <c r="E64" t="str">
-        <v>Plantefiber-blanding</v>
+        <v>Kid mohair-blanding</v>
       </c>
       <c r="F64" t="str">
-        <v>fingering</v>
+        <v>bulky</v>
       </c>
       <c r="G64">
         <v>50</v>
       </c>
       <c r="H64">
-        <v>600</v>
+        <v>290</v>
       </c>
       <c r="I64">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J64">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="K64">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L64">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="M64">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N64" t="str">
-        <v>Plied plantefiber — mindre elasticitet end uld, falder tungt og pænt</v>
+        <v>Brushed mohair-blanding med langt halo</v>
       </c>
       <c r="O64" t="str">
         <v/>
       </c>
       <c r="P64" t="str">
-        <v>plied</v>
+        <v/>
       </c>
       <c r="Q64" t="str">
         <v>standard</v>
       </c>
       <c r="R64" t="str">
-        <v>maskinvask_30</v>
+        <v>handvask</v>
       </c>
       <c r="S64" t="str">
-        <v>Tyskland</v>
+        <v/>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -5705,116 +5705,116 @@
         <v>[]</v>
       </c>
       <c r="X64" t="str">
-        <v>["sommertoppe","sjaler","viskestykker","tasker","hjemmetekstil"]</v>
+        <v>["store sweatre","kjoler","tørklæder","sjaler"]</v>
       </c>
       <c r="Y64" t="str">
-        <v>Aldi-kampagnegarn. Kølig drape, ingen varme.</v>
+        <v>Mohair-klassiker fra Permin. Langfibret halo, let og varm. Stort pind-interval. Kan strikkes med enkelttråd fx på pind 6 eller med flere tråde op til pind 15.</v>
       </c>
       <c r="Z64" t="str">
-        <v/>
+        <v>/garn-eksempler/permin-bella.jpg</v>
       </c>
       <c r="AA64" t="str">
-        <v>[{"fiber":"bomuld","percentage":73},{"fiber":"lin","percentage":27}]</v>
+        <v>[{"fiber":"kid_mohair","percentage":75},{"fiber":"uld","percentage":20},{"fiber":"nylon_polyamid","percentage":5}]</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v/>
+        <v>87699410-92dc-4d28-b711-a23bfad2cb6d</v>
       </c>
       <c r="B65" t="str">
-        <v>Drops</v>
+        <v>Permin</v>
       </c>
       <c r="C65" t="str">
-        <v>Baby Merino</v>
+        <v>Bella Color</v>
       </c>
       <c r="D65" t="str">
-        <v/>
+        <v>Bella Color by Permin</v>
       </c>
       <c r="E65" t="str">
-        <v>merinould</v>
+        <v>Kid mohair-blanding</v>
       </c>
       <c r="F65" t="str">
-        <v>sport</v>
+        <v>bulky</v>
       </c>
       <c r="G65">
         <v>50</v>
       </c>
       <c r="H65">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J65">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="K65">
-        <v>24</v>
-      </c>
-      <c r="L65" t="str">
-        <v/>
-      </c>
-      <c r="M65" t="str">
-        <v/>
+        <v>14</v>
+      </c>
+      <c r="L65">
+        <v>22</v>
+      </c>
+      <c r="M65">
+        <v>6</v>
       </c>
       <c r="N65" t="str">
-        <v>3-trådet plied, superwash extrafine merino, medium twist</v>
-      </c>
-      <c r="O65">
-        <v>3</v>
+        <v>Brushed mohair-blanding med langt halo</v>
+      </c>
+      <c r="O65" t="str">
+        <v/>
       </c>
       <c r="P65" t="str">
-        <v>plied</v>
+        <v>brushed_singles</v>
       </c>
       <c r="Q65" t="str">
-        <v>superwash</v>
+        <v>brushed</v>
       </c>
       <c r="R65" t="str">
-        <v>maskinvask_40</v>
+        <v>handvask</v>
       </c>
       <c r="S65" t="str">
-        <v>EU</v>
+        <v>Italien</v>
       </c>
       <c r="T65" t="str">
-        <v>Sydamerika</v>
+        <v/>
       </c>
       <c r="U65" t="str">
         <v>i_produktion</v>
       </c>
       <c r="V65" t="str">
-        <v>["Oeko-Tex Standard 100 (Class I)"]</v>
+        <v>[]</v>
       </c>
       <c r="W65" t="str">
         <v>[]</v>
       </c>
       <c r="X65" t="str">
-        <v>["babytøj","børnestrik","lette sweatre","sjaler","cardigans"]</v>
+        <v>["store sweatre","kjoler","tørklæder","sjaler"]</v>
       </c>
       <c r="Y65" t="str">
-        <v>Blød, superwash-behandlet extrafine merino til babytøj og lette voksenstrik. Oeko-Tex klasse I certificeret — godkendt til babyer under 3 år. Maskinvask på uldprogram 40°C.</v>
+        <v>Mohair-klassiker fra Permin. Langfibret halo, let og varm. Stort pind-interval. Kan strikkes med enkelttråd fx på pind 6 eller med flere tråde op til pind 15.</v>
       </c>
       <c r="Z65" t="str">
-        <v>/garn-eksempler/drops-baby-merino.jpg</v>
+        <v>/garn-eksempler/permin-bella-color.jpg</v>
       </c>
       <c r="AA65" t="str">
-        <v>[{"fiber":"merinould","percentage":100}]</v>
+        <v>[{"fiber":"kid_mohair","percentage":75},{"fiber":"uld","percentage":20},{"fiber":"nylon_polyamid","percentage":5}]</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v/>
+        <v>7839f1ad-bed5-4b8e-9be1-18a79709c53c</v>
       </c>
       <c r="B66" t="str">
-        <v>Filcolana</v>
+        <v>Permin</v>
       </c>
       <c r="C66" t="str">
-        <v>Alva</v>
+        <v>Hannah</v>
       </c>
       <c r="D66" t="str">
         <v/>
       </c>
       <c r="E66" t="str">
-        <v>alpaka</v>
+        <v>Merinould-blanding</v>
       </c>
       <c r="F66" t="str">
         <v>lace</v>
@@ -5823,43 +5823,43 @@
         <v>25</v>
       </c>
       <c r="H66">
-        <v>700</v>
-      </c>
-      <c r="I66" t="str">
-        <v/>
-      </c>
-      <c r="J66" t="str">
-        <v/>
-      </c>
-      <c r="K66" t="str">
-        <v/>
-      </c>
-      <c r="L66" t="str">
-        <v/>
-      </c>
-      <c r="M66" t="str">
-        <v/>
+        <v>1100</v>
+      </c>
+      <c r="I66">
+        <v>2.5</v>
+      </c>
+      <c r="J66">
+        <v>3</v>
+      </c>
+      <c r="K66">
+        <v>28</v>
+      </c>
+      <c r="L66">
+        <v>46</v>
+      </c>
+      <c r="M66">
+        <v>3</v>
       </c>
       <c r="N66" t="str">
-        <v>tyndt 2-trådet alpakagarn</v>
-      </c>
-      <c r="O66">
-        <v>2</v>
+        <v>Brushed, silkekerne med uld/cashmere spundet udenom — let halo</v>
+      </c>
+      <c r="O66" t="str">
+        <v/>
       </c>
       <c r="P66" t="str">
-        <v>plied</v>
+        <v>brushed_singles</v>
       </c>
       <c r="Q66" t="str">
-        <v/>
+        <v>brushed</v>
       </c>
       <c r="R66" t="str">
         <v>handvask</v>
       </c>
       <c r="S66" t="str">
-        <v>Peru</v>
+        <v>Italien</v>
       </c>
       <c r="T66" t="str">
-        <v>Peru</v>
+        <v/>
       </c>
       <c r="U66" t="str">
         <v>i_produktion</v>
@@ -5871,21 +5871,1930 @@
         <v>[]</v>
       </c>
       <c r="X66" t="str">
-        <v>["følgegarn","sjaler","lette bluser"]</v>
+        <v>["sjaler","tørklæder","holdtråd","babygaver"]</v>
       </c>
       <c r="Y66" t="str">
-        <v>Alva er et tyndt 2-trådet garn spundet af fibre fra peruvianske alpakaer. Alva er blød, varm og glansfuld og velegnet til mange slags projekter. Det tynde garn er perfekt til at strikke sammen med vores andre kvaliteter. Desuden er Alva et herligt alternativt følgegarn i stedet for et tyndt mohairgarn.</v>
+        <v>Følgetråd sammen med andre for blødhed og brushed effekt</v>
       </c>
       <c r="Z66" t="str">
-        <v>/garn-eksempler/filcolana-alva.jpg</v>
+        <v>/garn-eksempler/permin-hannah.jpg</v>
       </c>
       <c r="AA66" t="str">
-        <v>[{"fiber":"alpaka","percentage":100}]</v>
+        <v>[{"fiber":"merinould","percentage":50},{"fiber":"silke","percentage":30},{"fiber":"kashmir","percentage":20}]</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v/>
+      </c>
+      <c r="B67" t="str">
+        <v>Rauma Garn</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Finull</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v>uld</v>
+      </c>
+      <c r="F67" t="str">
+        <v>sport</v>
+      </c>
+      <c r="G67">
+        <v>50</v>
+      </c>
+      <c r="H67">
+        <v>350</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67">
+        <v>3.5</v>
+      </c>
+      <c r="K67">
+        <v>25</v>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67">
+        <v>2</v>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S67" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T67" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="U67" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V67" t="str">
+        <v/>
+      </c>
+      <c r="W67" t="str">
+        <v/>
+      </c>
+      <c r="X67" t="str">
+        <v/>
+      </c>
+      <c r="Y67" t="str">
+        <v/>
+      </c>
+      <c r="Z67" t="str">
+        <v/>
+      </c>
+      <c r="AA67" t="str">
+        <v>[{"fiber":"uld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>5775ac2a-7b97-4858-a2cc-f9a9df63dee8</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Rauma Garn</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Vams</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v>Uld</v>
+      </c>
+      <c r="F68" t="str">
+        <v>aran</v>
+      </c>
+      <c r="G68">
+        <v>50</v>
+      </c>
+      <c r="H68">
+        <v>166</v>
+      </c>
+      <c r="I68">
+        <v>5</v>
+      </c>
+      <c r="J68">
+        <v>6</v>
+      </c>
+      <c r="K68">
+        <v>15</v>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68">
+        <v>5.5</v>
+      </c>
+      <c r="N68" t="str">
+        <v>Kardegarn (woolen-spun), single, blød twist, luftig og let filtbar</v>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v>singles</v>
+      </c>
+      <c r="Q68" t="str">
+        <v>standard</v>
+      </c>
+      <c r="R68" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S68" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T68" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="U68" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V68" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W68" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X68" t="str">
+        <v>["tykke sweatre","jakker","vanter","tæpper","toveprojekter"]</v>
+      </c>
+      <c r="Y68" t="str">
+        <v>Kardegarn = kartet ulden er på kryds og tværs, hvilket giver et luftigt, blødt rustikt garn der bloomer kraftigt ved vask.</v>
+      </c>
+      <c r="Z68" t="str">
+        <v/>
+      </c>
+      <c r="AA68" t="str">
+        <v>[{"fiber":"uld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>bce5c06c-a587-47e4-a824-5d3de89c05d7</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Rico Design</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Creative Make It Blümchen</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v>Lyocell</v>
+      </c>
+      <c r="F69" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G69">
+        <v>25</v>
+      </c>
+      <c r="H69">
+        <v>1500</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v>Tråd med applikerede tekstil-blomster langs tråden (effektgarn)</v>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v>standard</v>
+      </c>
+      <c r="R69" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S69" t="str">
+        <v>Tyskland</v>
+      </c>
+      <c r="T69" t="str">
+        <v/>
+      </c>
+      <c r="U69" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V69" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W69" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X69" t="str">
+        <v>["børnehuer","dekorative projekter","amigurumi-detaljer"]</v>
+      </c>
+      <c r="Y69" t="str">
+        <v>USIKKER — bekræft producent og specs på banderolen.</v>
+      </c>
+      <c r="Z69" t="str">
+        <v>/garn-eksempler/rico-design-creative-make-it-blumchen.jpg</v>
+      </c>
+      <c r="AA69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>953a7d29-d932-4334-a9ca-6403f4db7c28</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Rosários 4</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Paillettes Classic Collection</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v>Polyester</v>
+      </c>
+      <c r="F70" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G70">
+        <v>25</v>
+      </c>
+      <c r="H70">
+        <v>548</v>
+      </c>
+      <c r="I70">
+        <v>3</v>
+      </c>
+      <c r="J70">
+        <v>3.5</v>
+      </c>
+      <c r="K70">
+        <v>28</v>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v>Tråd med indspundne/påsyede pailletter — effektgarn</v>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v>standard</v>
+      </c>
+      <c r="R70" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S70" t="str">
+        <v>Portugal</v>
+      </c>
+      <c r="T70" t="str">
+        <v/>
+      </c>
+      <c r="U70" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V70" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W70" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X70" t="str">
+        <v>["fest-projekter","holdtråd","aftentoppe"]</v>
+      </c>
+      <c r="Y70" t="str">
+        <v>USIKKER — Rosários 4 har flere pailletgarn-serier. Bør verificeres på banderolen.</v>
+      </c>
+      <c r="Z70" t="str">
+        <v>/garn-eksempler/rosarios-4-paillettes-classic-collection.jpg</v>
+      </c>
+      <c r="AA70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>d73ecbc9-ecf6-4a05-8fcc-6719640cd6b7</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Sandnes Garn</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Kitten Mohair</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v>Mohair-blanding</v>
+      </c>
+      <c r="F71" t="str">
+        <v>dk</v>
+      </c>
+      <c r="G71">
+        <v>50</v>
+      </c>
+      <c r="H71">
+        <v>326</v>
+      </c>
+      <c r="I71">
+        <v>4</v>
+      </c>
+      <c r="J71">
+        <v>4</v>
+      </c>
+      <c r="K71">
+        <v>19</v>
+      </c>
+      <c r="L71">
+        <v>26</v>
+      </c>
+      <c r="M71">
+        <v>4</v>
+      </c>
+      <c r="N71" t="str">
+        <v>Plied DK-mohair-blend, let halo, blødt</v>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>standard</v>
+      </c>
+      <c r="R71" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S71" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T71" t="str">
+        <v/>
+      </c>
+      <c r="U71" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V71" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W71" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X71" t="str">
+        <v>["hverdagshuer","vanter","vintertilbehør","retro-projekter"]</v>
+      </c>
+      <c r="Y71" t="str">
+        <v>80er/90er-stilstrik. Akrylindholdet gør den mere robust og mindre elegant — ikke et luksusgarn til lette overdele.</v>
+      </c>
+      <c r="Z71" t="str">
+        <v/>
+      </c>
+      <c r="AA71" t="str">
+        <v>[{"fiber":"courtelle","percentage":50},{"fiber":"mohair","percentage":30},{"fiber":"uld","percentage":20}]</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v/>
+      </c>
+      <c r="B72" t="str">
+        <v>Sandnes Garn</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Kos</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v>alpaka/uld/nylon</v>
+      </c>
+      <c r="F72" t="str">
+        <v>aran</v>
+      </c>
+      <c r="G72">
+        <v>50</v>
+      </c>
+      <c r="H72">
+        <v>300</v>
+      </c>
+      <c r="I72">
+        <v>4.5</v>
+      </c>
+      <c r="J72">
+        <v>5.5</v>
+      </c>
+      <c r="K72">
+        <v>17</v>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S72" t="str">
+        <v/>
+      </c>
+      <c r="T72" t="str">
+        <v>Uruguay (uld), Peru (alpaka)</v>
+      </c>
+      <c r="U72" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V72" t="str">
+        <v/>
+      </c>
+      <c r="W72" t="str">
+        <v/>
+      </c>
+      <c r="X72" t="str">
+        <v/>
+      </c>
+      <c r="Y72" t="str">
+        <v/>
+      </c>
+      <c r="Z72" t="str">
+        <v/>
+      </c>
+      <c r="AA72" t="str">
+        <v>[{"fiber":"alpaka","percentage":62},{"fiber":"nylon_polyamid","percentage":29},{"fiber":"uld","percentage":9}]</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v/>
+      </c>
+      <c r="B73" t="str">
+        <v>Sandnes Garn</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Line</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v>bomuld/viskose/lin</v>
+      </c>
+      <c r="F73" t="str">
+        <v>dk</v>
+      </c>
+      <c r="G73">
+        <v>50</v>
+      </c>
+      <c r="H73">
+        <v>220</v>
+      </c>
+      <c r="I73">
+        <v>4</v>
+      </c>
+      <c r="J73">
+        <v>4</v>
+      </c>
+      <c r="K73">
+        <v>20</v>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
+      <c r="T73" t="str">
+        <v>Indien</v>
+      </c>
+      <c r="U73" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V73" t="str">
+        <v/>
+      </c>
+      <c r="W73" t="str">
+        <v/>
+      </c>
+      <c r="X73" t="str">
+        <v/>
+      </c>
+      <c r="Y73" t="str">
+        <v/>
+      </c>
+      <c r="Z73" t="str">
+        <v/>
+      </c>
+      <c r="AA73" t="str">
+        <v>[{"fiber":"bomuld","percentage":53},{"fiber":"viskose","percentage":33},{"fiber":"lin","percentage":14}]</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>41e54067-9d9b-45a7-83f0-873ba436eaf3</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Sandnes Garn</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Peer Gynt</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v>Uld</v>
+      </c>
+      <c r="F74" t="str">
+        <v>dk</v>
+      </c>
+      <c r="G74">
+        <v>50</v>
+      </c>
+      <c r="H74">
+        <v>182</v>
+      </c>
+      <c r="I74">
+        <v>3.5</v>
+      </c>
+      <c r="J74">
+        <v>4</v>
+      </c>
+      <c r="K74">
+        <v>22</v>
+      </c>
+      <c r="L74">
+        <v>28</v>
+      </c>
+      <c r="M74">
+        <v>4</v>
+      </c>
+      <c r="N74" t="str">
+        <v>3-trådet, klassisk plied</v>
+      </c>
+      <c r="O74">
+        <v>3</v>
+      </c>
+      <c r="P74" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q74" t="str">
+        <v>superwash</v>
+      </c>
+      <c r="R74" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S74" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T74" t="str">
+        <v/>
+      </c>
+      <c r="U74" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V74" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W74" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X74" t="str">
+        <v>["huer","vanter","sweatre","børnetøj"]</v>
+      </c>
+      <c r="Y74" t="str">
+        <v>Nordisk klassiker. Bredt farveudvalg. Meget brugt i PetiteKnit-opskrifter.</v>
+      </c>
+      <c r="Z74" t="str">
+        <v/>
+      </c>
+      <c r="AA74" t="str">
+        <v>[{"fiber":"uld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>55127529-cff3-4ec8-bb48-60d902d1cbda</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Sandnes Garn</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Poppy</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v>Bomuld</v>
+      </c>
+      <c r="F75" t="str">
+        <v>dk</v>
+      </c>
+      <c r="G75">
+        <v>50</v>
+      </c>
+      <c r="H75">
+        <v>210</v>
+      </c>
+      <c r="I75">
+        <v>4</v>
+      </c>
+      <c r="J75">
+        <v>4</v>
+      </c>
+      <c r="K75">
+        <v>21</v>
+      </c>
+      <c r="L75">
+        <v>28</v>
+      </c>
+      <c r="M75">
+        <v>4</v>
+      </c>
+      <c r="N75" t="str">
+        <v>Flertrådet, blød kæmmet bomuld</v>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>standard</v>
+      </c>
+      <c r="R75" t="str">
+        <v>maskinvask_40</v>
+      </c>
+      <c r="S75" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T75" t="str">
+        <v>Tyrkiet</v>
+      </c>
+      <c r="U75" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V75" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W75" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X75" t="str">
+        <v>["sommertoppe","babytøj","tørklæder","hverdagsbomuld"]</v>
+      </c>
+      <c r="Y75" t="str">
+        <v>Blød bomuld uden glans, hverdagsprojekter i DK.</v>
+      </c>
+      <c r="Z75" t="str">
+        <v>/garn-eksempler/sandnes-garn-poppy.jpg</v>
+      </c>
+      <c r="AA75" t="str">
+        <v>[{"fiber":"bomuld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>6f707938-0284-4d82-afab-72fbe185cb5b</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Sandnes Garn</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Sunday</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v>Merinould</v>
+      </c>
+      <c r="F76" t="str">
+        <v>fingering</v>
+      </c>
+      <c r="G76">
+        <v>50</v>
+      </c>
+      <c r="H76">
+        <v>470</v>
+      </c>
+      <c r="I76">
+        <v>3</v>
+      </c>
+      <c r="J76">
+        <v>3</v>
+      </c>
+      <c r="K76">
+        <v>28</v>
+      </c>
+      <c r="L76">
+        <v>28</v>
+      </c>
+      <c r="M76">
+        <v>3</v>
+      </c>
+      <c r="N76" t="str">
+        <v>3-trådet plied kamgarn, non-superwash merino, blød</v>
+      </c>
+      <c r="O76">
+        <v>3</v>
+      </c>
+      <c r="P76" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q76" t="str">
+        <v>standard</v>
+      </c>
+      <c r="R76" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S76" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T76" t="str">
+        <v>Uruguay</v>
+      </c>
+      <c r="U76" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V76" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W76" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X76" t="str">
+        <v>["sweatre","cardigans","babytøj","huer","sjaler"]</v>
+      </c>
+      <c r="Y76" t="str">
+        <v>Et af Sandnes' mest populære garner — ekstremt smukt farvekort med jordfarver og pasteller valgt i samarbejde med PetiteKnit. Non-superwash merino, meget blød. Bruges i mange af de mest downloadede opskrifter i Danmark.</v>
+      </c>
+      <c r="Z76" t="str">
+        <v/>
+      </c>
+      <c r="AA76" t="str">
+        <v>[{"fiber":"merinould","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>ed2c4d04-de90-4cfb-96fe-220123f18b56</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Sandnes Garn</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Tynn Silk Mohair</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v>Kid mohair-blanding</v>
+      </c>
+      <c r="F77" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G77">
+        <v>25</v>
+      </c>
+      <c r="H77">
+        <v>848</v>
+      </c>
+      <c r="I77">
+        <v>3</v>
+      </c>
+      <c r="J77">
+        <v>5</v>
+      </c>
+      <c r="K77">
+        <v>18</v>
+      </c>
+      <c r="L77">
+        <v>28</v>
+      </c>
+      <c r="M77">
+        <v>4</v>
+      </c>
+      <c r="N77" t="str">
+        <v>Brushed single, angora-ged mohair med silkekerne, medium halo</v>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v>brushed_singles</v>
+      </c>
+      <c r="Q77" t="str">
+        <v>brushed</v>
+      </c>
+      <c r="R77" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S77" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T77" t="str">
+        <v>Sydafrika</v>
+      </c>
+      <c r="U77" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V77" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W77" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X77" t="str">
+        <v>["holdtråd","lette bluser","sjaler","oversize sweatre"]</v>
+      </c>
+      <c r="Y77" t="str">
+        <v>Meget populær silk mohair fra Sandnes — høj kvalitet, tåler maskinvask ved 30 grader (uldprogram), og bruges i mange gennemtestede opskrifter fra kendte strikkedesignere. Luksuriøs og luftig holdtråd.</v>
+      </c>
+      <c r="Z77" t="str">
+        <v/>
+      </c>
+      <c r="AA77" t="str">
+        <v>[{"fiber":"mohair","percentage":57},{"fiber":"silke","percentage":28},{"fiber":"uld","percentage":15}]</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>c31f243d-5f2e-47de-89a2-d9e5a80d63d9</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Schachenmayr</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Regia 4-ply</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Regia</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Uld</v>
+      </c>
+      <c r="F78" t="str">
+        <v>fingering</v>
+      </c>
+      <c r="G78">
+        <v>50</v>
+      </c>
+      <c r="H78">
+        <v>420</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+      <c r="J78">
+        <v>3</v>
+      </c>
+      <c r="K78">
+        <v>30</v>
+      </c>
+      <c r="L78">
+        <v>42</v>
+      </c>
+      <c r="M78">
+        <v>2.5</v>
+      </c>
+      <c r="N78" t="str">
+        <v>4-trådet klassisk sokkegarn, superwash</v>
+      </c>
+      <c r="O78">
+        <v>4</v>
+      </c>
+      <c r="P78" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q78" t="str">
+        <v>superwash</v>
+      </c>
+      <c r="R78" t="str">
+        <v>maskinvask_40</v>
+      </c>
+      <c r="S78" t="str">
+        <v>Tyskland</v>
+      </c>
+      <c r="T78" t="str">
+        <v/>
+      </c>
+      <c r="U78" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V78" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W78" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X78" t="str">
+        <v>["sokker","vanter","slidstærkt hverdagsstrik"]</v>
+      </c>
+      <c r="Y78" t="str">
+        <v>Tysk sokkegarn-klassiker. Enormt farveudvalg inkl. selvstribende.</v>
+      </c>
+      <c r="Z78" t="str">
+        <v/>
+      </c>
+      <c r="AA78" t="str">
+        <v>[{"fiber":"uld","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v/>
+      </c>
+      <c r="B79" t="str">
+        <v>Schoppel Wolle</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Edition 3</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v>merino</v>
+      </c>
+      <c r="F79" t="str">
+        <v>sport</v>
+      </c>
+      <c r="G79">
+        <v>50</v>
+      </c>
+      <c r="H79">
+        <v>300</v>
+      </c>
+      <c r="I79">
+        <v>3</v>
+      </c>
+      <c r="J79">
+        <v>3.5</v>
+      </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v>superwash</v>
+      </c>
+      <c r="R79" t="str">
+        <v>maskinvask_40</v>
+      </c>
+      <c r="S79" t="str">
+        <v/>
+      </c>
+      <c r="T79" t="str">
+        <v/>
+      </c>
+      <c r="U79" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V79" t="str">
+        <v/>
+      </c>
+      <c r="W79" t="str">
+        <v/>
+      </c>
+      <c r="X79" t="str">
+        <v/>
+      </c>
+      <c r="Y79" t="str">
+        <v/>
+      </c>
+      <c r="Z79" t="str">
+        <v/>
+      </c>
+      <c r="AA79" t="str">
+        <v>[{"fiber":"merinould","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v/>
+      </c>
+      <c r="B80" t="str">
+        <v>Schoppel Wolle</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Zauberball Stärke 6</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v>uld/nylon</v>
+      </c>
+      <c r="F80" t="str">
+        <v>sport</v>
+      </c>
+      <c r="G80">
+        <v>150</v>
+      </c>
+      <c r="H80">
+        <v>266.667</v>
+      </c>
+      <c r="I80">
+        <v>3</v>
+      </c>
+      <c r="J80">
+        <v>4</v>
+      </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v>superwash</v>
+      </c>
+      <c r="R80" t="str">
+        <v>maskinvask_40</v>
+      </c>
+      <c r="S80" t="str">
+        <v/>
+      </c>
+      <c r="T80" t="str">
+        <v/>
+      </c>
+      <c r="U80" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V80" t="str">
+        <v/>
+      </c>
+      <c r="W80" t="str">
+        <v/>
+      </c>
+      <c r="X80" t="str">
+        <v/>
+      </c>
+      <c r="Y80" t="str">
+        <v/>
+      </c>
+      <c r="Z80" t="str">
+        <v/>
+      </c>
+      <c r="AA80" t="str">
+        <v>[{"fiber":"uld","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v/>
+      </c>
+      <c r="B81" t="str">
+        <v>Strikkefeber</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Kul Tråd</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v>polyester</v>
+      </c>
+      <c r="F81" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G81">
+        <v>50</v>
+      </c>
+      <c r="H81">
+        <v>500</v>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S81" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T81" t="str">
+        <v/>
+      </c>
+      <c r="U81" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V81" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W81" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X81" t="str">
+        <v>["effektgarn", "beilauf", "accentstrik"]</v>
+      </c>
+      <c r="Y81" t="str">
+        <v>Norsk effekttråd i 100% polyester på cone (50g/250m). Bruges som beilauf sammen med uld eller mohair for at tilføre struktur, farve eller diskret skinneffekt.</v>
+      </c>
+      <c r="Z81" t="str">
+        <v>/garn-eksempler/strikkefeber-kul-trad.jpg</v>
+      </c>
+      <c r="AA81" t="str">
+        <v>[{"fiber": "polyester", "percentage": 100}]</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v/>
+      </c>
+      <c r="B82" t="str">
+        <v>Strikkefeber</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Kul Tråd Disco</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v>bomuld</v>
+      </c>
+      <c r="F82" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G82">
+        <v>50</v>
+      </c>
+      <c r="H82">
+        <v>300</v>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
+      <c r="R82" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S82" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T82" t="str">
+        <v/>
+      </c>
+      <c r="U82" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V82" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W82" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X82" t="str">
+        <v>["effektgarn", "beilauf", "festtøj"]</v>
+      </c>
+      <c r="Y82" t="str">
+        <v>Norsk pailet-tråd i 100% bomuld med blanding af store og små pailletter (50g/150m). Strikkes sammen med fx silk mohair eller merinould til festtøj med skinneffekt.</v>
+      </c>
+      <c r="Z82" t="str">
+        <v>/garn-eksempler/strikkefeber-kul-trad-disco.jpg</v>
+      </c>
+      <c r="AA82" t="str">
+        <v>[{"fiber": "bomuld", "percentage": 100}]</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v/>
+      </c>
+      <c r="B83" t="str">
+        <v>Strikkefeber</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Glitter</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v>lurex/polyester</v>
+      </c>
+      <c r="F83" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S83" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T83" t="str">
+        <v/>
+      </c>
+      <c r="U83" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V83" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W83" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X83" t="str">
+        <v>["effektgarn", "beilauf", "festtøj"]</v>
+      </c>
+      <c r="Y83" t="str">
+        <v>Norsk glitter-/lurextråd til beilauf. Tilføjer subtil eller markant glimt sammen med andet garn — fås i flere farver inkl. sølv, guld, mint og koral.</v>
+      </c>
+      <c r="Z83" t="str">
+        <v>/garn-eksempler/strikkefeber-glitter.jpg</v>
+      </c>
+      <c r="AA83" t="str">
+        <v>[{"fiber": "polyester", "percentage": 100}]</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>f385005c-a56f-475f-bb89-ff2a53809dae</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Søstrene Grene</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Mohair Blend</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v>Kid mohair</v>
+      </c>
+      <c r="F84" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G84">
+        <v>25</v>
+      </c>
+      <c r="H84">
+        <v>860</v>
+      </c>
+      <c r="I84">
+        <v>3</v>
+      </c>
+      <c r="J84">
+        <v>3</v>
+      </c>
+      <c r="K84">
+        <v>41</v>
+      </c>
+      <c r="L84">
+        <v>47</v>
+      </c>
+      <c r="M84">
+        <v>3</v>
+      </c>
+      <c r="N84" t="str">
+        <v>Brushed kid mohair single med syntetisk kerne, let halo</v>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v>brushed_singles</v>
+      </c>
+      <c r="Q84" t="str">
+        <v>brushed</v>
+      </c>
+      <c r="R84" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S84" t="str">
+        <v/>
+      </c>
+      <c r="T84" t="str">
+        <v/>
+      </c>
+      <c r="U84" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V84" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W84" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X84" t="str">
+        <v>["lette mohairbluser","sjaler","holdtråd","øve-projekter"]</v>
+      </c>
+      <c r="Y84" t="str">
+        <v>Budget-alternativ til Tilia/Hannah. Mange bruger den til at teste mønstre før de investerer i dyrere mohair.</v>
+      </c>
+      <c r="Z84" t="str">
+        <v/>
+      </c>
+      <c r="AA84" t="str">
+        <v>[{"fiber":"kid_mohair","percentage":80},{"fiber":"nylon_polyamid","percentage":20}]</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v/>
+      </c>
+      <c r="B85" t="str">
+        <v>Tynd Uld / dansk spinderi</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Spelsau</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v>uld</v>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
+        <v>ikke_angivet</v>
+      </c>
+      <c r="S85" t="str">
+        <v>Danmark</v>
+      </c>
+      <c r="T85" t="str">
+        <v>Danmark</v>
+      </c>
+      <c r="U85" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V85" t="str">
+        <v/>
+      </c>
+      <c r="W85" t="str">
+        <v/>
+      </c>
+      <c r="X85" t="str">
+        <v/>
+      </c>
+      <c r="Y85" t="str">
+        <v/>
+      </c>
+      <c r="Z85" t="str">
+        <v/>
+      </c>
+      <c r="AA85" t="str">
+        <v>[{"fiber":"uld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>a049e5a8-e7f4-4310-8267-96d259e78076</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Vendita GmbH</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Korsika</v>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v>Plantefiber-blanding</v>
+      </c>
+      <c r="F86" t="str">
+        <v>fingering</v>
+      </c>
+      <c r="G86">
+        <v>50</v>
+      </c>
+      <c r="H86">
+        <v>600</v>
+      </c>
+      <c r="I86">
+        <v>2.5</v>
+      </c>
+      <c r="J86">
+        <v>3.5</v>
+      </c>
+      <c r="K86">
+        <v>24</v>
+      </c>
+      <c r="L86">
+        <v>34</v>
+      </c>
+      <c r="M86">
+        <v>3</v>
+      </c>
+      <c r="N86" t="str">
+        <v>Plied plantefiber — mindre elasticitet end uld, falder tungt og pænt</v>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q86" t="str">
+        <v>standard</v>
+      </c>
+      <c r="R86" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S86" t="str">
+        <v>Tyskland</v>
+      </c>
+      <c r="T86" t="str">
+        <v/>
+      </c>
+      <c r="U86" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V86" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W86" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X86" t="str">
+        <v>["sommertoppe","sjaler","viskestykker","tasker","hjemmetekstil"]</v>
+      </c>
+      <c r="Y86" t="str">
+        <v>Aldi-kampagnegarn. Kølig drape, ingen varme.</v>
+      </c>
+      <c r="Z86" t="str">
+        <v/>
+      </c>
+      <c r="AA86" t="str">
+        <v>[{"fiber":"bomuld","percentage":73},{"fiber":"lin","percentage":27}]</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v/>
+      </c>
+      <c r="B87" t="str">
+        <v>Drops</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Kid-Silk</v>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v>Kid mohair-blanding</v>
+      </c>
+      <c r="F87" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G87">
+        <v>25</v>
+      </c>
+      <c r="H87">
+        <v>840</v>
+      </c>
+      <c r="I87">
+        <v>3</v>
+      </c>
+      <c r="J87">
+        <v>4</v>
+      </c>
+      <c r="K87">
+        <v>24</v>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87">
+        <v>3.5</v>
+      </c>
+      <c r="N87" t="str">
+        <v>Brushed singles, kid mohair med silke-kerne, blød halo</v>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v>brushed_singles</v>
+      </c>
+      <c r="Q87" t="str">
+        <v>brushed</v>
+      </c>
+      <c r="R87" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S87" t="str">
+        <v>Italien</v>
+      </c>
+      <c r="T87" t="str">
+        <v/>
+      </c>
+      <c r="U87" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V87" t="str">
+        <v>["Oeko-Tex Standard 100 (Class I)"]</v>
+      </c>
+      <c r="W87" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X87" t="str">
+        <v>["holdtråd","sjaler","lette bluser","luftige sweatre"]</v>
+      </c>
+      <c r="Y87" t="str">
+        <v>DROPS' klassiske kid silk — let, luftig holdtråd. Bruges typisk holdt sammen med et tyndt uld- eller alpakagarn for at give halo og varme. Egnet til pind 4-8 i held-together.</v>
+      </c>
+      <c r="Z87" t="str">
+        <v/>
+      </c>
+      <c r="AA87" t="str">
+        <v>[{"fiber":"mohair","percentage":75},{"fiber":"silke","percentage":25}]</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v/>
+      </c>
+      <c r="B88" t="str">
+        <v>Önling</v>
+      </c>
+      <c r="C88" t="str">
+        <v>No 12</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v>Kid mohair-blanding</v>
+      </c>
+      <c r="F88" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G88">
+        <v>25</v>
+      </c>
+      <c r="H88">
+        <v>840</v>
+      </c>
+      <c r="I88">
+        <v>3</v>
+      </c>
+      <c r="J88">
+        <v>4</v>
+      </c>
+      <c r="K88">
+        <v>23</v>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88">
+        <v>3.5</v>
+      </c>
+      <c r="N88" t="str">
+        <v>Brushed singles, kid mohair + silke, fin halo</v>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v>brushed_singles</v>
+      </c>
+      <c r="Q88" t="str">
+        <v>brushed</v>
+      </c>
+      <c r="R88" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S88" t="str">
+        <v>Italien</v>
+      </c>
+      <c r="T88" t="str">
+        <v/>
+      </c>
+      <c r="U88" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V88" t="str">
+        <v>["Oeko-Tex Standard 100"]</v>
+      </c>
+      <c r="W88" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X88" t="str">
+        <v>["holdtråd","sjaler","lette bluser","luftige sweatre"]</v>
+      </c>
+      <c r="Y88" t="str">
+        <v>Dansk silk-mohair fra Önling i klassisk kvalitet. Bruges typisk som holdtråd sammen med et tyndt uldgarn til pind 4-8.</v>
+      </c>
+      <c r="Z88" t="str">
+        <v/>
+      </c>
+      <c r="AA88" t="str">
+        <v>[{"fiber":"mohair","percentage":70},{"fiber":"silke","percentage":30}]</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v/>
+      </c>
+      <c r="B89" t="str">
+        <v>Sandnes Garn</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Tynn Merinoull</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v>Merinould</v>
+      </c>
+      <c r="F89" t="str">
+        <v>fingering</v>
+      </c>
+      <c r="G89">
+        <v>50</v>
+      </c>
+      <c r="H89">
+        <v>350</v>
+      </c>
+      <c r="I89">
+        <v>3</v>
+      </c>
+      <c r="J89">
+        <v>3.5</v>
+      </c>
+      <c r="K89">
+        <v>26</v>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89">
+        <v>3</v>
+      </c>
+      <c r="N89" t="str">
+        <v>Plied fingering merino, blødt og let spundet</v>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q89" t="str">
+        <v>standard</v>
+      </c>
+      <c r="R89" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S89" t="str">
+        <v>Norge</v>
+      </c>
+      <c r="T89" t="str">
+        <v>Sydamerika</v>
+      </c>
+      <c r="U89" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V89" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W89" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X89" t="str">
+        <v>["strukturtråd","lette sweatre","babytøj","holdtråd-base"]</v>
+      </c>
+      <c r="Y89" t="str">
+        <v>Sandnes' tynde 100% merinoull. Klassisk strukturtråd der bruges sammen med fx Tynn Silk Mohair til en blød pind 6-strik med både halo og fald.</v>
+      </c>
+      <c r="Z89" t="str">
+        <v/>
+      </c>
+      <c r="AA89" t="str">
+        <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA89"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/content/yarns.xlsx
+++ b/content/yarns.xlsx
@@ -1393,7 +1393,7 @@
         <v>Lofty "blown" garn hvor baby-alpaka og merinould blæses ind i en tynd nylon-tube i stedet for at blive spundet. Færdige plagg er 30-35% lettere end tilsvarende tykkelse i klassisk spundet garn. Meget populær til behagelige oversize sweatre.</v>
       </c>
       <c r="Z12" t="str">
-        <v/>
+        <v>/garn-eksempler/drops-air.jpg</v>
       </c>
       <c r="AA12" t="str">
         <v>[{"fiber":"baby_alpaka","percentage":65},{"fiber":"nylon_polyamid","percentage":28},{"fiber":"merinould","percentage":7}]</v>
@@ -1476,7 +1476,7 @@
         <v>Billigt budget-garn. Kan filtes.</v>
       </c>
       <c r="Z13" t="str">
-        <v/>
+        <v>/garn-eksempler/drops-alaska.jpg</v>
       </c>
       <c r="AA13" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -1559,7 +1559,7 @@
         <v>Klassisk, let alpakagarn med fantastisk drapering og farvemætning. Populært til sjaler og lette projekter. Kradser ikke og er blødt mod huden. Et af DROPS' ældste og mest elskede kvaliteter.</v>
       </c>
       <c r="Z14" t="str">
-        <v/>
+        <v>/garn-eksempler/drops-alpaca.jpg</v>
       </c>
       <c r="AA14" t="str">
         <v>[{"fiber":"alpaka","percentage":100}]</v>
@@ -1725,7 +1725,7 @@
         <v>Slidstærkt fingering-garn med alpaka-blanding — særligt populær til sokker pga. holdbarheden. Tynd nok til colorwork og sjaler, blød nok til barnetøj.</v>
       </c>
       <c r="Z16" t="str">
-        <v/>
+        <v>/garn-eksempler/drops-flora.jpg</v>
       </c>
       <c r="AA16" t="str">
         <v>[{"fiber":"uld","percentage":65},{"fiber":"alpaka","percentage":35}]</v>
@@ -1808,7 +1808,7 @@
         <v>En af de absolut mest populære DROPS-kvaliteter. Slidstærkt, superwash-behandlet uldgarn til en meget prisvenlig pris. Fast twist giver god maskedefinition — god til farvemønstre.</v>
       </c>
       <c r="Z17" t="str">
-        <v/>
+        <v>/garn-eksempler/drops-karisma.jpg</v>
       </c>
       <c r="AA17" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -1891,7 +1891,7 @@
         <v>Det foretrukne DK-garn fra DROPS — alsidigt, blødt og maskinvaskbart. Et af DROPS' absolut bedst sælgende garner i Danmark. Stor farvepalette og skarp pris.</v>
       </c>
       <c r="Z18" t="str">
-        <v/>
+        <v>/garn-eksempler/drops-merino-extra-fine.jpg</v>
       </c>
       <c r="AA18" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -1974,7 +1974,7 @@
         <v>Go-to bomuldsgarn til sommerstrik og karklude. Enorm farvepalette og skarp pris — under 25 kr per nøgle. OEKO-TEX certificeret. Maskinvask 40°C på skåneprogram.</v>
       </c>
       <c r="Z19" t="str">
-        <v/>
+        <v>/garn-eksempler/drops-safran.jpg</v>
       </c>
       <c r="AA19" t="str">
         <v>[{"fiber":"bomuld","percentage":100}]</v>
@@ -7620,7 +7620,7 @@
         <v>DROPS' klassiske kid silk — let, luftig holdtråd. Bruges typisk holdt sammen med et tyndt uld- eller alpakagarn for at give halo og varme. Egnet til pind 4-8 i held-together.</v>
       </c>
       <c r="Z87" t="str">
-        <v/>
+        <v>/garn-eksempler/drops-kid-silk.jpg</v>
       </c>
       <c r="AA87" t="str">
         <v>[{"fiber":"mohair","percentage":75},{"fiber":"silke","percentage":25}]</v>

--- a/content/yarns.xlsx
+++ b/content/yarns.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA89"/>
+  <dimension ref="A1:AA100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -981,7 +981,7 @@
         <v>/garn-eksempler/camarose-loevetand.jpg</v>
       </c>
       <c r="AA7" t="str">
-        <v>[{"fiber": "lin", "percentage": 100}]</v>
+        <v>[{"fiber":"hør", "percentage": 100}]</v>
       </c>
     </row>
     <row r="8">
@@ -2223,7 +2223,7 @@
         <v>Dansk merino-alpaka-blanding fra Edy Angola: 26% alpaca, 66% merino og 8% polyamid. 50g/155m på pind 3,5-5 mm — blødt, varmt og slidstærkt, godt til klassisk strik.</v>
       </c>
       <c r="Z22" t="str">
-        <v/>
+        <v>/garn-eksempler/edy-angola-alpaca-merino.jpg</v>
       </c>
       <c r="AA22" t="str">
         <v>[{"fiber": "merinould", "percentage": 66}, {"fiber": "alpaka", "percentage": 26}, {"fiber": "nylon_polyamid", "percentage": 8}]</v>
@@ -3407,10 +3407,10 @@
         <v/>
       </c>
       <c r="E37" t="str">
-        <v>uld/bomuld</v>
+        <v>uld</v>
       </c>
       <c r="F37" t="str">
-        <v>fingering</v>
+        <v>light_fingering</v>
       </c>
       <c r="G37">
         <v>50</v>
@@ -3430,26 +3430,26 @@
       <c r="L37" t="str">
         <v/>
       </c>
-      <c r="M37" t="str">
-        <v/>
+      <c r="M37">
+        <v>3</v>
       </c>
       <c r="N37" t="str">
-        <v/>
+        <v>2-trådet</v>
       </c>
       <c r="O37">
         <v>2</v>
       </c>
       <c r="P37" t="str">
-        <v/>
+        <v>plied</v>
       </c>
       <c r="Q37" t="str">
         <v/>
       </c>
       <c r="R37" t="str">
-        <v>maskinvask_30</v>
+        <v>handvask</v>
       </c>
       <c r="S37" t="str">
-        <v/>
+        <v>Danmark</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -3458,16 +3458,16 @@
         <v>i_produktion</v>
       </c>
       <c r="V37" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="W37" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="X37" t="str">
-        <v/>
+        <v>["sjaler","lette bluser","følgegarn"]</v>
       </c>
       <c r="Y37" t="str">
-        <v/>
+        <v>Coast er et meget tyndt 2-trådet garn fra danske Holst Garn, blandet af 55% merinould og 45% bomuld. Bomulden giver tyngde og holdbarhed, mens merinoulden tilfører blødhed og varme. Strikkes ofte sammen med andre garner i fair isle eller dobbelt-tråd.</v>
       </c>
       <c r="Z37" t="str">
         <v/>
@@ -3636,7 +3636,7 @@
         <v>Isagers mest populære garn og en dansk klassiker siden 1977. Blød alpaka-uldblanding med smuk farvepalet og god drapering. Ikke-superwash — bæredygtig og holdbar. Meget brugt i Isager og Helga Isager opskrifter.</v>
       </c>
       <c r="Z39" t="str">
-        <v/>
+        <v>/garn-eksempler/isager-alpaca-2.jpg</v>
       </c>
       <c r="AA39" t="str">
         <v>[{"fiber":"alpaka","percentage":50},{"fiber":"uld","percentage":50}]</v>
@@ -3968,7 +3968,7 @@
         <v>Singles-garn med karakteristisk islandsk tovhet. God til sjaler og som holdtråd.</v>
       </c>
       <c r="Z43" t="str">
-        <v/>
+        <v>/garn-eksempler/istex-einband.jpg</v>
       </c>
       <c r="AA43" t="str">
         <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
@@ -4051,7 +4051,7 @@
         <v>Light-version af Álafosslopi — halv vægt, halv tykkelse. Mest populære Lopi-kvalitet til moderne lopapeysa.</v>
       </c>
       <c r="Z44" t="str">
-        <v/>
+        <v>/garn-eksempler/istex-lettlopi.jpg</v>
       </c>
       <c r="AA44" t="str">
         <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
@@ -4134,7 +4134,7 @@
         <v>Kommer i runde plader à ca. 100 g. Kan holdes 2-3 tråde sammen for tykkere strik.</v>
       </c>
       <c r="Z45" t="str">
-        <v/>
+        <v>/garn-eksempler/istex-plotulopi.jpg</v>
       </c>
       <c r="AA45" t="str">
         <v>[{"fiber":"islandsk_uld","percentage":100}]</v>
@@ -4632,7 +4632,7 @@
         <v>KFO's suverænt mest solgte garn og det mest profilerede bæredygtige garnmærke i Danmark. Non-superwash, mulesing-fri og OEKO-TEX certificeret. Smukt farvekort og meget brugt i baby- og børnestrik.</v>
       </c>
       <c r="Z51" t="str">
-        <v/>
+        <v>/garn-eksempler/knitting-for-olive-merino.jpg</v>
       </c>
       <c r="AA51" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -5545,7 +5545,7 @@
         <v/>
       </c>
       <c r="Z62" t="str">
-        <v/>
+        <v>/garn-eksempler/mayflower-nordia.jpg</v>
       </c>
       <c r="AA62" t="str">
         <v>[{"fiber":"uld","percentage":51},{"fiber":"acryl","percentage":34},{"fiber":"nylon_polyamid","percentage":15}]</v>
@@ -6395,7 +6395,7 @@
         <v/>
       </c>
       <c r="E73" t="str">
-        <v>bomuld/viskose/lin</v>
+        <v>bomuld/viskose/hør</v>
       </c>
       <c r="F73" t="str">
         <v>dk</v>
@@ -6461,7 +6461,7 @@
         <v/>
       </c>
       <c r="AA73" t="str">
-        <v>[{"fiber":"bomuld","percentage":53},{"fiber":"viskose","percentage":33},{"fiber":"lin","percentage":14}]</v>
+        <v>[{"fiber":"bomuld","percentage":53},{"fiber":"viskose","percentage":33},{"fiber":"hør","percentage":14}]</v>
       </c>
     </row>
     <row r="74">
@@ -7540,7 +7540,7 @@
         <v/>
       </c>
       <c r="AA86" t="str">
-        <v>[{"fiber":"bomuld","percentage":73},{"fiber":"lin","percentage":27}]</v>
+        <v>[{"fiber":"bomuld","percentage":73},{"fiber":"hør","percentage":27}]</v>
       </c>
     </row>
     <row r="87">
@@ -7792,9 +7792,922 @@
         <v>[{"fiber":"merinould","percentage":100}]</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v/>
+      </c>
+      <c r="B90" t="str">
+        <v>Filcolana</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Saga</v>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v>uld</v>
+      </c>
+      <c r="F90" t="str">
+        <v>light_fingering</v>
+      </c>
+      <c r="G90">
+        <v>50</v>
+      </c>
+      <c r="H90">
+        <v>600</v>
+      </c>
+      <c r="I90">
+        <v>2.5</v>
+      </c>
+      <c r="J90">
+        <v>3</v>
+      </c>
+      <c r="K90">
+        <v>26</v>
+      </c>
+      <c r="L90">
+        <v>38</v>
+      </c>
+      <c r="M90">
+        <v>3</v>
+      </c>
+      <c r="N90" t="str">
+        <v>2-trådet lambsuld</v>
+      </c>
+      <c r="O90">
+        <v>2</v>
+      </c>
+      <c r="P90" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
+      <c r="T90" t="str">
+        <v>Falklandsøerne</v>
+      </c>
+      <c r="U90" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V90" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W90" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X90" t="str">
+        <v>["sjaler","lette bluser","babytøj"]</v>
+      </c>
+      <c r="Y90" t="str">
+        <v>Saga er et tyndt, blødt 2-trådet garn af 100% lambsuld fra Falklandsøerne. Det er let, varmt og elastisk og velegnet til sjaler, lette bluser og babytøj. En god alternativ til klassiske fingering-garner når man ønsker noget endnu tyndere.</v>
+      </c>
+      <c r="Z90" t="str">
+        <v/>
+      </c>
+      <c r="AA90" t="str">
+        <v>[{"fiber":"uld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v/>
+      </c>
+      <c r="B91" t="str">
+        <v>BC Garn</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Semilla Cable</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v>uld</v>
+      </c>
+      <c r="F91" t="str">
+        <v>dk</v>
+      </c>
+      <c r="G91">
+        <v>50</v>
+      </c>
+      <c r="H91">
+        <v>290</v>
+      </c>
+      <c r="I91">
+        <v>3.5</v>
+      </c>
+      <c r="J91">
+        <v>4.5</v>
+      </c>
+      <c r="K91">
+        <v>20</v>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91">
+        <v>4</v>
+      </c>
+      <c r="N91" t="str">
+        <v>kablet</v>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v>cabled</v>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S91" t="str">
+        <v>Italien</v>
+      </c>
+      <c r="T91" t="str">
+        <v>Argentina</v>
+      </c>
+      <c r="U91" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V91" t="str">
+        <v>["GOTS"]</v>
+      </c>
+      <c r="W91" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X91" t="str">
+        <v>["sweatre","cardigans","børnetøj","tilbehør"]</v>
+      </c>
+      <c r="Y91" t="str">
+        <v>Semilla Cablé er den kablede DK-version af BC Garns Semilla-serie — 100% økologisk uld, GOTS-certificeret og blødt vasket uden klorin. Den kablede konstruktion giver et stabilt og elastisk garn med god maskedefinition. Råvaren er fra GOTS-certificerede gårde i Argentina, spundet og farvet i Italien.</v>
+      </c>
+      <c r="Z91" t="str">
+        <v/>
+      </c>
+      <c r="AA91" t="str">
+        <v>[{"fiber":"uld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v/>
+      </c>
+      <c r="B92" t="str">
+        <v>Hjertegarn</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Incawool</v>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v>uld</v>
+      </c>
+      <c r="F92" t="str">
+        <v>aran</v>
+      </c>
+      <c r="G92">
+        <v>100</v>
+      </c>
+      <c r="H92">
+        <v>160</v>
+      </c>
+      <c r="I92">
+        <v>4.5</v>
+      </c>
+      <c r="J92">
+        <v>5</v>
+      </c>
+      <c r="K92">
+        <v>18</v>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92">
+        <v>5</v>
+      </c>
+      <c r="N92" t="str">
+        <v>enkelttrådet højlandsuld</v>
+      </c>
+      <c r="O92">
+        <v>1</v>
+      </c>
+      <c r="P92" t="str">
+        <v>singles</v>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
+      <c r="T92" t="str">
+        <v>Peru</v>
+      </c>
+      <c r="U92" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V92" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W92" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X92" t="str">
+        <v>["sweatre","cardigans","huer","tæpper"]</v>
+      </c>
+      <c r="Y92" t="str">
+        <v>Incawool er et klassisk enkelt-trådet garn af 100% peruviansk højlandsuld. De fine, glatte fibre giver et blødt men robust garn der holder formen og er behageligt mod huden. Velegnet til varme strik som sweatre, cardigans og tæpper.</v>
+      </c>
+      <c r="Z92" t="str">
+        <v/>
+      </c>
+      <c r="AA92" t="str">
+        <v>[{"fiber":"uld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v/>
+      </c>
+      <c r="B93" t="str">
+        <v>Drops</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Andes</v>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v>uld</v>
+      </c>
+      <c r="F93" t="str">
+        <v>super_bulky</v>
+      </c>
+      <c r="G93">
+        <v>100</v>
+      </c>
+      <c r="H93">
+        <v>90</v>
+      </c>
+      <c r="I93">
+        <v>8</v>
+      </c>
+      <c r="J93">
+        <v>10</v>
+      </c>
+      <c r="K93">
+        <v>10</v>
+      </c>
+      <c r="L93">
+        <v>14</v>
+      </c>
+      <c r="M93">
+        <v>9</v>
+      </c>
+      <c r="N93" t="str">
+        <v>2-trådet</v>
+      </c>
+      <c r="O93">
+        <v>2</v>
+      </c>
+      <c r="P93" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S93" t="str">
+        <v>Peru</v>
+      </c>
+      <c r="T93" t="str">
+        <v>Sydamerika</v>
+      </c>
+      <c r="U93" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V93" t="str">
+        <v>["Oeko-Tex Standard 100"]</v>
+      </c>
+      <c r="W93" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X93" t="str">
+        <v>["sweatre","jakker","tæpper","huer"]</v>
+      </c>
+      <c r="Y93" t="str">
+        <v>Andes er et blødt og tykt garn spundet af 65% uld og 35% superfin alpaka. Alpakaen giver en silkeagtig overflade og glans, mens ulden bidrager med formstabilitet. Velegnet til hurtige projekter som sweatre, jakker og varme tæpper.</v>
+      </c>
+      <c r="Z93" t="str">
+        <v>/garn-eksempler/drops-andes.jpg</v>
+      </c>
+      <c r="AA93" t="str">
+        <v>[{"fiber":"uld","percentage":65},{"fiber":"alpaka","percentage":35}]</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v/>
+      </c>
+      <c r="B94" t="str">
+        <v>Drops</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Snow</v>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v>uld</v>
+      </c>
+      <c r="F94" t="str">
+        <v>super_bulky</v>
+      </c>
+      <c r="G94">
+        <v>50</v>
+      </c>
+      <c r="H94">
+        <v>100</v>
+      </c>
+      <c r="I94">
+        <v>8</v>
+      </c>
+      <c r="J94">
+        <v>10</v>
+      </c>
+      <c r="K94">
+        <v>10</v>
+      </c>
+      <c r="L94">
+        <v>14</v>
+      </c>
+      <c r="M94">
+        <v>9</v>
+      </c>
+      <c r="N94" t="str">
+        <v>enkelttrådet</v>
+      </c>
+      <c r="O94">
+        <v>1</v>
+      </c>
+      <c r="P94" t="str">
+        <v>singles</v>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
+      <c r="T94" t="str">
+        <v>Sydamerika</v>
+      </c>
+      <c r="U94" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V94" t="str">
+        <v>["Oeko-Tex Standard 100"]</v>
+      </c>
+      <c r="W94" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X94" t="str">
+        <v>["sweatre","huer","tørklæder","filtning"]</v>
+      </c>
+      <c r="Y94" t="str">
+        <v>Snow (tidligere kaldet Drops Eskimo) er et blødt, tykt enkelt-trådet garn af 100% uld. Fibrene er ubehandlede — kun vasket og ikke kemisk behandlet inden farvning — hvilket fremhæver uldens naturlige egenskaber og giver god form og struktur. Velegnet til filtning.</v>
+      </c>
+      <c r="Z94" t="str">
+        <v>/garn-eksempler/drops-snow.jpg</v>
+      </c>
+      <c r="AA94" t="str">
+        <v>[{"fiber":"uld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v/>
+      </c>
+      <c r="B95" t="str">
+        <v>Drops</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Polaris</v>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v>uld</v>
+      </c>
+      <c r="F95" t="str">
+        <v>jumbo</v>
+      </c>
+      <c r="G95">
+        <v>100</v>
+      </c>
+      <c r="H95">
+        <v>36</v>
+      </c>
+      <c r="I95">
+        <v>10</v>
+      </c>
+      <c r="J95">
+        <v>15</v>
+      </c>
+      <c r="K95">
+        <v>8</v>
+      </c>
+      <c r="L95">
+        <v>10</v>
+      </c>
+      <c r="M95">
+        <v>12</v>
+      </c>
+      <c r="N95" t="str">
+        <v>enkelttrådet</v>
+      </c>
+      <c r="O95">
+        <v>1</v>
+      </c>
+      <c r="P95" t="str">
+        <v>singles</v>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
+      <c r="R95" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
+      <c r="T95" t="str">
+        <v>Sydamerika</v>
+      </c>
+      <c r="U95" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V95" t="str">
+        <v>["Oeko-Tex Standard 100"]</v>
+      </c>
+      <c r="W95" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X95" t="str">
+        <v>["tæpper","huer","tørklæder","ponchos"]</v>
+      </c>
+      <c r="Y95" t="str">
+        <v>Polaris er et af Drops' tykkeste garner — et enkelt-trådet garn af samme bløde uld som Snow, men meget kraftigere. Strikkes på pinde 10–15 mm og er ideelt til hurtige indretningsprojekter, varme huer, tørklæder og ponchos.</v>
+      </c>
+      <c r="Z95" t="str">
+        <v>/garn-eksempler/drops-polaris.jpg</v>
+      </c>
+      <c r="AA95" t="str">
+        <v>[{"fiber":"uld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v/>
+      </c>
+      <c r="B96" t="str">
+        <v>Lang Yarns</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Merino 120</v>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v>merinould</v>
+      </c>
+      <c r="F96" t="str">
+        <v>dk</v>
+      </c>
+      <c r="G96">
+        <v>50</v>
+      </c>
+      <c r="H96">
+        <v>240</v>
+      </c>
+      <c r="I96">
+        <v>3.5</v>
+      </c>
+      <c r="J96">
+        <v>4.5</v>
+      </c>
+      <c r="K96">
+        <v>22</v>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96">
+        <v>4</v>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q96" t="str">
+        <v>superwash</v>
+      </c>
+      <c r="R96" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
+      <c r="T96" t="str">
+        <v/>
+      </c>
+      <c r="U96" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V96" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W96" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X96" t="str">
+        <v>["sweatre","cardigans","tilbehør","babytøj"]</v>
+      </c>
+      <c r="Y96" t="str">
+        <v>Merino 120 er et klassisk DK-garn af 100% merinould (extrafine), superwash-behandlet så det kan maskinvaskes. Velegnet til hverdagsstrik, babytøj og tilbehør hvor pleje skal være enkel.</v>
+      </c>
+      <c r="Z96" t="str">
+        <v>/garn-eksempler/lang-yarns-merino-120.jpg</v>
+      </c>
+      <c r="AA96" t="str">
+        <v>[{"fiber":"merinould","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v/>
+      </c>
+      <c r="B97" t="str">
+        <v>Isager</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Trio 1</v>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v>hør</v>
+      </c>
+      <c r="F97" t="str">
+        <v>light_fingering</v>
+      </c>
+      <c r="G97">
+        <v>50</v>
+      </c>
+      <c r="H97">
+        <v>700</v>
+      </c>
+      <c r="I97">
+        <v>2.5</v>
+      </c>
+      <c r="J97">
+        <v>3</v>
+      </c>
+      <c r="K97">
+        <v>26</v>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97">
+        <v>3</v>
+      </c>
+      <c r="N97" t="str">
+        <v>3-trådet</v>
+      </c>
+      <c r="O97">
+        <v>3</v>
+      </c>
+      <c r="P97" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S97" t="str">
+        <v>Italien</v>
+      </c>
+      <c r="T97" t="str">
+        <v/>
+      </c>
+      <c r="U97" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V97" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W97" t="str">
+        <v>["sommer"]</v>
+      </c>
+      <c r="X97" t="str">
+        <v>["sommerbluser","sjaler","tørklæder","lette projekter"]</v>
+      </c>
+      <c r="Y97" t="str">
+        <v>Trio 1 er et tyndt 3-trådet plante-garn af 50% hør, 30% bomuld og 20% tencel. Det har en let, kølig karakter og er velegnet til sommerstrik som lette bluser og sjaler. Spundet og farvet i Italien.</v>
+      </c>
+      <c r="Z97" t="str">
+        <v>/garn-eksempler/isager-trio-1.jpg</v>
+      </c>
+      <c r="AA97" t="str">
+        <v>[{"fiber":"hør","percentage":50},{"fiber":"bomuld","percentage":30},{"fiber":"tencel","percentage":20}]</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v/>
+      </c>
+      <c r="B98" t="str">
+        <v>Isager</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Soft</v>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v>alpaka</v>
+      </c>
+      <c r="F98" t="str">
+        <v>bulky</v>
+      </c>
+      <c r="G98">
+        <v>50</v>
+      </c>
+      <c r="H98">
+        <v>250</v>
+      </c>
+      <c r="I98">
+        <v>5.5</v>
+      </c>
+      <c r="J98">
+        <v>6</v>
+      </c>
+      <c r="K98">
+        <v>16</v>
+      </c>
+      <c r="L98">
+        <v>25</v>
+      </c>
+      <c r="M98">
+        <v>6</v>
+      </c>
+      <c r="N98" t="str">
+        <v>luftigt blanding</v>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S98" t="str">
+        <v>Peru</v>
+      </c>
+      <c r="T98" t="str">
+        <v>Peru</v>
+      </c>
+      <c r="U98" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V98" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W98" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X98" t="str">
+        <v>["sweatre","jakker","tæpper","huer"]</v>
+      </c>
+      <c r="Y98" t="str">
+        <v>Soft er et blødt, luftigt garn af 56% alpaka og 44% økologisk bomuld. Alpakaen giver varme og glans, mens bomulden tilfører tyngde og struktur. Velegnet til hurtige projekter og varme strik.</v>
+      </c>
+      <c r="Z98" t="str">
+        <v>/garn-eksempler/isager-soft.jpg</v>
+      </c>
+      <c r="AA98" t="str">
+        <v>[{"fiber":"alpaka","percentage":56},{"fiber":"oekologisk_bomuld","percentage":44}]</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v/>
+      </c>
+      <c r="B99" t="str">
+        <v>Kit Couture</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Cashmere</v>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v>kashmir</v>
+      </c>
+      <c r="F99" t="str">
+        <v>light_fingering</v>
+      </c>
+      <c r="G99">
+        <v>25</v>
+      </c>
+      <c r="H99">
+        <v>700</v>
+      </c>
+      <c r="I99">
+        <v>2.5</v>
+      </c>
+      <c r="J99">
+        <v>3.5</v>
+      </c>
+      <c r="K99">
+        <v>28</v>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99">
+        <v>3</v>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S99" t="str">
+        <v>Italien</v>
+      </c>
+      <c r="T99" t="str">
+        <v/>
+      </c>
+      <c r="U99" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V99" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W99" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X99" t="str">
+        <v>["sweatre","cardigans","tørklæder","luksus-projekter"]</v>
+      </c>
+      <c r="Y99" t="str">
+        <v>Cashmere fra Kit Couture er et tyndt, blødt og temperatur-regulerende garn af 100% kashmir. Det er produceret hos Kit Coutures faste italienske spinderi i Norditalien. Perfekt til luksuriøse projekter hvor blødhed mod huden er afgørende.</v>
+      </c>
+      <c r="Z99" t="str">
+        <v>/garn-eksempler/kit-couture-cashmere.jpg</v>
+      </c>
+      <c r="AA99" t="str">
+        <v>[{"fiber":"kashmir","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v/>
+      </c>
+      <c r="B100" t="str">
+        <v>Katia</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Linen</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Natural Selection</v>
+      </c>
+      <c r="E100" t="str">
+        <v>bomuld</v>
+      </c>
+      <c r="F100" t="str">
+        <v>dk</v>
+      </c>
+      <c r="G100">
+        <v>50</v>
+      </c>
+      <c r="H100">
+        <v>224</v>
+      </c>
+      <c r="I100">
+        <v>3.5</v>
+      </c>
+      <c r="J100">
+        <v>4</v>
+      </c>
+      <c r="K100">
+        <v>22</v>
+      </c>
+      <c r="L100">
+        <v>29</v>
+      </c>
+      <c r="M100">
+        <v>4</v>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
+      <c r="T100" t="str">
+        <v/>
+      </c>
+      <c r="U100" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V100" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W100" t="str">
+        <v>["sommer"]</v>
+      </c>
+      <c r="X100" t="str">
+        <v>["sommerbluser","tilbehør","tæpper"]</v>
+      </c>
+      <c r="Y100" t="str">
+        <v>Linen fra Katias Natural Selection-serie er et DK-vægtet garn af 53% bomuld og 47% lin. Bomulden gør det blødere og lettere at strikke end rent hørgarn, mens hørren giver en kølig drape og struktur. Velegnet til sommerstrik. Kan maskinvaskes ved 30°.</v>
+      </c>
+      <c r="Z100" t="str">
+        <v>/garn-eksempler/katia-linen.jpg</v>
+      </c>
+      <c r="AA100" t="str">
+        <v>[{"fiber":"bomuld","percentage":53},{"fiber":"hør","percentage":47}]</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA89"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA100"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/content/yarns.xlsx
+++ b/content/yarns.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA100"/>
+  <dimension ref="A1:AA108"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -563,7 +563,7 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v/>
+        <v>/garn-eksempler/bc-garn-bio-balance.jpg</v>
       </c>
       <c r="AA2" t="str">
         <v>[{"fiber":"uld","percentage":55},{"fiber":"bomuld","percentage":45}]</v>
@@ -729,7 +729,7 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v/>
+        <v>/garn-eksempler/bc-garn-semilla-grosso.jpg</v>
       </c>
       <c r="AA4" t="str">
         <v>[{"fiber":"uld","percentage":100}]</v>
@@ -3387,7 +3387,7 @@
         <v>Klassisk dansk storsælger fra Hjertegarn — bredt tilgængeligt i hele Danmark og meget prisvenligt. Superwash-behandlet merino i DK-tykkelse. Stor farvepalette og god kvalitet til hverdagsprojekter.</v>
       </c>
       <c r="Z36" t="str">
-        <v/>
+        <v>/garn-eksempler/hjertegarn-extrafine-merino-90.jpg</v>
       </c>
       <c r="AA36" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -4798,7 +4798,7 @@
         <v/>
       </c>
       <c r="Z53" t="str">
-        <v/>
+        <v>/garn-eksempler/lana-grossa-cool-wool.jpg</v>
       </c>
       <c r="AA53" t="str">
         <v>[{"fiber":"merinould","percentage":100}]</v>
@@ -5047,7 +5047,7 @@
         <v/>
       </c>
       <c r="Z56" t="str">
-        <v/>
+        <v>/garn-eksempler/lang-yarns-jawoll-superwash.jpg</v>
       </c>
       <c r="AA56" t="str">
         <v>[{"fiber":"uld","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
@@ -8705,9 +8705,673 @@
         <v>[{"fiber":"bomuld","percentage":53},{"fiber":"hør","percentage":47}]</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v/>
+      </c>
+      <c r="B101" t="str">
+        <v>Hjertegarn</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Børstet Uld</v>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v>uld/alpaka</v>
+      </c>
+      <c r="F101" t="str">
+        <v>bulky</v>
+      </c>
+      <c r="G101">
+        <v>50</v>
+      </c>
+      <c r="H101">
+        <v>300</v>
+      </c>
+      <c r="I101">
+        <v>7</v>
+      </c>
+      <c r="J101">
+        <v>8</v>
+      </c>
+      <c r="K101">
+        <v>14</v>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101">
+        <v>7</v>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v>brushed_singles</v>
+      </c>
+      <c r="Q101" t="str">
+        <v>brushed</v>
+      </c>
+      <c r="R101" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
+      <c r="T101" t="str">
+        <v/>
+      </c>
+      <c r="U101" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V101" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W101" t="str">
+        <v>["vinter"]</v>
+      </c>
+      <c r="X101" t="str">
+        <v>["sweatre","jakker","huer","tørklæder","tæpper"]</v>
+      </c>
+      <c r="Y101" t="str">
+        <v>Børstet Uld fra Hjertegarn er et luftigt, lodden garn af 57% uld, 25% alpaka og 18% nylon. Den børstede overflade giver varme og volumen uden at gøre strikket tungt. Velegnet til hurtige projekter på pind 7-8 — sweatre, jakker og varme tilbehør.</v>
+      </c>
+      <c r="Z101" t="str">
+        <v>/garn-eksempler/hjertegarn-borstet-uld.jpg</v>
+      </c>
+      <c r="AA101" t="str">
+        <v>[{"fiber":"uld","percentage":57},{"fiber":"alpaka","percentage":25},{"fiber":"nylon_polyamid","percentage":18}]</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v/>
+      </c>
+      <c r="B102" t="str">
+        <v>Hjertegarn</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Bamboo Wool</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v>uld-blanding</v>
+      </c>
+      <c r="F102" t="str">
+        <v>fingering</v>
+      </c>
+      <c r="G102">
+        <v>50</v>
+      </c>
+      <c r="H102">
+        <v>400</v>
+      </c>
+      <c r="I102">
+        <v>2.5</v>
+      </c>
+      <c r="J102">
+        <v>3</v>
+      </c>
+      <c r="K102">
+        <v>28</v>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102">
+        <v>3</v>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q102" t="str">
+        <v>superwash</v>
+      </c>
+      <c r="R102" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
+      <c r="T102" t="str">
+        <v/>
+      </c>
+      <c r="U102" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V102" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W102" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X102" t="str">
+        <v>["sokker","strømper","lette sweatre","babytøj"]</v>
+      </c>
+      <c r="Y102" t="str">
+        <v>Bamboo Wool fra Hjertegarn er et fingering-vægtet sok-/pulover-garn af 55% uld superwash, 30% bambus-viskose og 15% nylon. Bambusandelen giver et let, kølende skær og glat overflade, mens superwash-uld og nylon gør det slidstærkt — perfekt til sokker. Kan maskinvaskes ved uldprogram 30°.</v>
+      </c>
+      <c r="Z102" t="str">
+        <v>/garn-eksempler/hjertegarn-bamboo-wool.jpg</v>
+      </c>
+      <c r="AA102" t="str">
+        <v>[{"fiber":"uld","percentage":55},{"fiber":"viskose","percentage":30},{"fiber":"nylon_polyamid","percentage":15}]</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v/>
+      </c>
+      <c r="B103" t="str">
+        <v>Hjertegarn</v>
+      </c>
+      <c r="C103" t="str">
+        <v>New Arezzo</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v>plantefiber-blanding</v>
+      </c>
+      <c r="F103" t="str">
+        <v>sport</v>
+      </c>
+      <c r="G103">
+        <v>50</v>
+      </c>
+      <c r="H103">
+        <v>300</v>
+      </c>
+      <c r="I103">
+        <v>3</v>
+      </c>
+      <c r="J103">
+        <v>3.5</v>
+      </c>
+      <c r="K103">
+        <v>26</v>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103">
+        <v>3</v>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v>maskinvask_40</v>
+      </c>
+      <c r="S103" t="str">
+        <v/>
+      </c>
+      <c r="T103" t="str">
+        <v/>
+      </c>
+      <c r="U103" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V103" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W103" t="str">
+        <v>["sommer"]</v>
+      </c>
+      <c r="X103" t="str">
+        <v>["sommerbluser","tilbehør","lette projekter"]</v>
+      </c>
+      <c r="Y103" t="str">
+        <v>New Arezzo fra Hjertegarn er et plantegarn af 47% bambus-viskose, 33% hør og 20% bomuld. Bambus tilfører blødhed og glans, mens hør giver struktur og kølig drape — ideelt til sommerstrik som lette bluser og tilbehør. Strikkes på pind 3-3½ med ca. 26 masker pr. 10 cm.</v>
+      </c>
+      <c r="Z103" t="str">
+        <v>/garn-eksempler/hjertegarn-new-arezzo.jpg</v>
+      </c>
+      <c r="AA103" t="str">
+        <v>[{"fiber":"viskose","percentage":47},{"fiber":"hør","percentage":33},{"fiber":"bomuld","percentage":20}]</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v/>
+      </c>
+      <c r="B104" t="str">
+        <v>Hjertegarn</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Alpaca 400</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v>alpaka</v>
+      </c>
+      <c r="F104" t="str">
+        <v>lace</v>
+      </c>
+      <c r="G104">
+        <v>50</v>
+      </c>
+      <c r="H104">
+        <v>800</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
+      </c>
+      <c r="J104">
+        <v>3</v>
+      </c>
+      <c r="K104">
+        <v>30</v>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104">
+        <v>2.5</v>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v>singles</v>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S104" t="str">
+        <v/>
+      </c>
+      <c r="T104" t="str">
+        <v/>
+      </c>
+      <c r="U104" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V104" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W104" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X104" t="str">
+        <v>["sjaler","tørklæder","blonder","følgegarn"]</v>
+      </c>
+      <c r="Y104" t="str">
+        <v>Alpaca 400 fra Hjertegarn er et tyndt lace-garn af 100% alpaka med 400 m pr. 50 g. Velegnet til sjaler og fine tørklæder, eller som følgegarn der gør tykkere garner blødere og lettere. Strikkes på pind 2-3 med ca. 30 masker pr. 10 cm. Håndvaskes.</v>
+      </c>
+      <c r="Z104" t="str">
+        <v>/garn-eksempler/hjertegarn-alpaca-400.jpg</v>
+      </c>
+      <c r="AA104" t="str">
+        <v>[{"fiber":"alpaka","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v/>
+      </c>
+      <c r="B105" t="str">
+        <v>Hjertegarn</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Dream Air</v>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v>uld/alpaka/nylon</v>
+      </c>
+      <c r="F105" t="str">
+        <v>bulky</v>
+      </c>
+      <c r="G105">
+        <v>50</v>
+      </c>
+      <c r="H105">
+        <v>400</v>
+      </c>
+      <c r="I105">
+        <v>6</v>
+      </c>
+      <c r="J105">
+        <v>6</v>
+      </c>
+      <c r="K105">
+        <v>17</v>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105">
+        <v>6</v>
+      </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v>brushed_singles</v>
+      </c>
+      <c r="Q105" t="str">
+        <v>brushed</v>
+      </c>
+      <c r="R105" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S105" t="str">
+        <v/>
+      </c>
+      <c r="T105" t="str">
+        <v/>
+      </c>
+      <c r="U105" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V105" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W105" t="str">
+        <v>["vinter"]</v>
+      </c>
+      <c r="X105" t="str">
+        <v>["sweatre","cardigans","jakker","tæpper"]</v>
+      </c>
+      <c r="Y105" t="str">
+        <v>Dream Air fra Hjertegarn er et fabelagtigt blødt og luftigt børstet garn af 53% uld, 22% alpaka og 25% nylon. Trods tyngden strikker det op til en let og varm trøje — som at have luft på kroppen. Strikkes på pind 6 med ca. 17 masker pr. 10 cm. Håndvaskes.</v>
+      </c>
+      <c r="Z105" t="str">
+        <v>/garn-eksempler/hjertegarn-dream-air.jpg</v>
+      </c>
+      <c r="AA105" t="str">
+        <v>[{"fiber":"uld","percentage":53},{"fiber":"nylon_polyamid","percentage":25},{"fiber":"alpaka","percentage":22}]</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v/>
+      </c>
+      <c r="B106" t="str">
+        <v>Hjertegarn</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Brushed Armonia</v>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v>merino/nylon</v>
+      </c>
+      <c r="F106" t="str">
+        <v>fingering</v>
+      </c>
+      <c r="G106">
+        <v>50</v>
+      </c>
+      <c r="H106">
+        <v>400</v>
+      </c>
+      <c r="I106">
+        <v>3</v>
+      </c>
+      <c r="J106">
+        <v>4</v>
+      </c>
+      <c r="K106">
+        <v>28</v>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106">
+        <v>3</v>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v>brushed_singles</v>
+      </c>
+      <c r="Q106" t="str">
+        <v>brushed</v>
+      </c>
+      <c r="R106" t="str">
+        <v>maskinvask_30</v>
+      </c>
+      <c r="S106" t="str">
+        <v/>
+      </c>
+      <c r="T106" t="str">
+        <v/>
+      </c>
+      <c r="U106" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V106" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W106" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X106" t="str">
+        <v>["sweatre","cardigans","tilbehør","babytøj"]</v>
+      </c>
+      <c r="Y106" t="str">
+        <v>Brushed Armonia (Børstet Superfine Merino) fra Hjertegarn er et blødt, let børstet 4-trådet garn af 75% superwash merinould og 25% nylon. Børstningen giver et delikat halo, mens nylonet sikrer holdbarhed. Kan maskinvaskes ved uldprogram 30°. Strikkes på pind 3-4.</v>
+      </c>
+      <c r="Z106" t="str">
+        <v>/garn-eksempler/hjertegarn-brushed-armonia.jpg</v>
+      </c>
+      <c r="AA106" t="str">
+        <v>[{"fiber":"merinould","percentage":75},{"fiber":"nylon_polyamid","percentage":25}]</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v/>
+      </c>
+      <c r="B107" t="str">
+        <v>Hjertegarn</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Lima</v>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v>uld</v>
+      </c>
+      <c r="F107" t="str">
+        <v>worsted</v>
+      </c>
+      <c r="G107">
+        <v>50</v>
+      </c>
+      <c r="H107">
+        <v>200</v>
+      </c>
+      <c r="I107">
+        <v>4.5</v>
+      </c>
+      <c r="J107">
+        <v>5</v>
+      </c>
+      <c r="K107">
+        <v>20</v>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107">
+        <v>5</v>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v>plied</v>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S107" t="str">
+        <v/>
+      </c>
+      <c r="T107" t="str">
+        <v>Peru</v>
+      </c>
+      <c r="U107" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V107" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W107" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X107" t="str">
+        <v>["sweatre","huer","vanter","tilbehør","filtning"]</v>
+      </c>
+      <c r="Y107" t="str">
+        <v>Lima fra Hjertegarn er et worsted-vægtet garn af 100% blød uld fra Peru. Garnet kradser mindre end mange tilsvarende kvaliteter og er velegnet til både børne- og voksenstrik. Kan filtes. Strikkes på pind 4½-5 med ca. 20 masker pr. 10 cm. Håndvaskes ved 30°.</v>
+      </c>
+      <c r="Z107" t="str">
+        <v>/garn-eksempler/hjertegarn-lima.jpg</v>
+      </c>
+      <c r="AA107" t="str">
+        <v>[{"fiber":"uld","percentage":100}]</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v/>
+      </c>
+      <c r="B108" t="str">
+        <v>Nordic Sky</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Kiruna</v>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v>alpaka/merino/nylon</v>
+      </c>
+      <c r="F108" t="str">
+        <v>worsted</v>
+      </c>
+      <c r="G108">
+        <v>50</v>
+      </c>
+      <c r="H108">
+        <v>300</v>
+      </c>
+      <c r="I108">
+        <v>5</v>
+      </c>
+      <c r="J108">
+        <v>5</v>
+      </c>
+      <c r="K108">
+        <v>17</v>
+      </c>
+      <c r="L108">
+        <v>22</v>
+      </c>
+      <c r="M108">
+        <v>5</v>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v>chainette</v>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108" t="str">
+        <v>handvask</v>
+      </c>
+      <c r="S108" t="str">
+        <v>Sverige</v>
+      </c>
+      <c r="T108" t="str">
+        <v/>
+      </c>
+      <c r="U108" t="str">
+        <v>i_produktion</v>
+      </c>
+      <c r="V108" t="str">
+        <v>[]</v>
+      </c>
+      <c r="W108" t="str">
+        <v>[]</v>
+      </c>
+      <c r="X108" t="str">
+        <v>["sweatre","cardigans","huer","tørklæder"]</v>
+      </c>
+      <c r="Y108" t="str">
+        <v>Kiruna fra svenske Nordic Sky er et "blow yarn" af 63% baby-alpaka, 30% nylon og 7% merino. Fibrene blæses gennem et chainette-rør i stedet for at blive spundet på traditionel vis — det giver et meget let, blødt og volumiøst garn. Strikkes på pind 5 med 17 masker og 22 pinde pr. 10 cm. Håndvaskes ved 30°.</v>
+      </c>
+      <c r="Z108" t="str">
+        <v>/garn-eksempler/nordic-sky-kiruna.jpg</v>
+      </c>
+      <c r="AA108" t="str">
+        <v>[{"fiber":"baby_alpaka","percentage":63},{"fiber":"nylon_polyamid","percentage":30},{"fiber":"merinould","percentage":7}]</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA108"/>
   </ignoredErrors>
 </worksheet>
 </file>
